--- a/spec/fixtures/batch_submission_manifest_errors_test.xlsx
+++ b/spec/fixtures/batch_submission_manifest_errors_test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smc101/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smc101/vagrant/morphosource-vagrant/MorphoSource_SF/spec/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D00219F-5B23-5F44-BC12-95CEE2F1B68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{513E6CE7-33BA-AB48-81AF-B560B7A5C81D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="32000" windowHeight="16280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="32000" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="273">
   <si>
     <t>Field Section</t>
   </si>
@@ -188,12 +188,6 @@
   </si>
   <si>
     <t>Shading correction</t>
-  </si>
-  <si>
-    <t>Filter material</t>
-  </si>
-  <si>
-    <t>Filter thickness</t>
   </si>
   <si>
     <t>Frame averaging</t>
@@ -534,15 +528,6 @@
 Gynandromorph: Gynandromorph</t>
   </si>
   <si>
-    <t>Molybdenum: Molybdenum
-Aluminum: Aluminum
-Copper: Copper
-Rhodium: Rhodium
-Niobium: Niobium
-Europium: Europium
-Lead: Lead</t>
-  </si>
-  <si>
     <t>Reflection: Reflection
 Transmission: Transmission</t>
   </si>
@@ -739,12 +724,6 @@
     <t>imaging_event.ct.shading_correction</t>
   </si>
   <si>
-    <t>imaging_event.ct.filter_material</t>
-  </si>
-  <si>
-    <t>imaging_event.ct.filter_thickness</t>
-  </si>
-  <si>
     <t>imaging_event.ct.frame_averaging</t>
   </si>
   <si>
@@ -920,6 +899,12 @@
   </si>
   <si>
     <t>ce447a9f-1500-43d6-83c2-59de00c6ca9c</t>
+  </si>
+  <si>
+    <t>Filter</t>
+  </si>
+  <si>
+    <t>imaging_event.ct.ie_filter</t>
   </si>
 </sst>
 </file>
@@ -1328,10 +1313,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06ED7EC9-286B-1D49-A57D-A989376D77CC}">
-  <dimension ref="A1:CI13"/>
+  <dimension ref="A1:CH13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:87" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:86" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1562,13 +1547,13 @@
         <v>11</v>
       </c>
       <c r="BZ1" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CA1" s="6" t="s">
         <v>12</v>
       </c>
       <c r="CB1" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CC1" s="6" t="s">
         <v>13</v>
@@ -1576,8 +1561,8 @@
       <c r="CD1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="CE1" s="6" t="s">
-        <v>13</v>
+      <c r="CE1" s="24" t="s">
+        <v>14</v>
       </c>
       <c r="CF1" s="24" t="s">
         <v>14</v>
@@ -1588,11 +1573,8 @@
       <c r="CH1" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="CI1" s="24" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="2" spans="1:87" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:86" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
@@ -1737,165 +1719,162 @@
         <v>55</v>
       </c>
       <c r="BD2" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="BE2" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="BE2" s="6" t="s">
+      <c r="BF2" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="BF2" s="6" t="s">
+      <c r="BG2" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="BG2" s="6" t="s">
+      <c r="BH2" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="BH2" s="6" t="s">
+      <c r="BI2" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="BI2" s="6" t="s">
+      <c r="BJ2" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="BJ2" s="6" t="s">
+      <c r="BK2" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="BK2" s="6" t="s">
+      <c r="BL2" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="BL2" s="6" t="s">
+      <c r="BM2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="BM2" s="6" t="s">
+      <c r="BN2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="BN2" s="6" t="s">
+      <c r="BO2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="BO2" s="6" t="s">
+      <c r="BP2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="BP2" s="6" t="s">
+      <c r="BQ2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="BQ2" s="6" t="s">
+      <c r="BR2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="BR2" s="6" t="s">
+      <c r="BS2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="BS2" s="6" t="s">
+      <c r="BT2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="BT2" s="6" t="s">
+      <c r="BU2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="BU2" s="6" t="s">
+      <c r="BV2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="BV2" s="6" t="s">
+      <c r="BW2" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="BW2" s="6" t="s">
+      <c r="BX2" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="BX2" s="6" t="s">
+      <c r="BY2" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="BY2" s="6" t="s">
+      <c r="BZ2" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="BZ2" s="6" t="s">
+      <c r="CA2" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="CA2" s="6" t="s">
+      <c r="CB2" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="CB2" s="6" t="s">
+      <c r="CC2" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="CC2" s="6" t="s">
+      <c r="CD2" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="CD2" s="6" t="s">
+      <c r="CE2" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="CF2" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="CG2" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="CH2" s="24" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:86" ht="139.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="CE2" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="CF2" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="CG2" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="CH2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="CI2" s="24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:87" ht="139.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="7" t="s">
+      <c r="C3" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="D3" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>87</v>
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="10"/>
       <c r="G3" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H3" s="10"/>
       <c r="I3" s="11"/>
       <c r="J3" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K3" s="12"/>
       <c r="L3" s="12"/>
       <c r="M3" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="O3" s="13" t="s">
         <v>90</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="O3" s="13" t="s">
-        <v>92</v>
       </c>
       <c r="P3" s="14"/>
       <c r="Q3" s="14"/>
       <c r="R3" s="13" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="S3" s="13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="T3" s="2"/>
       <c r="U3" s="13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="V3" s="13"/>
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="Z3" s="15" t="s">
+      <c r="AB3" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="AA3" s="15" t="s">
+      <c r="AC3" s="13" t="s">
         <v>98</v>
-      </c>
-      <c r="AB3" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="AC3" s="13" t="s">
-        <v>100</v>
       </c>
       <c r="AD3" s="14"/>
       <c r="AE3" s="2"/>
@@ -1912,7 +1891,7 @@
       <c r="AP3" s="16"/>
       <c r="AQ3" s="16"/>
       <c r="AR3" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AS3" s="17"/>
       <c r="AT3" s="17"/>
@@ -1920,141 +1899,138 @@
       <c r="AV3" s="6"/>
       <c r="AW3" s="6"/>
       <c r="AX3" s="18" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AY3" s="18"/>
       <c r="AZ3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="BA3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="BB3" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="BA3" s="19" t="s">
+      <c r="BC3" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="BB3" s="19" t="s">
+      <c r="BD3" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="BC3" s="19" t="s">
+      <c r="BE3" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="BD3" s="19" t="s">
+      <c r="BF3" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="BE3" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="BF3" s="19" t="s">
+      <c r="BG3" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="BG3" s="19" t="s">
+      <c r="BH3" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="BH3" s="19" t="s">
+      <c r="BI3" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="BI3" s="19" t="s">
+      <c r="BJ3" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="BJ3" s="19" t="s">
+      <c r="BK3" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="BK3" s="19" t="s">
+      <c r="BL3" s="18"/>
+      <c r="BM3" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="BL3" s="18" t="s">
+      <c r="BN3" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="BM3" s="18"/>
-      <c r="BN3" s="18" t="s">
+      <c r="BO3" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="BO3" s="20" t="s">
+      <c r="BP3" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="BP3" s="20" t="s">
+      <c r="BQ3" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="BQ3" s="20" t="s">
+      <c r="BR3" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="BR3" s="20" t="s">
+      <c r="BS3" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="BS3" s="18" t="s">
+      <c r="BT3" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="BT3" s="18" t="s">
+      <c r="BU3" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="BU3" s="18" t="s">
+      <c r="BV3" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="BV3" s="18" t="s">
+      <c r="BW3" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="BW3" s="18" t="s">
+      <c r="BX3" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="BX3" s="18" t="s">
+      <c r="BY3" s="19"/>
+      <c r="BZ3" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="BY3" s="18" t="s">
+      <c r="CA3" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="BZ3" s="19"/>
-      <c r="CA3" s="18" t="s">
+      <c r="CB3" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="CB3" s="18" t="s">
+      <c r="CC3" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CD3" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="CC3" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="CD3" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="CE3" s="19" t="s">
-        <v>130</v>
-      </c>
+      <c r="CE3" s="24"/>
       <c r="CF3" s="24"/>
       <c r="CG3" s="24"/>
       <c r="CH3" s="24"/>
-      <c r="CI3" s="24"/>
     </row>
-    <row r="4" spans="1:87" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:86" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>133</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
       <c r="K4" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="P4" s="14"/>
       <c r="Q4" s="14"/>
@@ -2066,13 +2042,13 @@
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
       <c r="Y4" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AB4" s="2"/>
       <c r="AC4" s="2"/>
@@ -2129,289 +2105,285 @@
       <c r="CB4" s="6"/>
       <c r="CC4" s="6"/>
       <c r="CD4" s="6"/>
-      <c r="CE4" s="6"/>
+      <c r="CE4" s="24"/>
       <c r="CF4" s="24"/>
       <c r="CG4" s="24"/>
       <c r="CH4" s="24"/>
-      <c r="CI4" s="24"/>
     </row>
-    <row r="5" spans="1:87" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:86" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="F5" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="W5" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="X5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AB5" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AD5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF5" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG5" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AH5" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="AI5" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AJ5" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AK5" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="AL5" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="M5" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="N5" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q5" s="2" t="s">
+      <c r="AM5" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AN5" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AO5" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AP5" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="AQ5" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="AR5" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="AS5" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="AT5" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="AU5" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="AV5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AW5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AX5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AY5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AZ5" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="R5" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="W5" s="2" t="s">
+      <c r="BA5" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="X5" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y5" s="2" t="s">
+      <c r="BB5" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="BC5" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="BD5" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="BE5" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="BF5" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="BG5" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="BH5" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="BI5" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="BJ5" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="BK5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BL5" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="BM5" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="BN5" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="Z5" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="AA5" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="AB5" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="AC5" s="2" t="s">
+      <c r="BO5" s="23" t="s">
         <v>139</v>
-      </c>
-      <c r="AD5" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AE5" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AF5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="AG5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="AH5" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="AI5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="AK5" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="AL5" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="AM5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="AN5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="AO5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="AP5" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="AQ5" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="AR5" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="AS5" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="AT5" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="AU5" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="AV5" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="AW5" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="AX5" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="AY5" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="AZ5" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="BA5" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="BB5" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="BC5" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="BD5" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="BE5" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="BF5" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="BG5" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="BH5" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="BI5" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="BJ5" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="BK5" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="BL5" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="BM5" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="BN5" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="BO5" s="23" t="s">
-        <v>143</v>
       </c>
       <c r="BP5" s="23" t="s">
         <v>141</v>
       </c>
       <c r="BQ5" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="BR5" s="23" t="s">
-        <v>141</v>
+        <v>139</v>
+      </c>
+      <c r="BR5" s="6" t="s">
+        <v>137</v>
       </c>
       <c r="BS5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BT5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BU5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BV5" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="BT5" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="BU5" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="BV5" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="BW5" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BX5" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BY5" s="6" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="BZ5" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="CA5" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="CB5" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="CC5" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="CD5" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="CE5" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
+      </c>
+      <c r="CE5" s="24" t="s">
+        <v>136</v>
       </c>
       <c r="CF5" s="24" t="s">
         <v>138</v>
       </c>
       <c r="CG5" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="CH5" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="CI5" s="24" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
-    <row r="6" spans="1:87" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:86" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -2424,7 +2396,7 @@
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
@@ -2438,13 +2410,13 @@
       <c r="AA6" s="2"/>
       <c r="AB6" s="2"/>
       <c r="AC6" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="AD6" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AE6" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="AD6" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="AE6" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="AF6" s="21"/>
       <c r="AG6" s="21"/>
@@ -2458,7 +2430,7 @@
       <c r="AO6" s="21"/>
       <c r="AP6" s="21"/>
       <c r="AQ6" s="21" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AR6" s="21"/>
       <c r="AS6" s="3"/>
@@ -2472,9 +2444,7 @@
       <c r="BA6" s="6"/>
       <c r="BB6" s="6"/>
       <c r="BC6" s="6"/>
-      <c r="BD6" s="6" t="s">
-        <v>153</v>
-      </c>
+      <c r="BD6" s="6"/>
       <c r="BE6" s="6"/>
       <c r="BF6" s="6"/>
       <c r="BG6" s="6"/>
@@ -2482,367 +2452,363 @@
       <c r="BI6" s="6"/>
       <c r="BJ6" s="6"/>
       <c r="BK6" s="6"/>
-      <c r="BL6" s="6"/>
+      <c r="BL6" s="6" t="s">
+        <v>151</v>
+      </c>
       <c r="BM6" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="BN6" s="6" t="s">
-        <v>155</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="BN6" s="6"/>
       <c r="BO6" s="6"/>
       <c r="BP6" s="6"/>
       <c r="BQ6" s="6"/>
-      <c r="BR6" s="6"/>
-      <c r="BS6" s="6" t="s">
-        <v>156</v>
-      </c>
+      <c r="BR6" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="BS6" s="6"/>
       <c r="BT6" s="6"/>
       <c r="BU6" s="6"/>
       <c r="BV6" s="6"/>
       <c r="BW6" s="6"/>
       <c r="BX6" s="6"/>
-      <c r="BY6" s="6"/>
+      <c r="BY6" s="6" t="s">
+        <v>154</v>
+      </c>
       <c r="BZ6" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="CA6" s="6" t="s">
-        <v>158</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="CA6" s="6"/>
       <c r="CB6" s="6"/>
       <c r="CC6" s="6"/>
-      <c r="CD6" s="6"/>
-      <c r="CE6" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="CD6" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="CE6" s="24"/>
       <c r="CF6" s="24"/>
       <c r="CG6" s="24"/>
       <c r="CH6" s="24"/>
-      <c r="CI6" s="24"/>
     </row>
-    <row r="7" spans="1:87" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:86" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="E7" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="I7" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="J7" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="K7" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="L7" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="M7" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="N7" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="O7" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="P7" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="Q7" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="O7" s="26" t="s">
+      <c r="R7" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="P7" s="26" t="s">
+      <c r="S7" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="Q7" s="26" t="s">
+      <c r="T7" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="X7" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="Y7" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="Z7" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="AA7" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="Y7" s="26" t="s">
+      <c r="AB7" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="Z7" s="26" t="s">
+      <c r="AC7" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="AA7" s="26" t="s">
+      <c r="AD7" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="AB7" s="2" t="s">
+      <c r="AE7" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="AC7" s="2" t="s">
+      <c r="AF7" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="AD7" s="26" t="s">
+      <c r="AG7" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="AE7" s="2" t="s">
+      <c r="AH7" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="AF7" s="27" t="s">
+      <c r="AI7" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="AG7" s="27" t="s">
+      <c r="AJ7" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="AH7" s="27" t="s">
+      <c r="AK7" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="AI7" s="27" t="s">
+      <c r="AL7" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="AJ7" s="27" t="s">
+      <c r="AM7" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="AK7" s="27" t="s">
+      <c r="AN7" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="AL7" s="27" t="s">
+      <c r="AO7" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="AM7" s="27" t="s">
+      <c r="AP7" s="27" t="s">
         <v>198</v>
       </c>
-      <c r="AN7" s="27" t="s">
+      <c r="AQ7" s="27" t="s">
         <v>199</v>
       </c>
-      <c r="AO7" s="27" t="s">
+      <c r="AR7" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="AP7" s="27" t="s">
+      <c r="AS7" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="AQ7" s="27" t="s">
+      <c r="AT7" s="30" t="s">
         <v>202</v>
       </c>
-      <c r="AR7" s="27" t="s">
+      <c r="AU7" s="30" t="s">
         <v>203</v>
       </c>
-      <c r="AS7" s="30" t="s">
+      <c r="AV7" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="AT7" s="30" t="s">
+      <c r="AW7" s="30" t="s">
         <v>205</v>
       </c>
-      <c r="AU7" s="30" t="s">
+      <c r="AX7" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="AV7" s="30" t="s">
+      <c r="AY7" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="AW7" s="30" t="s">
+      <c r="AZ7" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="AX7" s="6" t="s">
+      <c r="BA7" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="AY7" s="6" t="s">
+      <c r="BB7" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="AZ7" s="30" t="s">
+      <c r="BC7" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="BA7" s="30" t="s">
+      <c r="BD7" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="BE7" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="BB7" s="30" t="s">
+      <c r="BF7" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="BC7" s="30" t="s">
+      <c r="BG7" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="BD7" s="6" t="s">
+      <c r="BH7" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="BE7" s="6" t="s">
+      <c r="BI7" s="30" t="s">
         <v>216</v>
       </c>
-      <c r="BF7" s="30" t="s">
+      <c r="BJ7" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="BG7" s="30" t="s">
+      <c r="BK7" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="BH7" s="30" t="s">
+      <c r="BL7" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="BI7" s="30" t="s">
+      <c r="BM7" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="BJ7" s="30" t="s">
+      <c r="BN7" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="BK7" s="30" t="s">
+      <c r="BO7" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="BL7" s="6" t="s">
+      <c r="BP7" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="BM7" s="6" t="s">
+      <c r="BQ7" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="BN7" s="6" t="s">
+      <c r="BR7" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="BO7" s="6" t="s">
+      <c r="BS7" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="BP7" s="6" t="s">
+      <c r="BT7" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="BQ7" s="6" t="s">
+      <c r="BU7" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="BR7" s="6" t="s">
+      <c r="BV7" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="BS7" s="6" t="s">
+      <c r="BW7" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="BT7" s="6" t="s">
+      <c r="BX7" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="BU7" s="6" t="s">
+      <c r="BY7" s="28" t="s">
         <v>232</v>
       </c>
-      <c r="BV7" s="6" t="s">
+      <c r="BZ7" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="BW7" s="6" t="s">
+      <c r="CA7" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="BX7" s="6" t="s">
+      <c r="CB7" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="BY7" s="6" t="s">
+      <c r="CC7" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="BZ7" s="28" t="s">
+      <c r="CD7" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="CA7" s="6" t="s">
+      <c r="CE7" s="30" t="s">
         <v>238</v>
       </c>
-      <c r="CB7" s="6" t="s">
+      <c r="CF7" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="CC7" s="6" t="s">
+      <c r="CG7" s="30" t="s">
         <v>240</v>
       </c>
-      <c r="CD7" s="6" t="s">
+      <c r="CH7" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="CE7" s="6" t="s">
+    </row>
+    <row r="8" spans="1:86" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="CF7" s="30" t="s">
+      <c r="B8" s="29" t="s">
         <v>243</v>
       </c>
-      <c r="CG7" s="30" t="s">
+      <c r="C8" s="30" t="s">
         <v>244</v>
       </c>
-      <c r="CH7" s="30" t="s">
+      <c r="D8" t="s">
+        <v>266</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="F8" s="30" t="s">
         <v>245</v>
       </c>
-      <c r="CI7" s="30" t="s">
+      <c r="G8" t="s">
+        <v>269</v>
+      </c>
+      <c r="H8" t="s">
+        <v>269</v>
+      </c>
+      <c r="I8" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="J8" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="K8" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="L8" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="M8" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="N8" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="O8" s="30" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="8" spans="1:87" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+      <c r="P8" s="30" t="s">
         <v>247</v>
       </c>
-      <c r="B8" s="29" t="s">
-        <v>248</v>
-      </c>
-      <c r="C8" s="30" t="s">
+      <c r="Q8" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="R8" s="30" t="s">
         <v>249</v>
-      </c>
-      <c r="D8" t="s">
-        <v>271</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>270</v>
-      </c>
-      <c r="F8" s="30" t="s">
-        <v>250</v>
-      </c>
-      <c r="G8" t="s">
-        <v>274</v>
-      </c>
-      <c r="H8" t="s">
-        <v>274</v>
-      </c>
-      <c r="I8" s="30" t="s">
-        <v>273</v>
-      </c>
-      <c r="J8" s="30" t="s">
-        <v>273</v>
-      </c>
-      <c r="K8" s="30" t="s">
-        <v>273</v>
-      </c>
-      <c r="L8" s="30" t="s">
-        <v>273</v>
-      </c>
-      <c r="M8" s="30" t="s">
-        <v>273</v>
-      </c>
-      <c r="N8" s="30" t="s">
-        <v>273</v>
-      </c>
-      <c r="O8" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="P8" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q8" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="R8" s="30" t="s">
-        <v>254</v>
       </c>
       <c r="S8" s="31"/>
       <c r="T8" s="31"/>
       <c r="U8" s="32"/>
       <c r="V8" s="32"/>
       <c r="W8" s="30" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="X8" s="32"/>
       <c r="Y8" s="31">
@@ -2850,22 +2816,22 @@
       </c>
       <c r="Z8" s="31"/>
       <c r="AA8" s="31" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="AB8" s="31"/>
       <c r="AC8" s="30" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="AD8" s="30" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="AE8" s="30" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="AF8" s="30"/>
       <c r="AG8" s="30"/>
       <c r="AH8" s="30" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="AI8" s="30"/>
       <c r="AJ8" s="30"/>
@@ -2875,109 +2841,106 @@
       <c r="AN8" s="30"/>
       <c r="AO8" s="30"/>
       <c r="AP8" s="30" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="AQ8" s="30" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="AR8" s="30" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AS8" s="30"/>
       <c r="AT8" s="30"/>
       <c r="AU8" s="30"/>
       <c r="AV8" s="30"/>
       <c r="AW8" s="30" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="AX8" s="31"/>
       <c r="AY8" s="31"/>
       <c r="AZ8" s="30" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="BA8" s="30" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="BB8" s="30" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="BC8" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="BD8" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="BE8" s="33"/>
-      <c r="BF8" s="31">
+        <v>251</v>
+      </c>
+      <c r="BD8" s="33"/>
+      <c r="BE8" s="31">
         <v>3</v>
       </c>
-      <c r="BG8" s="30" t="s">
-        <v>269</v>
+      <c r="BF8" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="BG8" s="31">
+        <v>70</v>
       </c>
       <c r="BH8" s="31">
-        <v>70</v>
+        <v>1.4E-2</v>
       </c>
       <c r="BI8" s="31">
-        <v>1.4E-2</v>
-      </c>
-      <c r="BJ8" s="31">
         <v>200</v>
       </c>
-      <c r="BK8" s="30"/>
-      <c r="BL8" s="33"/>
+      <c r="BJ8" s="30"/>
+      <c r="BK8" s="33"/>
+      <c r="BL8" s="30" t="s">
+        <v>264</v>
+      </c>
       <c r="BM8" s="30" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="BN8" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="BO8" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="BP8" s="33"/>
-      <c r="BQ8" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="BR8" s="33"/>
-      <c r="BS8" s="30" t="s">
-        <v>269</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="BO8" s="33"/>
+      <c r="BP8" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="BQ8" s="33"/>
+      <c r="BR8" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="BS8" s="33"/>
       <c r="BT8" s="33"/>
       <c r="BU8" s="33"/>
       <c r="BV8" s="33"/>
       <c r="BW8" s="33"/>
       <c r="BX8" s="33"/>
-      <c r="BY8" s="33"/>
+      <c r="BY8" s="30" t="s">
+        <v>264</v>
+      </c>
       <c r="BZ8" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="CA8" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="CB8" s="30"/>
+        <v>264</v>
+      </c>
+      <c r="CA8" s="30"/>
+      <c r="CB8" s="33"/>
       <c r="CC8" s="33"/>
-      <c r="CD8" s="33"/>
+      <c r="CD8" s="30" t="s">
+        <v>264</v>
+      </c>
       <c r="CE8" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="CF8" s="30" t="s">
-        <v>257</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="CF8" s="30"/>
       <c r="CG8" s="30"/>
       <c r="CH8" s="30"/>
-      <c r="CI8" s="30"/>
     </row>
-    <row r="9" spans="1:87" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:86" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="C9" s="30" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D9" s="34"/>
       <c r="E9" s="30" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="I9" s="30"/>
       <c r="J9" s="30"/>
@@ -2986,16 +2949,16 @@
       <c r="M9" s="30"/>
       <c r="N9" s="30"/>
       <c r="O9" s="30" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="R9" s="30" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="S9" s="31"/>
       <c r="T9" s="31"/>
@@ -3015,7 +2978,7 @@
       <c r="AB9" s="31"/>
       <c r="AC9" s="31"/>
       <c r="AD9" s="30" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="AE9" s="31"/>
       <c r="AF9" s="30"/>
@@ -3031,14 +2994,14 @@
       <c r="AP9" s="30"/>
       <c r="AQ9" s="30"/>
       <c r="AR9" s="30" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AS9" s="30"/>
       <c r="AT9" s="30"/>
       <c r="AU9" s="30"/>
       <c r="AV9" s="30"/>
       <c r="AW9" s="30" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="AX9" s="31"/>
       <c r="AY9" s="31"/>
@@ -3046,32 +3009,32 @@
         <v>0.200098</v>
       </c>
       <c r="BA9" s="30" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="BB9" s="30" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="BC9" s="30" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="BD9" s="34"/>
-      <c r="BE9" s="34"/>
+      <c r="BE9" s="31">
+        <v>3</v>
+      </c>
       <c r="BF9" s="31">
-        <v>3</v>
+        <v>1680</v>
       </c>
       <c r="BG9" s="31">
-        <v>1680</v>
+        <v>70</v>
       </c>
       <c r="BH9" s="31">
-        <v>70</v>
+        <v>1.54E-2</v>
       </c>
       <c r="BI9" s="31">
-        <v>1.54E-2</v>
-      </c>
-      <c r="BJ9" s="31">
         <v>220</v>
       </c>
-      <c r="BK9" s="30"/>
+      <c r="BJ9" s="30"/>
+      <c r="BK9" s="34"/>
       <c r="BL9" s="34"/>
       <c r="BM9" s="34"/>
       <c r="BN9" s="34"/>
@@ -3085,52 +3048,51 @@
       <c r="BV9" s="34"/>
       <c r="BW9" s="34"/>
       <c r="BX9" s="34"/>
-      <c r="BY9" s="34"/>
+      <c r="BY9" s="30"/>
       <c r="BZ9" s="30"/>
       <c r="CA9" s="30"/>
-      <c r="CB9" s="30"/>
+      <c r="CB9" s="34"/>
       <c r="CC9" s="34"/>
       <c r="CD9" s="34"/>
-      <c r="CE9" s="34"/>
-      <c r="CF9" s="30" t="s">
-        <v>257</v>
-      </c>
+      <c r="CE9" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="CF9" s="30"/>
       <c r="CG9" s="30"/>
       <c r="CH9" s="30"/>
-      <c r="CI9" s="30"/>
     </row>
-    <row r="10" spans="1:87" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:86" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
       <c r="C10" s="30" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D10" s="34"/>
       <c r="E10" s="30"/>
       <c r="F10" s="30" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="H10" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I10" s="30"/>
       <c r="J10" s="30" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="K10" s="30"/>
       <c r="L10" s="30"/>
       <c r="M10" s="30"/>
       <c r="N10" s="30"/>
       <c r="O10" s="30" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="P10" s="30" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="Q10" s="30" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="R10" s="30" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="S10" s="31"/>
       <c r="T10" s="31"/>
@@ -3150,7 +3112,7 @@
       <c r="AB10" s="31"/>
       <c r="AC10" s="31"/>
       <c r="AD10" s="30" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="AE10" s="31"/>
       <c r="AF10" s="30"/>
@@ -3166,14 +3128,14 @@
       <c r="AP10" s="30"/>
       <c r="AQ10" s="30"/>
       <c r="AR10" s="30" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AS10" s="30"/>
       <c r="AT10" s="30"/>
       <c r="AU10" s="30"/>
       <c r="AV10" s="30"/>
       <c r="AW10" s="30" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="AX10" s="31"/>
       <c r="AY10" s="31"/>
@@ -3181,32 +3143,32 @@
         <v>0.200098</v>
       </c>
       <c r="BA10" s="30" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="BB10" s="30" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="BC10" s="30" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="BD10" s="34"/>
-      <c r="BE10" s="34"/>
+      <c r="BE10" s="31">
+        <v>3</v>
+      </c>
       <c r="BF10" s="31">
-        <v>3</v>
+        <v>1680</v>
       </c>
       <c r="BG10" s="31">
-        <v>1680</v>
+        <v>70</v>
       </c>
       <c r="BH10" s="31">
-        <v>70</v>
+        <v>1.54E-2</v>
       </c>
       <c r="BI10" s="31">
-        <v>1.54E-2</v>
-      </c>
-      <c r="BJ10" s="31">
         <v>220</v>
       </c>
-      <c r="BK10" s="30"/>
+      <c r="BJ10" s="30"/>
+      <c r="BK10" s="34"/>
       <c r="BL10" s="34"/>
       <c r="BM10" s="34"/>
       <c r="BN10" s="34"/>
@@ -3220,33 +3182,32 @@
       <c r="BV10" s="34"/>
       <c r="BW10" s="34"/>
       <c r="BX10" s="34"/>
-      <c r="BY10" s="34"/>
+      <c r="BY10" s="30"/>
       <c r="BZ10" s="30"/>
       <c r="CA10" s="30"/>
-      <c r="CB10" s="30"/>
+      <c r="CB10" s="34"/>
       <c r="CC10" s="34"/>
       <c r="CD10" s="34"/>
-      <c r="CE10" s="34"/>
-      <c r="CF10" s="30" t="s">
-        <v>257</v>
-      </c>
+      <c r="CE10" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="CF10" s="30"/>
       <c r="CG10" s="30"/>
       <c r="CH10" s="30"/>
-      <c r="CI10" s="30"/>
     </row>
-    <row r="11" spans="1:87" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:86" ht="16" x14ac:dyDescent="0.2">
       <c r="C11" s="30" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D11" s="34"/>
       <c r="E11" s="30" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="G11" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="H11" s="34"/>
       <c r="I11" s="30"/>
@@ -3256,16 +3217,16 @@
       <c r="M11" s="30"/>
       <c r="N11" s="30"/>
       <c r="O11" s="30" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P11" s="30" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="Q11" s="30" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="R11" s="30" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="S11" s="31"/>
       <c r="T11" s="31"/>
@@ -3285,7 +3246,7 @@
       <c r="AB11" s="31"/>
       <c r="AC11" s="31"/>
       <c r="AD11" s="30" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="AE11" s="31"/>
       <c r="AF11" s="30"/>
@@ -3301,14 +3262,14 @@
       <c r="AP11" s="30"/>
       <c r="AQ11" s="30"/>
       <c r="AR11" s="30" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AS11" s="30"/>
       <c r="AT11" s="30"/>
       <c r="AU11" s="30"/>
       <c r="AV11" s="30"/>
       <c r="AW11" s="30" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="AX11" s="31"/>
       <c r="AY11" s="31"/>
@@ -3316,32 +3277,32 @@
         <v>0.200098</v>
       </c>
       <c r="BA11" s="30" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="BB11" s="30" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="BC11" s="30" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="BD11" s="34"/>
-      <c r="BE11" s="34"/>
+      <c r="BE11" s="31">
+        <v>3</v>
+      </c>
       <c r="BF11" s="31">
-        <v>3</v>
+        <v>600</v>
       </c>
       <c r="BG11" s="31">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="BH11" s="31">
-        <v>70</v>
+        <v>1.54E-2</v>
       </c>
       <c r="BI11" s="31">
-        <v>1.54E-2</v>
-      </c>
-      <c r="BJ11" s="31">
         <v>220</v>
       </c>
-      <c r="BK11" s="30"/>
+      <c r="BJ11" s="30"/>
+      <c r="BK11" s="34"/>
       <c r="BL11" s="34"/>
       <c r="BM11" s="34"/>
       <c r="BN11" s="34"/>
@@ -3355,33 +3316,32 @@
       <c r="BV11" s="34"/>
       <c r="BW11" s="34"/>
       <c r="BX11" s="34"/>
-      <c r="BY11" s="34"/>
+      <c r="BY11" s="30"/>
       <c r="BZ11" s="30"/>
       <c r="CA11" s="30"/>
-      <c r="CB11" s="30"/>
+      <c r="CB11" s="34"/>
       <c r="CC11" s="34"/>
       <c r="CD11" s="34"/>
-      <c r="CE11" s="34"/>
-      <c r="CF11" s="30" t="s">
-        <v>257</v>
-      </c>
+      <c r="CE11" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="CF11" s="30"/>
       <c r="CG11" s="30"/>
       <c r="CH11" s="30"/>
-      <c r="CI11" s="30"/>
     </row>
-    <row r="12" spans="1:87" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:86" ht="16" x14ac:dyDescent="0.2">
       <c r="C12" s="30" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D12" s="34"/>
       <c r="E12" s="30" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="F12" s="30" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="G12" s="30" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="H12" s="34"/>
       <c r="I12" s="30"/>
@@ -3391,16 +3351,16 @@
       <c r="M12" s="30"/>
       <c r="N12" s="30"/>
       <c r="O12" s="30" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="P12" s="30" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="Q12" s="30" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="R12" s="30" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="S12" s="31"/>
       <c r="T12" s="31"/>
@@ -3420,7 +3380,7 @@
       <c r="AB12" s="31"/>
       <c r="AC12" s="31"/>
       <c r="AD12" s="30" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="AE12" s="31"/>
       <c r="AF12" s="30"/>
@@ -3436,14 +3396,14 @@
       <c r="AP12" s="30"/>
       <c r="AQ12" s="30"/>
       <c r="AR12" s="30" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AS12" s="30"/>
       <c r="AT12" s="30"/>
       <c r="AU12" s="30"/>
       <c r="AV12" s="30"/>
       <c r="AW12" s="30" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="AX12" s="31"/>
       <c r="AY12" s="31"/>
@@ -3451,32 +3411,32 @@
         <v>0.200098</v>
       </c>
       <c r="BA12" s="30" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="BB12" s="30" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="BC12" s="30" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="BD12" s="34"/>
-      <c r="BE12" s="34"/>
+      <c r="BE12" s="31">
+        <v>3</v>
+      </c>
       <c r="BF12" s="31">
-        <v>3</v>
+        <v>1440</v>
       </c>
       <c r="BG12" s="31">
-        <v>1440</v>
+        <v>70</v>
       </c>
       <c r="BH12" s="31">
-        <v>70</v>
+        <v>1.4E-2</v>
       </c>
       <c r="BI12" s="31">
-        <v>1.4E-2</v>
-      </c>
-      <c r="BJ12" s="31">
         <v>200</v>
       </c>
-      <c r="BK12" s="30"/>
+      <c r="BJ12" s="30"/>
+      <c r="BK12" s="34"/>
       <c r="BL12" s="34"/>
       <c r="BM12" s="34"/>
       <c r="BN12" s="34"/>
@@ -3490,27 +3450,26 @@
       <c r="BV12" s="34"/>
       <c r="BW12" s="34"/>
       <c r="BX12" s="34"/>
-      <c r="BY12" s="34"/>
+      <c r="BY12" s="30"/>
       <c r="BZ12" s="30"/>
       <c r="CA12" s="30"/>
-      <c r="CB12" s="30"/>
+      <c r="CB12" s="34"/>
       <c r="CC12" s="34"/>
       <c r="CD12" s="34"/>
-      <c r="CE12" s="34"/>
-      <c r="CF12" s="30" t="s">
-        <v>257</v>
-      </c>
+      <c r="CE12" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="CF12" s="30"/>
       <c r="CG12" s="30"/>
       <c r="CH12" s="30"/>
-      <c r="CI12" s="30"/>
     </row>
-    <row r="13" spans="1:87" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:86" ht="16" x14ac:dyDescent="0.2">
       <c r="C13" s="30" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D13" s="34"/>
       <c r="E13" s="30" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="F13" s="30"/>
       <c r="G13" s="34"/>
@@ -3522,16 +3481,16 @@
       <c r="M13" s="30"/>
       <c r="N13" s="30"/>
       <c r="O13" s="30" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="P13" s="30" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="Q13" s="30" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="R13" s="30" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="S13" s="31"/>
       <c r="T13" s="31"/>
@@ -3551,7 +3510,7 @@
       <c r="AB13" s="31"/>
       <c r="AC13" s="31"/>
       <c r="AD13" s="30" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="AE13" s="31"/>
       <c r="AF13" s="30"/>
@@ -3567,14 +3526,14 @@
       <c r="AP13" s="30"/>
       <c r="AQ13" s="30"/>
       <c r="AR13" s="30" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AS13" s="30"/>
       <c r="AT13" s="30"/>
       <c r="AU13" s="30"/>
       <c r="AV13" s="30"/>
       <c r="AW13" s="30" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="AX13" s="31"/>
       <c r="AY13" s="31"/>
@@ -3582,32 +3541,32 @@
         <v>0.200098</v>
       </c>
       <c r="BA13" s="30" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="BB13" s="30" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="BC13" s="30" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="BD13" s="34"/>
-      <c r="BE13" s="34"/>
+      <c r="BE13" s="31">
+        <v>3</v>
+      </c>
       <c r="BF13" s="31">
-        <v>3</v>
+        <v>1680</v>
       </c>
       <c r="BG13" s="31">
-        <v>1680</v>
+        <v>70</v>
       </c>
       <c r="BH13" s="31">
-        <v>70</v>
+        <v>1.54E-2</v>
       </c>
       <c r="BI13" s="31">
-        <v>1.54E-2</v>
-      </c>
-      <c r="BJ13" s="31">
         <v>220</v>
       </c>
-      <c r="BK13" s="30"/>
+      <c r="BJ13" s="30"/>
+      <c r="BK13" s="34"/>
       <c r="BL13" s="34"/>
       <c r="BM13" s="34"/>
       <c r="BN13" s="34"/>
@@ -3621,19 +3580,18 @@
       <c r="BV13" s="34"/>
       <c r="BW13" s="34"/>
       <c r="BX13" s="34"/>
-      <c r="BY13" s="34"/>
+      <c r="BY13" s="30"/>
       <c r="BZ13" s="30"/>
       <c r="CA13" s="30"/>
-      <c r="CB13" s="30"/>
+      <c r="CB13" s="34"/>
       <c r="CC13" s="34"/>
       <c r="CD13" s="34"/>
-      <c r="CE13" s="34"/>
-      <c r="CF13" s="30" t="s">
-        <v>257</v>
-      </c>
+      <c r="CE13" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="CF13" s="30"/>
       <c r="CG13" s="30"/>
       <c r="CH13" s="30"/>
-      <c r="CI13" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/spec/fixtures/batch_submission_manifest_errors_test.xlsx
+++ b/spec/fixtures/batch_submission_manifest_errors_test.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smc101/vagrant/morphosource-vagrant/MorphoSource_SF/spec/fixtures/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smc101/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{513E6CE7-33BA-AB48-81AF-B560B7A5C81D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55141641-F608-FE49-874F-2F4A3DA82165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="32000" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="278">
   <si>
     <t>Field Section</t>
   </si>
@@ -906,12 +906,28 @@
   <si>
     <t>imaging_event.ct.ie_filter</t>
   </si>
+  <si>
+    <t>Whether this file was created with minimal or no processing (raw) or whether software processing was used to create the file (derived). Raw files only have Imaging Event metadata to describe how the media was initially imaged, derived files have imaging event and processing event metadata to describe both how the media was initially imaged and how it was subsequently processed.</t>
+  </si>
+  <si>
+    <t>Raw: Raw
+Derived: Derived</t>
+  </si>
+  <si>
+    <t>media.raw_or_derived</t>
+  </si>
+  <si>
+    <t>Derived</t>
+  </si>
+  <si>
+    <t>Raw</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -951,6 +967,10 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -1040,7 +1060,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1098,6 +1118,11 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1313,10 +1338,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06ED7EC9-286B-1D49-A57D-A989376D77CC}">
-  <dimension ref="A1:CH13"/>
+  <dimension ref="A1:CI14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:86" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:87" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1335,16 +1360,16 @@
       <c r="F1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="35" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12" t="s">
-        <v>3</v>
-      </c>
+      <c r="I1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="12"/>
       <c r="K1" s="12" t="s">
         <v>3</v>
       </c>
@@ -1357,8 +1382,8 @@
       <c r="N1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>4</v>
+      <c r="O1" s="12" t="s">
+        <v>3</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>4</v>
@@ -1388,7 +1413,7 @@
         <v>4</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z1" s="2" t="s">
         <v>5</v>
@@ -1403,13 +1428,13 @@
         <v>5</v>
       </c>
       <c r="AD1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="AF1" s="21" t="s">
-        <v>8</v>
       </c>
       <c r="AG1" s="21" t="s">
         <v>8</v>
@@ -1447,8 +1472,8 @@
       <c r="AR1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="AS1" s="3" t="s">
-        <v>9</v>
+      <c r="AS1" s="21" t="s">
+        <v>8</v>
       </c>
       <c r="AT1" s="3" t="s">
         <v>9</v>
@@ -1456,8 +1481,8 @@
       <c r="AU1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AV1" s="6" t="s">
-        <v>10</v>
+      <c r="AV1" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="AW1" s="6" t="s">
         <v>10</v>
@@ -1469,7 +1494,7 @@
         <v>10</v>
       </c>
       <c r="AZ1" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA1" s="6" t="s">
         <v>11</v>
@@ -1547,13 +1572,13 @@
         <v>11</v>
       </c>
       <c r="BZ1" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CA1" s="6" t="s">
         <v>12</v>
       </c>
       <c r="CB1" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CC1" s="6" t="s">
         <v>13</v>
@@ -1561,8 +1586,8 @@
       <c r="CD1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="CE1" s="24" t="s">
-        <v>14</v>
+      <c r="CE1" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="CF1" s="24" t="s">
         <v>14</v>
@@ -1573,8 +1598,11 @@
       <c r="CH1" s="24" t="s">
         <v>14</v>
       </c>
+      <c r="CI1" s="24" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:86" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:87" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
@@ -1585,234 +1613,235 @@
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="G2" s="36"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="5"/>
+      <c r="J2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="12"/>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="12"/>
+      <c r="P2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AF2" s="21" t="s">
+      <c r="AG2" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="AG2" s="21" t="s">
+      <c r="AH2" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="AH2" s="21" t="s">
+      <c r="AI2" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="AI2" s="21" t="s">
+      <c r="AJ2" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="AJ2" s="21" t="s">
+      <c r="AK2" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="AK2" s="21" t="s">
+      <c r="AL2" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="AL2" s="21" t="s">
+      <c r="AM2" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="AM2" s="21" t="s">
+      <c r="AN2" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="AN2" s="21" t="s">
+      <c r="AO2" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="AO2" s="21" t="s">
+      <c r="AP2" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="AP2" s="21" t="s">
+      <c r="AQ2" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="AQ2" s="21" t="s">
+      <c r="AR2" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="AR2" s="21" t="s">
+      <c r="AS2" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="AS2" s="3" t="s">
+      <c r="AT2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AT2" s="3" t="s">
+      <c r="AU2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AU2" s="3" t="s">
+      <c r="AV2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AV2" s="6" t="s">
+      <c r="AW2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="AW2" s="6" t="s">
+      <c r="AX2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="AX2" s="6" t="s">
+      <c r="AY2" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="AY2" s="6" t="s">
+      <c r="AZ2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AZ2" s="6" t="s">
+      <c r="BA2" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="BA2" s="6" t="s">
+      <c r="BB2" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="BB2" s="6" t="s">
+      <c r="BC2" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="BC2" s="6" t="s">
+      <c r="BD2" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="BD2" s="6" t="s">
+      <c r="BE2" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="BE2" s="6" t="s">
+      <c r="BF2" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="BF2" s="6" t="s">
+      <c r="BG2" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="BG2" s="6" t="s">
+      <c r="BH2" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="BH2" s="6" t="s">
+      <c r="BI2" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="BI2" s="6" t="s">
+      <c r="BJ2" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="BJ2" s="6" t="s">
+      <c r="BK2" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="BK2" s="6" t="s">
+      <c r="BL2" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="BL2" s="6" t="s">
+      <c r="BM2" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="BM2" s="6" t="s">
+      <c r="BN2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="BN2" s="6" t="s">
+      <c r="BO2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="BO2" s="6" t="s">
+      <c r="BP2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="BP2" s="6" t="s">
+      <c r="BQ2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="BQ2" s="6" t="s">
+      <c r="BR2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="BR2" s="6" t="s">
+      <c r="BS2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="BS2" s="6" t="s">
+      <c r="BT2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="BT2" s="6" t="s">
+      <c r="BU2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="BU2" s="6" t="s">
+      <c r="BV2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="BV2" s="6" t="s">
+      <c r="BW2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="BW2" s="6" t="s">
+      <c r="BX2" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="BX2" s="6" t="s">
+      <c r="BY2" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="BY2" s="6" t="s">
+      <c r="BZ2" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="BZ2" s="6" t="s">
+      <c r="CA2" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="CA2" s="6" t="s">
+      <c r="CB2" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="CB2" s="6" t="s">
+      <c r="CC2" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="CC2" s="6" t="s">
+      <c r="CD2" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="CD2" s="6" t="s">
+      <c r="CE2" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="CE2" s="24" t="s">
+      <c r="CF2" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="CF2" s="24" t="s">
+      <c r="CG2" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="CG2" s="24" t="s">
+      <c r="CH2" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="CH2" s="24" t="s">
+      <c r="CI2" s="24" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:86" ht="139.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:87" ht="139.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
         <v>82</v>
       </c>
@@ -1827,62 +1856,64 @@
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="10"/>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="37" t="s">
+        <v>273</v>
+      </c>
+      <c r="H3" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="H3" s="10"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11" t="s">
+      <c r="I3" s="10"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="K3" s="12"/>
       <c r="L3" s="12"/>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="12"/>
+      <c r="N3" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="O3" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="P3" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="P3" s="14"/>
       <c r="Q3" s="14"/>
-      <c r="R3" s="13" t="s">
+      <c r="R3" s="14"/>
+      <c r="S3" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="S3" s="13" t="s">
+      <c r="T3" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="T3" s="2"/>
-      <c r="U3" s="13" t="s">
+      <c r="U3" s="2"/>
+      <c r="V3" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="V3" s="13"/>
-      <c r="W3" s="2"/>
+      <c r="W3" s="13"/>
       <c r="X3" s="2"/>
-      <c r="Y3" s="15" t="s">
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="Z3" s="15" t="s">
+      <c r="AA3" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="AA3" s="15" t="s">
+      <c r="AB3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="AB3" s="13" t="s">
+      <c r="AC3" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="AC3" s="13" t="s">
+      <c r="AD3" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="2"/>
-      <c r="AF3" s="21"/>
+      <c r="AE3" s="14"/>
+      <c r="AF3" s="2"/>
       <c r="AG3" s="21"/>
       <c r="AH3" s="21"/>
       <c r="AI3" s="21"/>
-      <c r="AJ3" s="16"/>
+      <c r="AJ3" s="21"/>
       <c r="AK3" s="16"/>
       <c r="AL3" s="16"/>
       <c r="AM3" s="16"/>
@@ -1890,113 +1921,114 @@
       <c r="AO3" s="16"/>
       <c r="AP3" s="16"/>
       <c r="AQ3" s="16"/>
-      <c r="AR3" s="21" t="s">
+      <c r="AR3" s="16"/>
+      <c r="AS3" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="AS3" s="17"/>
       <c r="AT3" s="17"/>
       <c r="AU3" s="17"/>
-      <c r="AV3" s="6"/>
+      <c r="AV3" s="17"/>
       <c r="AW3" s="6"/>
-      <c r="AX3" s="18" t="s">
+      <c r="AX3" s="6"/>
+      <c r="AY3" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="AY3" s="18"/>
-      <c r="AZ3" s="19" t="s">
+      <c r="AZ3" s="18"/>
+      <c r="BA3" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="BA3" s="19" t="s">
+      <c r="BB3" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="BB3" s="19" t="s">
+      <c r="BC3" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="BC3" s="19" t="s">
+      <c r="BD3" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="BD3" s="19" t="s">
+      <c r="BE3" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="BE3" s="19" t="s">
+      <c r="BF3" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="BF3" s="19" t="s">
+      <c r="BG3" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="BG3" s="19" t="s">
+      <c r="BH3" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="BH3" s="19" t="s">
+      <c r="BI3" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="BI3" s="19" t="s">
+      <c r="BJ3" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="BJ3" s="19" t="s">
+      <c r="BK3" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="BK3" s="18" t="s">
+      <c r="BL3" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="BL3" s="18"/>
-      <c r="BM3" s="18" t="s">
+      <c r="BM3" s="18"/>
+      <c r="BN3" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="BN3" s="20" t="s">
+      <c r="BO3" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="BO3" s="20" t="s">
+      <c r="BP3" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="BP3" s="20" t="s">
+      <c r="BQ3" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="BQ3" s="20" t="s">
+      <c r="BR3" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="BR3" s="18" t="s">
+      <c r="BS3" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="BS3" s="18" t="s">
+      <c r="BT3" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="BT3" s="18" t="s">
+      <c r="BU3" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="BU3" s="18" t="s">
+      <c r="BV3" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="BV3" s="18" t="s">
+      <c r="BW3" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="BW3" s="18" t="s">
+      <c r="BX3" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="BX3" s="18" t="s">
+      <c r="BY3" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="BY3" s="19"/>
-      <c r="BZ3" s="18" t="s">
+      <c r="BZ3" s="19"/>
+      <c r="CA3" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="CA3" s="18" t="s">
+      <c r="CB3" s="18" t="s">
         <v>126</v>
-      </c>
-      <c r="CB3" s="18" t="s">
-        <v>127</v>
       </c>
       <c r="CC3" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="CD3" s="19" t="s">
+      <c r="CD3" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CE3" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="CE3" s="24"/>
       <c r="CF3" s="24"/>
       <c r="CG3" s="24"/>
       <c r="CH3" s="24"/>
+      <c r="CI3" s="24"/>
     </row>
-    <row r="4" spans="1:86" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:87" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>129</v>
       </c>
@@ -2013,13 +2045,13 @@
       <c r="F4" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4" s="35" t="s">
+        <v>131</v>
+      </c>
       <c r="H4" s="5"/>
-      <c r="I4" s="12"/>
+      <c r="I4" s="5"/>
       <c r="J4" s="12"/>
-      <c r="K4" s="12" t="s">
-        <v>132</v>
-      </c>
+      <c r="K4" s="12"/>
       <c r="L4" s="12" t="s">
         <v>132</v>
       </c>
@@ -2029,32 +2061,34 @@
       <c r="N4" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="O4" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="P4" s="14"/>
+      <c r="P4" s="2" t="s">
+        <v>132</v>
+      </c>
       <c r="Q4" s="14"/>
-      <c r="R4" s="2"/>
+      <c r="R4" s="14"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
-      <c r="Y4" s="2" t="s">
-        <v>133</v>
-      </c>
+      <c r="Y4" s="2"/>
       <c r="Z4" s="2" t="s">
         <v>133</v>
       </c>
       <c r="AA4" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="AB4" s="2"/>
+      <c r="AB4" s="2" t="s">
+        <v>133</v>
+      </c>
       <c r="AC4" s="2"/>
-      <c r="AD4" s="14"/>
-      <c r="AE4" s="2"/>
-      <c r="AF4" s="16"/>
+      <c r="AD4" s="2"/>
+      <c r="AE4" s="14"/>
+      <c r="AF4" s="2"/>
       <c r="AG4" s="16"/>
       <c r="AH4" s="16"/>
       <c r="AI4" s="16"/>
@@ -2067,10 +2101,10 @@
       <c r="AP4" s="16"/>
       <c r="AQ4" s="16"/>
       <c r="AR4" s="16"/>
-      <c r="AS4" s="17"/>
+      <c r="AS4" s="16"/>
       <c r="AT4" s="17"/>
       <c r="AU4" s="17"/>
-      <c r="AV4" s="6"/>
+      <c r="AV4" s="17"/>
       <c r="AW4" s="6"/>
       <c r="AX4" s="6"/>
       <c r="AY4" s="6"/>
@@ -2105,12 +2139,13 @@
       <c r="CB4" s="6"/>
       <c r="CC4" s="6"/>
       <c r="CD4" s="6"/>
-      <c r="CE4" s="24"/>
+      <c r="CE4" s="6"/>
       <c r="CF4" s="24"/>
       <c r="CG4" s="24"/>
       <c r="CH4" s="24"/>
+      <c r="CI4" s="24"/>
     </row>
-    <row r="5" spans="1:86" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:87" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
         <v>134</v>
       </c>
@@ -2129,13 +2164,13 @@
       <c r="F5" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>136</v>
+      <c r="G5" s="35" t="s">
+        <v>137</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="5" t="s">
         <v>136</v>
       </c>
       <c r="J5" s="12" t="s">
@@ -2153,18 +2188,18 @@
       <c r="N5" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="O5" s="12" t="s">
         <v>136</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>136</v>
       </c>
       <c r="Q5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="R5" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="R5" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="S5" s="2" t="s">
         <v>136</v>
       </c>
@@ -2178,13 +2213,13 @@
         <v>136</v>
       </c>
       <c r="W5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="X5" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="X5" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="Y5" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="Z5" s="2" t="s">
         <v>139</v>
@@ -2196,7 +2231,7 @@
         <v>139</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AD5" s="2" t="s">
         <v>137</v>
@@ -2204,29 +2239,29 @@
       <c r="AE5" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="AF5" s="21" t="s">
-        <v>136</v>
+      <c r="AF5" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="AG5" s="21" t="s">
         <v>136</v>
       </c>
       <c r="AH5" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AI5" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="AI5" s="21" t="s">
-        <v>136</v>
-      </c>
       <c r="AJ5" s="21" t="s">
         <v>136</v>
       </c>
       <c r="AK5" s="21" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="AL5" s="21" t="s">
         <v>139</v>
       </c>
       <c r="AM5" s="21" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AN5" s="21" t="s">
         <v>136</v>
@@ -2235,24 +2270,24 @@
         <v>136</v>
       </c>
       <c r="AP5" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AQ5" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="AQ5" s="21" t="s">
+      <c r="AR5" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="AR5" s="21" t="s">
+      <c r="AS5" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="AS5" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="AT5" s="3" t="s">
         <v>136</v>
       </c>
       <c r="AU5" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="AV5" s="6" t="s">
+      <c r="AV5" s="3" t="s">
         <v>136</v>
       </c>
       <c r="AW5" s="6" t="s">
@@ -2264,11 +2299,11 @@
       <c r="AY5" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="AZ5" s="22" t="s">
+      <c r="AZ5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BA5" s="22" t="s">
         <v>139</v>
-      </c>
-      <c r="BA5" s="22" t="s">
-        <v>140</v>
       </c>
       <c r="BB5" s="22" t="s">
         <v>140</v>
@@ -2277,10 +2312,10 @@
         <v>140</v>
       </c>
       <c r="BD5" s="22" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BE5" s="22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="BF5" s="22" t="s">
         <v>139</v>
@@ -2295,35 +2330,35 @@
         <v>139</v>
       </c>
       <c r="BJ5" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="BK5" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="BK5" s="22" t="s">
         <v>136</v>
       </c>
       <c r="BL5" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="BM5" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="BN5" s="23" t="s">
+      <c r="BN5" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="BO5" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="BO5" s="23" t="s">
+      <c r="BP5" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="BP5" s="23" t="s">
+      <c r="BQ5" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="BQ5" s="23" t="s">
+      <c r="BR5" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="BR5" s="6" t="s">
+      <c r="BS5" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="BS5" s="6" t="s">
-        <v>136</v>
-      </c>
       <c r="BT5" s="6" t="s">
         <v>136</v>
       </c>
@@ -2331,22 +2366,22 @@
         <v>136</v>
       </c>
       <c r="BV5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BW5" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="BW5" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="BX5" s="6" t="s">
         <v>140</v>
       </c>
       <c r="BY5" s="6" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="BZ5" s="6" t="s">
         <v>137</v>
       </c>
       <c r="CA5" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="CB5" s="6" t="s">
         <v>136</v>
@@ -2355,22 +2390,25 @@
         <v>136</v>
       </c>
       <c r="CD5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="CE5" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="CE5" s="24" t="s">
-        <v>136</v>
-      </c>
       <c r="CF5" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="CG5" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="CG5" s="24" t="s">
-        <v>136</v>
-      </c>
       <c r="CH5" s="24" t="s">
         <v>136</v>
       </c>
+      <c r="CI5" s="24" t="s">
+        <v>136</v>
+      </c>
     </row>
-    <row r="6" spans="1:86" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:87" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
         <v>142</v>
       </c>
@@ -2385,20 +2423,22 @@
       <c r="F6" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6" s="35" t="s">
+        <v>274</v>
+      </c>
       <c r="H6" s="5"/>
-      <c r="I6" s="12"/>
+      <c r="I6" s="5"/>
       <c r="J6" s="12"/>
       <c r="K6" s="12"/>
       <c r="L6" s="12"/>
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
-      <c r="O6" s="2"/>
+      <c r="O6" s="12"/>
       <c r="P6" s="2"/>
-      <c r="Q6" s="2" t="s">
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
@@ -2409,16 +2449,16 @@
       <c r="Z6" s="2"/>
       <c r="AA6" s="2"/>
       <c r="AB6" s="2"/>
-      <c r="AC6" s="2" t="s">
+      <c r="AC6" s="2"/>
+      <c r="AD6" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="AD6" s="2" t="s">
+      <c r="AE6" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="AE6" s="2" t="s">
+      <c r="AF6" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="AF6" s="21"/>
       <c r="AG6" s="21"/>
       <c r="AH6" s="21"/>
       <c r="AI6" s="21"/>
@@ -2429,14 +2469,14 @@
       <c r="AN6" s="21"/>
       <c r="AO6" s="21"/>
       <c r="AP6" s="21"/>
-      <c r="AQ6" s="21" t="s">
+      <c r="AQ6" s="21"/>
+      <c r="AR6" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="AR6" s="21"/>
-      <c r="AS6" s="3"/>
+      <c r="AS6" s="21"/>
       <c r="AT6" s="3"/>
       <c r="AU6" s="3"/>
-      <c r="AV6" s="6"/>
+      <c r="AV6" s="3"/>
       <c r="AW6" s="6"/>
       <c r="AX6" s="6"/>
       <c r="AY6" s="6"/>
@@ -2452,43 +2492,44 @@
       <c r="BI6" s="6"/>
       <c r="BJ6" s="6"/>
       <c r="BK6" s="6"/>
-      <c r="BL6" s="6" t="s">
+      <c r="BL6" s="6"/>
+      <c r="BM6" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="BM6" s="6" t="s">
+      <c r="BN6" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="BN6" s="6"/>
       <c r="BO6" s="6"/>
       <c r="BP6" s="6"/>
       <c r="BQ6" s="6"/>
-      <c r="BR6" s="6" t="s">
+      <c r="BR6" s="6"/>
+      <c r="BS6" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="BS6" s="6"/>
       <c r="BT6" s="6"/>
       <c r="BU6" s="6"/>
       <c r="BV6" s="6"/>
       <c r="BW6" s="6"/>
       <c r="BX6" s="6"/>
-      <c r="BY6" s="6" t="s">
+      <c r="BY6" s="6"/>
+      <c r="BZ6" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="BZ6" s="6" t="s">
+      <c r="CA6" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="CA6" s="6"/>
       <c r="CB6" s="6"/>
       <c r="CC6" s="6"/>
-      <c r="CD6" s="6" t="s">
+      <c r="CD6" s="6"/>
+      <c r="CE6" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="CE6" s="24"/>
       <c r="CF6" s="24"/>
       <c r="CG6" s="24"/>
       <c r="CH6" s="24"/>
+      <c r="CI6" s="24"/>
     </row>
-    <row r="7" spans="1:86" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>157</v>
       </c>
@@ -2507,248 +2548,251 @@
       <c r="F7" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="35" t="s">
+        <v>275</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="I7" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="J7" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="K7" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="L7" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="M7" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="N7" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="O7" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="O7" s="26" t="s">
+      <c r="P7" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="P7" s="26" t="s">
+      <c r="Q7" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="Q7" s="26" t="s">
+      <c r="R7" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="X7" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="Y7" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="Y7" s="26" t="s">
+      <c r="Z7" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="Z7" s="26" t="s">
+      <c r="AA7" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="AA7" s="26" t="s">
+      <c r="AB7" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="AB7" s="2" t="s">
+      <c r="AC7" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="AC7" s="2" t="s">
+      <c r="AD7" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="AD7" s="26" t="s">
+      <c r="AE7" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="AE7" s="2" t="s">
+      <c r="AF7" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="AF7" s="27" t="s">
+      <c r="AG7" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="AG7" s="27" t="s">
+      <c r="AH7" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="AH7" s="27" t="s">
+      <c r="AI7" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="AI7" s="27" t="s">
+      <c r="AJ7" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="AJ7" s="27" t="s">
+      <c r="AK7" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="AK7" s="27" t="s">
+      <c r="AL7" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="AL7" s="27" t="s">
+      <c r="AM7" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="AM7" s="27" t="s">
+      <c r="AN7" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="AN7" s="27" t="s">
+      <c r="AO7" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="AO7" s="27" t="s">
+      <c r="AP7" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="AP7" s="27" t="s">
+      <c r="AQ7" s="27" t="s">
         <v>198</v>
       </c>
-      <c r="AQ7" s="27" t="s">
+      <c r="AR7" s="27" t="s">
         <v>199</v>
       </c>
-      <c r="AR7" s="27" t="s">
+      <c r="AS7" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="AS7" s="30" t="s">
+      <c r="AT7" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="AT7" s="30" t="s">
+      <c r="AU7" s="30" t="s">
         <v>202</v>
       </c>
-      <c r="AU7" s="30" t="s">
+      <c r="AV7" s="30" t="s">
         <v>203</v>
       </c>
-      <c r="AV7" s="30" t="s">
+      <c r="AW7" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="AW7" s="30" t="s">
+      <c r="AX7" s="30" t="s">
         <v>205</v>
       </c>
-      <c r="AX7" s="6" t="s">
+      <c r="AY7" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="AY7" s="6" t="s">
+      <c r="AZ7" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="AZ7" s="30" t="s">
+      <c r="BA7" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="BA7" s="30" t="s">
+      <c r="BB7" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="BB7" s="30" t="s">
+      <c r="BC7" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="BC7" s="30" t="s">
+      <c r="BD7" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="BD7" s="6" t="s">
+      <c r="BE7" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="BE7" s="30" t="s">
+      <c r="BF7" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="BF7" s="30" t="s">
+      <c r="BG7" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="BG7" s="30" t="s">
+      <c r="BH7" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="BH7" s="30" t="s">
+      <c r="BI7" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="BI7" s="30" t="s">
+      <c r="BJ7" s="30" t="s">
         <v>216</v>
       </c>
-      <c r="BJ7" s="30" t="s">
+      <c r="BK7" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="BK7" s="6" t="s">
+      <c r="BL7" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="BL7" s="6" t="s">
+      <c r="BM7" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="BM7" s="6" t="s">
+      <c r="BN7" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="BN7" s="6" t="s">
+      <c r="BO7" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="BO7" s="6" t="s">
+      <c r="BP7" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="BP7" s="6" t="s">
+      <c r="BQ7" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="BQ7" s="6" t="s">
+      <c r="BR7" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="BR7" s="6" t="s">
+      <c r="BS7" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="BS7" s="6" t="s">
+      <c r="BT7" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="BT7" s="6" t="s">
+      <c r="BU7" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="BU7" s="6" t="s">
+      <c r="BV7" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="BV7" s="6" t="s">
+      <c r="BW7" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="BW7" s="6" t="s">
+      <c r="BX7" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="BX7" s="6" t="s">
+      <c r="BY7" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="BY7" s="28" t="s">
+      <c r="BZ7" s="28" t="s">
         <v>232</v>
       </c>
-      <c r="BZ7" s="6" t="s">
+      <c r="CA7" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="CA7" s="6" t="s">
+      <c r="CB7" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="CB7" s="6" t="s">
+      <c r="CC7" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="CC7" s="6" t="s">
+      <c r="CD7" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="CD7" s="6" t="s">
+      <c r="CE7" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="CE7" s="30" t="s">
+      <c r="CF7" s="30" t="s">
         <v>238</v>
       </c>
-      <c r="CF7" s="30" t="s">
+      <c r="CG7" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="CG7" s="30" t="s">
+      <c r="CH7" s="30" t="s">
         <v>240</v>
       </c>
-      <c r="CH7" s="30" t="s">
+      <c r="CI7" s="30" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="8" spans="1:86" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>242</v>
       </c>
@@ -2767,18 +2811,16 @@
       <c r="F8" s="30" t="s">
         <v>245</v>
       </c>
-      <c r="G8" t="s">
-        <v>269</v>
+      <c r="G8" s="30" t="s">
+        <v>276</v>
       </c>
       <c r="H8" t="s">
         <v>269</v>
       </c>
-      <c r="I8" s="30" t="s">
-        <v>268</v>
-      </c>
-      <c r="J8" s="30" t="s">
-        <v>268</v>
-      </c>
+      <c r="I8" t="s">
+        <v>269</v>
+      </c>
+      <c r="J8" s="30"/>
       <c r="K8" s="30" t="s">
         <v>268</v>
       </c>
@@ -2792,145 +2834,148 @@
         <v>268</v>
       </c>
       <c r="O8" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="P8" s="30" t="s">
         <v>246</v>
       </c>
-      <c r="P8" s="30" t="s">
+      <c r="Q8" s="30" t="s">
         <v>247</v>
       </c>
-      <c r="Q8" s="30" t="s">
+      <c r="R8" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="R8" s="30" t="s">
+      <c r="S8" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="S8" s="31"/>
       <c r="T8" s="31"/>
-      <c r="U8" s="32"/>
+      <c r="U8" s="31"/>
       <c r="V8" s="32"/>
-      <c r="W8" s="30" t="s">
+      <c r="W8" s="32"/>
+      <c r="X8" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="X8" s="32"/>
-      <c r="Y8" s="31">
+      <c r="Y8" s="32"/>
+      <c r="Z8" s="31">
         <v>2.169024E-2</v>
       </c>
-      <c r="Z8" s="31"/>
-      <c r="AA8" s="31" t="s">
+      <c r="AA8" s="31"/>
+      <c r="AB8" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="AB8" s="31"/>
-      <c r="AC8" s="30" t="s">
-        <v>264</v>
-      </c>
+      <c r="AC8" s="31"/>
       <c r="AD8" s="30" t="s">
         <v>264</v>
       </c>
       <c r="AE8" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="AF8" s="30"/>
+      <c r="AF8" s="30" t="s">
+        <v>264</v>
+      </c>
       <c r="AG8" s="30"/>
-      <c r="AH8" s="30" t="s">
+      <c r="AH8" s="30"/>
+      <c r="AI8" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="AI8" s="30"/>
       <c r="AJ8" s="30"/>
       <c r="AK8" s="30"/>
       <c r="AL8" s="30"/>
       <c r="AM8" s="30"/>
       <c r="AN8" s="30"/>
       <c r="AO8" s="30"/>
-      <c r="AP8" s="30" t="s">
-        <v>264</v>
-      </c>
+      <c r="AP8" s="30"/>
       <c r="AQ8" s="30" t="s">
         <v>264</v>
       </c>
       <c r="AR8" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="AS8" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="AS8" s="30"/>
       <c r="AT8" s="30"/>
       <c r="AU8" s="30"/>
       <c r="AV8" s="30"/>
-      <c r="AW8" s="30" t="s">
+      <c r="AW8" s="30"/>
+      <c r="AX8" s="30" t="s">
         <v>252</v>
       </c>
-      <c r="AX8" s="31"/>
       <c r="AY8" s="31"/>
-      <c r="AZ8" s="30" t="s">
+      <c r="AZ8" s="31"/>
+      <c r="BA8" s="30" t="s">
         <v>264</v>
-      </c>
-      <c r="BA8" s="30" t="s">
-        <v>253</v>
       </c>
       <c r="BB8" s="30" t="s">
         <v>253</v>
       </c>
       <c r="BC8" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="BD8" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="BD8" s="33"/>
-      <c r="BE8" s="31">
+      <c r="BE8" s="33"/>
+      <c r="BF8" s="31">
         <v>3</v>
       </c>
-      <c r="BF8" s="30" t="s">
+      <c r="BG8" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="BG8" s="31">
+      <c r="BH8" s="31">
         <v>70</v>
       </c>
-      <c r="BH8" s="31">
+      <c r="BI8" s="31">
         <v>1.4E-2</v>
       </c>
-      <c r="BI8" s="31">
+      <c r="BJ8" s="31">
         <v>200</v>
       </c>
-      <c r="BJ8" s="30"/>
-      <c r="BK8" s="33"/>
-      <c r="BL8" s="30" t="s">
-        <v>264</v>
-      </c>
+      <c r="BK8" s="30"/>
+      <c r="BL8" s="33"/>
       <c r="BM8" s="30" t="s">
         <v>264</v>
       </c>
       <c r="BN8" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="BO8" s="33"/>
-      <c r="BP8" s="30" t="s">
+      <c r="BO8" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="BQ8" s="33"/>
-      <c r="BR8" s="30" t="s">
+      <c r="BP8" s="33"/>
+      <c r="BQ8" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="BS8" s="33"/>
+      <c r="BR8" s="33"/>
+      <c r="BS8" s="30" t="s">
+        <v>264</v>
+      </c>
       <c r="BT8" s="33"/>
       <c r="BU8" s="33"/>
       <c r="BV8" s="33"/>
       <c r="BW8" s="33"/>
       <c r="BX8" s="33"/>
-      <c r="BY8" s="30" t="s">
-        <v>264</v>
-      </c>
+      <c r="BY8" s="33"/>
       <c r="BZ8" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="CA8" s="30"/>
-      <c r="CB8" s="33"/>
+      <c r="CA8" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="CB8" s="30"/>
       <c r="CC8" s="33"/>
-      <c r="CD8" s="30" t="s">
+      <c r="CD8" s="33"/>
+      <c r="CE8" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="CE8" s="30" t="s">
+      <c r="CF8" s="30" t="s">
         <v>252</v>
       </c>
-      <c r="CF8" s="30"/>
       <c r="CG8" s="30"/>
       <c r="CH8" s="30"/>
+      <c r="CI8" s="30"/>
     </row>
-    <row r="9" spans="1:86" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="C9" s="30" t="s">
         <v>254</v>
@@ -2942,46 +2987,46 @@
       <c r="F9" s="30" t="s">
         <v>263</v>
       </c>
-      <c r="I9" s="30"/>
+      <c r="G9" s="30"/>
       <c r="J9" s="30"/>
       <c r="K9" s="30"/>
       <c r="L9" s="30"/>
       <c r="M9" s="30"/>
       <c r="N9" s="30"/>
-      <c r="O9" s="30" t="s">
+      <c r="O9" s="30"/>
+      <c r="P9" s="30" t="s">
         <v>246</v>
       </c>
-      <c r="P9" s="30" t="s">
+      <c r="Q9" s="30" t="s">
         <v>247</v>
       </c>
-      <c r="Q9" s="30" t="s">
+      <c r="R9" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="R9" s="30" t="s">
+      <c r="S9" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="S9" s="31"/>
       <c r="T9" s="31"/>
-      <c r="U9" s="34"/>
+      <c r="U9" s="31"/>
       <c r="V9" s="34"/>
       <c r="W9" s="34"/>
       <c r="X9" s="34"/>
-      <c r="Y9" s="31">
-        <v>2.725352E-2</v>
-      </c>
+      <c r="Y9" s="34"/>
       <c r="Z9" s="31">
         <v>2.725352E-2</v>
       </c>
       <c r="AA9" s="31">
         <v>2.725352E-2</v>
       </c>
-      <c r="AB9" s="31"/>
+      <c r="AB9" s="31">
+        <v>2.725352E-2</v>
+      </c>
       <c r="AC9" s="31"/>
-      <c r="AD9" s="30" t="s">
+      <c r="AD9" s="31"/>
+      <c r="AE9" s="30" t="s">
         <v>250</v>
       </c>
-      <c r="AE9" s="31"/>
-      <c r="AF9" s="30"/>
+      <c r="AF9" s="31"/>
       <c r="AG9" s="30"/>
       <c r="AH9" s="30"/>
       <c r="AI9" s="30"/>
@@ -2993,48 +3038,48 @@
       <c r="AO9" s="30"/>
       <c r="AP9" s="30"/>
       <c r="AQ9" s="30"/>
-      <c r="AR9" s="30" t="s">
+      <c r="AR9" s="30"/>
+      <c r="AS9" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="AS9" s="30"/>
       <c r="AT9" s="30"/>
       <c r="AU9" s="30"/>
       <c r="AV9" s="30"/>
-      <c r="AW9" s="30" t="s">
+      <c r="AW9" s="30"/>
+      <c r="AX9" s="30" t="s">
         <v>252</v>
       </c>
-      <c r="AX9" s="31"/>
       <c r="AY9" s="31"/>
-      <c r="AZ9" s="31">
+      <c r="AZ9" s="31"/>
+      <c r="BA9" s="31">
         <v>0.200098</v>
-      </c>
-      <c r="BA9" s="30" t="s">
-        <v>253</v>
       </c>
       <c r="BB9" s="30" t="s">
         <v>253</v>
       </c>
       <c r="BC9" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="BD9" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="BD9" s="34"/>
-      <c r="BE9" s="31">
+      <c r="BE9" s="34"/>
+      <c r="BF9" s="31">
         <v>3</v>
       </c>
-      <c r="BF9" s="31">
+      <c r="BG9" s="31">
         <v>1680</v>
       </c>
-      <c r="BG9" s="31">
+      <c r="BH9" s="31">
         <v>70</v>
       </c>
-      <c r="BH9" s="31">
+      <c r="BI9" s="31">
         <v>1.54E-2</v>
       </c>
-      <c r="BI9" s="31">
+      <c r="BJ9" s="31">
         <v>220</v>
       </c>
-      <c r="BJ9" s="30"/>
-      <c r="BK9" s="34"/>
+      <c r="BK9" s="30"/>
       <c r="BL9" s="34"/>
       <c r="BM9" s="34"/>
       <c r="BN9" s="34"/>
@@ -3048,20 +3093,21 @@
       <c r="BV9" s="34"/>
       <c r="BW9" s="34"/>
       <c r="BX9" s="34"/>
-      <c r="BY9" s="30"/>
+      <c r="BY9" s="34"/>
       <c r="BZ9" s="30"/>
       <c r="CA9" s="30"/>
-      <c r="CB9" s="34"/>
+      <c r="CB9" s="30"/>
       <c r="CC9" s="34"/>
       <c r="CD9" s="34"/>
-      <c r="CE9" s="30" t="s">
+      <c r="CE9" s="34"/>
+      <c r="CF9" s="30" t="s">
         <v>252</v>
       </c>
-      <c r="CF9" s="30"/>
       <c r="CG9" s="30"/>
       <c r="CH9" s="30"/>
+      <c r="CI9" s="30"/>
     </row>
-    <row r="10" spans="1:86" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
       <c r="C10" s="30" t="s">
         <v>255</v>
@@ -3071,51 +3117,53 @@
       <c r="F10" s="30" t="s">
         <v>260</v>
       </c>
-      <c r="H10" t="s">
+      <c r="G10" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="I10" t="s">
         <v>268</v>
       </c>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30" t="s">
+      <c r="J10" s="30"/>
+      <c r="K10" s="30" t="s">
         <v>270</v>
       </c>
-      <c r="K10" s="30"/>
       <c r="L10" s="30"/>
       <c r="M10" s="30"/>
       <c r="N10" s="30"/>
-      <c r="O10" s="30" t="s">
+      <c r="O10" s="30"/>
+      <c r="P10" s="30" t="s">
         <v>246</v>
       </c>
-      <c r="P10" s="30" t="s">
+      <c r="Q10" s="30" t="s">
         <v>247</v>
       </c>
-      <c r="Q10" s="30" t="s">
+      <c r="R10" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="R10" s="30" t="s">
+      <c r="S10" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="S10" s="31"/>
       <c r="T10" s="31"/>
-      <c r="U10" s="34"/>
+      <c r="U10" s="31"/>
       <c r="V10" s="34"/>
       <c r="W10" s="34"/>
       <c r="X10" s="34"/>
-      <c r="Y10" s="31">
-        <v>1.5365230000000001E-2</v>
-      </c>
+      <c r="Y10" s="34"/>
       <c r="Z10" s="31">
         <v>1.5365230000000001E-2</v>
       </c>
       <c r="AA10" s="31">
         <v>1.5365230000000001E-2</v>
       </c>
-      <c r="AB10" s="31"/>
+      <c r="AB10" s="31">
+        <v>1.5365230000000001E-2</v>
+      </c>
       <c r="AC10" s="31"/>
-      <c r="AD10" s="30" t="s">
+      <c r="AD10" s="31"/>
+      <c r="AE10" s="30" t="s">
         <v>250</v>
       </c>
-      <c r="AE10" s="31"/>
-      <c r="AF10" s="30"/>
+      <c r="AF10" s="31"/>
       <c r="AG10" s="30"/>
       <c r="AH10" s="30"/>
       <c r="AI10" s="30"/>
@@ -3127,48 +3175,48 @@
       <c r="AO10" s="30"/>
       <c r="AP10" s="30"/>
       <c r="AQ10" s="30"/>
-      <c r="AR10" s="30" t="s">
+      <c r="AR10" s="30"/>
+      <c r="AS10" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="AS10" s="30"/>
       <c r="AT10" s="30"/>
       <c r="AU10" s="30"/>
       <c r="AV10" s="30"/>
-      <c r="AW10" s="30" t="s">
+      <c r="AW10" s="30"/>
+      <c r="AX10" s="30" t="s">
         <v>252</v>
       </c>
-      <c r="AX10" s="31"/>
       <c r="AY10" s="31"/>
-      <c r="AZ10" s="31">
+      <c r="AZ10" s="31"/>
+      <c r="BA10" s="31">
         <v>0.200098</v>
-      </c>
-      <c r="BA10" s="30" t="s">
-        <v>253</v>
       </c>
       <c r="BB10" s="30" t="s">
         <v>253</v>
       </c>
       <c r="BC10" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="BD10" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="BD10" s="34"/>
-      <c r="BE10" s="31">
+      <c r="BE10" s="34"/>
+      <c r="BF10" s="31">
         <v>3</v>
       </c>
-      <c r="BF10" s="31">
+      <c r="BG10" s="31">
         <v>1680</v>
       </c>
-      <c r="BG10" s="31">
+      <c r="BH10" s="31">
         <v>70</v>
       </c>
-      <c r="BH10" s="31">
+      <c r="BI10" s="31">
         <v>1.54E-2</v>
       </c>
-      <c r="BI10" s="31">
+      <c r="BJ10" s="31">
         <v>220</v>
       </c>
-      <c r="BJ10" s="30"/>
-      <c r="BK10" s="34"/>
+      <c r="BK10" s="30"/>
       <c r="BL10" s="34"/>
       <c r="BM10" s="34"/>
       <c r="BN10" s="34"/>
@@ -3182,20 +3230,21 @@
       <c r="BV10" s="34"/>
       <c r="BW10" s="34"/>
       <c r="BX10" s="34"/>
-      <c r="BY10" s="30"/>
+      <c r="BY10" s="34"/>
       <c r="BZ10" s="30"/>
       <c r="CA10" s="30"/>
-      <c r="CB10" s="34"/>
+      <c r="CB10" s="30"/>
       <c r="CC10" s="34"/>
       <c r="CD10" s="34"/>
-      <c r="CE10" s="30" t="s">
+      <c r="CE10" s="34"/>
+      <c r="CF10" s="30" t="s">
         <v>252</v>
       </c>
-      <c r="CF10" s="30"/>
       <c r="CG10" s="30"/>
       <c r="CH10" s="30"/>
+      <c r="CI10" s="30"/>
     </row>
-    <row r="11" spans="1:86" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="C11" s="30" t="s">
         <v>256</v>
       </c>
@@ -3206,50 +3255,54 @@
       <c r="F11" s="30" t="s">
         <v>261</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="H11" t="s">
         <v>267</v>
       </c>
-      <c r="H11" s="34"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="30" t="s">
+        <v>268</v>
+      </c>
       <c r="K11" s="30"/>
       <c r="L11" s="30"/>
       <c r="M11" s="30"/>
       <c r="N11" s="30"/>
-      <c r="O11" s="30" t="s">
+      <c r="O11" s="30"/>
+      <c r="P11" s="30" t="s">
         <v>257</v>
       </c>
-      <c r="P11" s="30" t="s">
+      <c r="Q11" s="30" t="s">
         <v>247</v>
       </c>
-      <c r="Q11" s="30" t="s">
+      <c r="R11" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="R11" s="30" t="s">
+      <c r="S11" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="S11" s="31"/>
       <c r="T11" s="31"/>
-      <c r="U11" s="34"/>
+      <c r="U11" s="31"/>
       <c r="V11" s="34"/>
       <c r="W11" s="34"/>
       <c r="X11" s="34"/>
-      <c r="Y11" s="31">
-        <v>4.8993170000000003E-2</v>
-      </c>
+      <c r="Y11" s="34"/>
       <c r="Z11" s="31">
         <v>4.8993170000000003E-2</v>
       </c>
       <c r="AA11" s="31">
         <v>4.8993170000000003E-2</v>
       </c>
-      <c r="AB11" s="31"/>
+      <c r="AB11" s="31">
+        <v>4.8993170000000003E-2</v>
+      </c>
       <c r="AC11" s="31"/>
-      <c r="AD11" s="30" t="s">
+      <c r="AD11" s="31"/>
+      <c r="AE11" s="30" t="s">
         <v>250</v>
       </c>
-      <c r="AE11" s="31"/>
-      <c r="AF11" s="30"/>
+      <c r="AF11" s="31"/>
       <c r="AG11" s="30"/>
       <c r="AH11" s="30"/>
       <c r="AI11" s="30"/>
@@ -3261,48 +3314,48 @@
       <c r="AO11" s="30"/>
       <c r="AP11" s="30"/>
       <c r="AQ11" s="30"/>
-      <c r="AR11" s="30" t="s">
+      <c r="AR11" s="30"/>
+      <c r="AS11" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="AS11" s="30"/>
       <c r="AT11" s="30"/>
       <c r="AU11" s="30"/>
       <c r="AV11" s="30"/>
-      <c r="AW11" s="30" t="s">
+      <c r="AW11" s="30"/>
+      <c r="AX11" s="30" t="s">
         <v>252</v>
       </c>
-      <c r="AX11" s="31"/>
       <c r="AY11" s="31"/>
-      <c r="AZ11" s="31">
+      <c r="AZ11" s="31"/>
+      <c r="BA11" s="31">
         <v>0.200098</v>
-      </c>
-      <c r="BA11" s="30" t="s">
-        <v>253</v>
       </c>
       <c r="BB11" s="30" t="s">
         <v>253</v>
       </c>
       <c r="BC11" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="BD11" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="BD11" s="34"/>
-      <c r="BE11" s="31">
+      <c r="BE11" s="34"/>
+      <c r="BF11" s="31">
         <v>3</v>
       </c>
-      <c r="BF11" s="31">
+      <c r="BG11" s="31">
         <v>600</v>
       </c>
-      <c r="BG11" s="31">
+      <c r="BH11" s="31">
         <v>70</v>
       </c>
-      <c r="BH11" s="31">
+      <c r="BI11" s="31">
         <v>1.54E-2</v>
       </c>
-      <c r="BI11" s="31">
+      <c r="BJ11" s="31">
         <v>220</v>
       </c>
-      <c r="BJ11" s="30"/>
-      <c r="BK11" s="34"/>
+      <c r="BK11" s="30"/>
       <c r="BL11" s="34"/>
       <c r="BM11" s="34"/>
       <c r="BN11" s="34"/>
@@ -3316,20 +3369,21 @@
       <c r="BV11" s="34"/>
       <c r="BW11" s="34"/>
       <c r="BX11" s="34"/>
-      <c r="BY11" s="30"/>
+      <c r="BY11" s="34"/>
       <c r="BZ11" s="30"/>
       <c r="CA11" s="30"/>
-      <c r="CB11" s="34"/>
+      <c r="CB11" s="30"/>
       <c r="CC11" s="34"/>
       <c r="CD11" s="34"/>
-      <c r="CE11" s="30" t="s">
+      <c r="CE11" s="34"/>
+      <c r="CF11" s="30" t="s">
         <v>252</v>
       </c>
-      <c r="CF11" s="30"/>
       <c r="CG11" s="30"/>
       <c r="CH11" s="30"/>
+      <c r="CI11" s="30"/>
     </row>
-    <row r="12" spans="1:86" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="C12" s="30" t="s">
         <v>258</v>
       </c>
@@ -3341,49 +3395,51 @@
         <v>262</v>
       </c>
       <c r="G12" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="H12" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="H12" s="34"/>
-      <c r="I12" s="30"/>
+      <c r="I12" s="34"/>
       <c r="J12" s="30"/>
       <c r="K12" s="30"/>
       <c r="L12" s="30"/>
       <c r="M12" s="30"/>
       <c r="N12" s="30"/>
-      <c r="O12" s="30" t="s">
+      <c r="O12" s="30"/>
+      <c r="P12" s="30" t="s">
         <v>246</v>
       </c>
-      <c r="P12" s="30" t="s">
+      <c r="Q12" s="30" t="s">
         <v>247</v>
       </c>
-      <c r="Q12" s="30" t="s">
+      <c r="R12" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="R12" s="30" t="s">
+      <c r="S12" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="S12" s="31"/>
       <c r="T12" s="31"/>
-      <c r="U12" s="34"/>
+      <c r="U12" s="31"/>
       <c r="V12" s="34"/>
       <c r="W12" s="34"/>
       <c r="X12" s="34"/>
-      <c r="Y12" s="31">
-        <v>1.4276580000000001E-2</v>
-      </c>
+      <c r="Y12" s="34"/>
       <c r="Z12" s="31">
         <v>1.4276580000000001E-2</v>
       </c>
       <c r="AA12" s="31">
         <v>1.4276580000000001E-2</v>
       </c>
-      <c r="AB12" s="31"/>
+      <c r="AB12" s="31">
+        <v>1.4276580000000001E-2</v>
+      </c>
       <c r="AC12" s="31"/>
-      <c r="AD12" s="30" t="s">
+      <c r="AD12" s="31"/>
+      <c r="AE12" s="30" t="s">
         <v>250</v>
       </c>
-      <c r="AE12" s="31"/>
-      <c r="AF12" s="30"/>
+      <c r="AF12" s="31"/>
       <c r="AG12" s="30"/>
       <c r="AH12" s="30"/>
       <c r="AI12" s="30"/>
@@ -3395,48 +3451,48 @@
       <c r="AO12" s="30"/>
       <c r="AP12" s="30"/>
       <c r="AQ12" s="30"/>
-      <c r="AR12" s="30" t="s">
+      <c r="AR12" s="30"/>
+      <c r="AS12" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="AS12" s="30"/>
       <c r="AT12" s="30"/>
       <c r="AU12" s="30"/>
       <c r="AV12" s="30"/>
-      <c r="AW12" s="30" t="s">
+      <c r="AW12" s="30"/>
+      <c r="AX12" s="30" t="s">
         <v>252</v>
       </c>
-      <c r="AX12" s="31"/>
       <c r="AY12" s="31"/>
-      <c r="AZ12" s="31">
+      <c r="AZ12" s="31"/>
+      <c r="BA12" s="31">
         <v>0.200098</v>
-      </c>
-      <c r="BA12" s="30" t="s">
-        <v>253</v>
       </c>
       <c r="BB12" s="30" t="s">
         <v>253</v>
       </c>
       <c r="BC12" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="BD12" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="BD12" s="34"/>
-      <c r="BE12" s="31">
+      <c r="BE12" s="34"/>
+      <c r="BF12" s="31">
         <v>3</v>
       </c>
-      <c r="BF12" s="31">
+      <c r="BG12" s="31">
         <v>1440</v>
       </c>
-      <c r="BG12" s="31">
+      <c r="BH12" s="31">
         <v>70</v>
       </c>
-      <c r="BH12" s="31">
+      <c r="BI12" s="31">
         <v>1.4E-2</v>
       </c>
-      <c r="BI12" s="31">
+      <c r="BJ12" s="31">
         <v>200</v>
       </c>
-      <c r="BJ12" s="30"/>
-      <c r="BK12" s="34"/>
+      <c r="BK12" s="30"/>
       <c r="BL12" s="34"/>
       <c r="BM12" s="34"/>
       <c r="BN12" s="34"/>
@@ -3450,20 +3506,21 @@
       <c r="BV12" s="34"/>
       <c r="BW12" s="34"/>
       <c r="BX12" s="34"/>
-      <c r="BY12" s="30"/>
+      <c r="BY12" s="34"/>
       <c r="BZ12" s="30"/>
       <c r="CA12" s="30"/>
-      <c r="CB12" s="34"/>
+      <c r="CB12" s="30"/>
       <c r="CC12" s="34"/>
       <c r="CD12" s="34"/>
-      <c r="CE12" s="30" t="s">
+      <c r="CE12" s="34"/>
+      <c r="CF12" s="30" t="s">
         <v>252</v>
       </c>
-      <c r="CF12" s="30"/>
       <c r="CG12" s="30"/>
       <c r="CH12" s="30"/>
+      <c r="CI12" s="30"/>
     </row>
-    <row r="13" spans="1:86" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="C13" s="30" t="s">
         <v>259</v>
       </c>
@@ -3472,48 +3529,50 @@
         <v>265</v>
       </c>
       <c r="F13" s="30"/>
-      <c r="G13" s="34"/>
+      <c r="G13" s="30" t="s">
+        <v>276</v>
+      </c>
       <c r="H13" s="34"/>
-      <c r="I13" s="30"/>
+      <c r="I13" s="34"/>
       <c r="J13" s="30"/>
       <c r="K13" s="30"/>
       <c r="L13" s="30"/>
       <c r="M13" s="30"/>
       <c r="N13" s="30"/>
-      <c r="O13" s="30" t="s">
+      <c r="O13" s="30"/>
+      <c r="P13" s="30" t="s">
         <v>246</v>
       </c>
-      <c r="P13" s="30" t="s">
+      <c r="Q13" s="30" t="s">
         <v>247</v>
       </c>
-      <c r="Q13" s="30" t="s">
+      <c r="R13" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="R13" s="30" t="s">
+      <c r="S13" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="S13" s="31"/>
       <c r="T13" s="31"/>
-      <c r="U13" s="34"/>
+      <c r="U13" s="31"/>
       <c r="V13" s="34"/>
       <c r="W13" s="34"/>
       <c r="X13" s="34"/>
-      <c r="Y13" s="31">
-        <v>2.725352E-2</v>
-      </c>
+      <c r="Y13" s="34"/>
       <c r="Z13" s="31">
         <v>2.725352E-2</v>
       </c>
       <c r="AA13" s="31">
         <v>2.725352E-2</v>
       </c>
-      <c r="AB13" s="31"/>
+      <c r="AB13" s="31">
+        <v>2.725352E-2</v>
+      </c>
       <c r="AC13" s="31"/>
-      <c r="AD13" s="30" t="s">
+      <c r="AD13" s="31"/>
+      <c r="AE13" s="30" t="s">
         <v>250</v>
       </c>
-      <c r="AE13" s="31"/>
-      <c r="AF13" s="30"/>
+      <c r="AF13" s="31"/>
       <c r="AG13" s="30"/>
       <c r="AH13" s="30"/>
       <c r="AI13" s="30"/>
@@ -3525,48 +3584,48 @@
       <c r="AO13" s="30"/>
       <c r="AP13" s="30"/>
       <c r="AQ13" s="30"/>
-      <c r="AR13" s="30" t="s">
+      <c r="AR13" s="30"/>
+      <c r="AS13" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="AS13" s="30"/>
       <c r="AT13" s="30"/>
       <c r="AU13" s="30"/>
       <c r="AV13" s="30"/>
-      <c r="AW13" s="30" t="s">
+      <c r="AW13" s="30"/>
+      <c r="AX13" s="30" t="s">
         <v>252</v>
       </c>
-      <c r="AX13" s="31"/>
       <c r="AY13" s="31"/>
-      <c r="AZ13" s="31">
+      <c r="AZ13" s="31"/>
+      <c r="BA13" s="31">
         <v>0.200098</v>
-      </c>
-      <c r="BA13" s="30" t="s">
-        <v>253</v>
       </c>
       <c r="BB13" s="30" t="s">
         <v>253</v>
       </c>
       <c r="BC13" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="BD13" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="BD13" s="34"/>
-      <c r="BE13" s="31">
+      <c r="BE13" s="34"/>
+      <c r="BF13" s="31">
         <v>3</v>
       </c>
-      <c r="BF13" s="31">
+      <c r="BG13" s="31">
         <v>1680</v>
       </c>
-      <c r="BG13" s="31">
+      <c r="BH13" s="31">
         <v>70</v>
       </c>
-      <c r="BH13" s="31">
+      <c r="BI13" s="31">
         <v>1.54E-2</v>
       </c>
-      <c r="BI13" s="31">
+      <c r="BJ13" s="31">
         <v>220</v>
       </c>
-      <c r="BJ13" s="30"/>
-      <c r="BK13" s="34"/>
+      <c r="BK13" s="30"/>
       <c r="BL13" s="34"/>
       <c r="BM13" s="34"/>
       <c r="BN13" s="34"/>
@@ -3580,18 +3639,156 @@
       <c r="BV13" s="34"/>
       <c r="BW13" s="34"/>
       <c r="BX13" s="34"/>
-      <c r="BY13" s="30"/>
+      <c r="BY13" s="34"/>
       <c r="BZ13" s="30"/>
       <c r="CA13" s="30"/>
-      <c r="CB13" s="34"/>
+      <c r="CB13" s="30"/>
       <c r="CC13" s="34"/>
       <c r="CD13" s="34"/>
-      <c r="CE13" s="30" t="s">
+      <c r="CE13" s="34"/>
+      <c r="CF13" s="30" t="s">
         <v>252</v>
       </c>
-      <c r="CF13" s="30"/>
       <c r="CG13" s="30"/>
       <c r="CH13" s="30"/>
+      <c r="CI13" s="30"/>
+    </row>
+    <row r="14" spans="1:87" ht="16" x14ac:dyDescent="0.2">
+      <c r="C14" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="D14" s="34"/>
+      <c r="E14" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="G14" s="30" t="s">
+        <v>277</v>
+      </c>
+      <c r="H14" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="I14" s="34"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="30"/>
+      <c r="P14" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q14" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="R14" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="S14" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="T14" s="31"/>
+      <c r="U14" s="31"/>
+      <c r="V14" s="34"/>
+      <c r="W14" s="34"/>
+      <c r="X14" s="34"/>
+      <c r="Y14" s="34"/>
+      <c r="Z14" s="31">
+        <v>1.4276580000000001E-2</v>
+      </c>
+      <c r="AA14" s="31">
+        <v>1.4276580000000001E-2</v>
+      </c>
+      <c r="AB14" s="31">
+        <v>1.4276580000000001E-2</v>
+      </c>
+      <c r="AC14" s="31"/>
+      <c r="AD14" s="31"/>
+      <c r="AE14" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="AF14" s="31"/>
+      <c r="AG14" s="30"/>
+      <c r="AH14" s="30"/>
+      <c r="AI14" s="30"/>
+      <c r="AJ14" s="30"/>
+      <c r="AK14" s="30"/>
+      <c r="AL14" s="30"/>
+      <c r="AM14" s="30"/>
+      <c r="AN14" s="30"/>
+      <c r="AO14" s="30"/>
+      <c r="AP14" s="30"/>
+      <c r="AQ14" s="30"/>
+      <c r="AR14" s="30"/>
+      <c r="AS14" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="AT14" s="30"/>
+      <c r="AU14" s="30"/>
+      <c r="AV14" s="30"/>
+      <c r="AW14" s="30"/>
+      <c r="AX14" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="AY14" s="31"/>
+      <c r="AZ14" s="31"/>
+      <c r="BA14" s="31">
+        <v>0.200098</v>
+      </c>
+      <c r="BB14" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="BC14" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="BD14" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="BE14" s="34"/>
+      <c r="BF14" s="31">
+        <v>3</v>
+      </c>
+      <c r="BG14" s="31">
+        <v>1440</v>
+      </c>
+      <c r="BH14" s="31">
+        <v>70</v>
+      </c>
+      <c r="BI14" s="31">
+        <v>1.4E-2</v>
+      </c>
+      <c r="BJ14" s="31">
+        <v>200</v>
+      </c>
+      <c r="BK14" s="30"/>
+      <c r="BL14" s="34"/>
+      <c r="BM14" s="34"/>
+      <c r="BN14" s="34"/>
+      <c r="BO14" s="34"/>
+      <c r="BP14" s="34"/>
+      <c r="BQ14" s="34"/>
+      <c r="BR14" s="34"/>
+      <c r="BS14" s="34"/>
+      <c r="BT14" s="34"/>
+      <c r="BU14" s="34"/>
+      <c r="BV14" s="34"/>
+      <c r="BW14" s="34"/>
+      <c r="BX14" s="34"/>
+      <c r="BY14" s="34"/>
+      <c r="BZ14" s="30"/>
+      <c r="CA14" s="30"/>
+      <c r="CB14" s="30"/>
+      <c r="CC14" s="34"/>
+      <c r="CD14" s="34"/>
+      <c r="CE14" s="34"/>
+      <c r="CF14" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="CG14" s="30"/>
+      <c r="CH14" s="30"/>
+      <c r="CI14" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/spec/fixtures/batch_submission_manifest_errors_test.xlsx
+++ b/spec/fixtures/batch_submission_manifest_errors_test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smc101/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smc101/vagrant/morphosource-vagrant/MorphoSource_SF/spec/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55141641-F608-FE49-874F-2F4A3DA82165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70DB331-65CB-DB42-924B-0AE2C2DEE44D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="32000" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -844,9 +844,6 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>Zach Randall</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -921,6 +918,9 @@
   </si>
   <si>
     <t>Raw</t>
+  </si>
+  <si>
+    <t>John Doe</t>
   </si>
 </sst>
 </file>
@@ -1748,7 +1748,7 @@
         <v>55</v>
       </c>
       <c r="BE2" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="BF2" s="6" t="s">
         <v>56</v>
@@ -1857,7 +1857,7 @@
       <c r="E3" s="9"/>
       <c r="F3" s="10"/>
       <c r="G3" s="37" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>86</v>
@@ -2424,7 +2424,7 @@
         <v>145</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -2549,7 +2549,7 @@
         <v>162</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>163</v>
@@ -2699,7 +2699,7 @@
         <v>211</v>
       </c>
       <c r="BE7" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="BF7" s="30" t="s">
         <v>212</v>
@@ -2803,38 +2803,38 @@
         <v>244</v>
       </c>
       <c r="D8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F8" s="30" t="s">
         <v>245</v>
       </c>
       <c r="G8" s="30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J8" s="30"/>
       <c r="K8" s="30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L8" s="30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="M8" s="30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="N8" s="30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O8" s="30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P8" s="30" t="s">
         <v>246</v>
@@ -2843,7 +2843,7 @@
         <v>247</v>
       </c>
       <c r="R8" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="S8" s="30" t="s">
         <v>249</v>
@@ -2853,7 +2853,7 @@
       <c r="V8" s="32"/>
       <c r="W8" s="32"/>
       <c r="X8" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Y8" s="32"/>
       <c r="Z8" s="31">
@@ -2861,22 +2861,22 @@
       </c>
       <c r="AA8" s="31"/>
       <c r="AB8" s="31" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AC8" s="31"/>
       <c r="AD8" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AE8" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AF8" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG8" s="30"/>
       <c r="AH8" s="30"/>
       <c r="AI8" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AJ8" s="30"/>
       <c r="AK8" s="30"/>
@@ -2886,10 +2886,10 @@
       <c r="AO8" s="30"/>
       <c r="AP8" s="30"/>
       <c r="AQ8" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AR8" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AS8" s="30" t="s">
         <v>251</v>
@@ -2899,18 +2899,18 @@
       <c r="AV8" s="30"/>
       <c r="AW8" s="30"/>
       <c r="AX8" s="30" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="AY8" s="31"/>
       <c r="AZ8" s="31"/>
       <c r="BA8" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="BB8" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="BC8" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="BD8" s="30" t="s">
         <v>251</v>
@@ -2920,7 +2920,7 @@
         <v>3</v>
       </c>
       <c r="BG8" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="BH8" s="31">
         <v>70</v>
@@ -2934,21 +2934,21 @@
       <c r="BK8" s="30"/>
       <c r="BL8" s="33"/>
       <c r="BM8" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="BN8" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="BO8" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="BP8" s="33"/>
       <c r="BQ8" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="BR8" s="33"/>
       <c r="BS8" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="BT8" s="33"/>
       <c r="BU8" s="33"/>
@@ -2957,19 +2957,19 @@
       <c r="BX8" s="33"/>
       <c r="BY8" s="33"/>
       <c r="BZ8" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="CA8" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="CB8" s="30"/>
       <c r="CC8" s="33"/>
       <c r="CD8" s="33"/>
       <c r="CE8" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="CF8" s="30" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="CG8" s="30"/>
       <c r="CH8" s="30"/>
@@ -2978,14 +2978,14 @@
     <row r="9" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="C9" s="30" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D9" s="34"/>
       <c r="E9" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G9" s="30"/>
       <c r="J9" s="30"/>
@@ -3047,7 +3047,7 @@
       <c r="AV9" s="30"/>
       <c r="AW9" s="30"/>
       <c r="AX9" s="30" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="AY9" s="31"/>
       <c r="AZ9" s="31"/>
@@ -3055,10 +3055,10 @@
         <v>0.200098</v>
       </c>
       <c r="BB9" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="BC9" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="BD9" s="30" t="s">
         <v>251</v>
@@ -3101,7 +3101,7 @@
       <c r="CD9" s="34"/>
       <c r="CE9" s="34"/>
       <c r="CF9" s="30" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="CG9" s="30"/>
       <c r="CH9" s="30"/>
@@ -3110,22 +3110,22 @@
     <row r="10" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
       <c r="C10" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D10" s="34"/>
       <c r="E10" s="30"/>
       <c r="F10" s="30" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G10" s="30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J10" s="30"/>
       <c r="K10" s="30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L10" s="30"/>
       <c r="M10" s="30"/>
@@ -3184,7 +3184,7 @@
       <c r="AV10" s="30"/>
       <c r="AW10" s="30"/>
       <c r="AX10" s="30" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="AY10" s="31"/>
       <c r="AZ10" s="31"/>
@@ -3192,10 +3192,10 @@
         <v>0.200098</v>
       </c>
       <c r="BB10" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="BC10" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="BD10" s="30" t="s">
         <v>251</v>
@@ -3238,7 +3238,7 @@
       <c r="CD10" s="34"/>
       <c r="CE10" s="34"/>
       <c r="CF10" s="30" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="CG10" s="30"/>
       <c r="CH10" s="30"/>
@@ -3246,24 +3246,24 @@
     </row>
     <row r="11" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="C11" s="30" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D11" s="34"/>
       <c r="E11" s="30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G11" s="30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I11" s="34"/>
       <c r="J11" s="30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K11" s="30"/>
       <c r="L11" s="30"/>
@@ -3271,7 +3271,7 @@
       <c r="N11" s="30"/>
       <c r="O11" s="30"/>
       <c r="P11" s="30" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Q11" s="30" t="s">
         <v>247</v>
@@ -3323,7 +3323,7 @@
       <c r="AV11" s="30"/>
       <c r="AW11" s="30"/>
       <c r="AX11" s="30" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="AY11" s="31"/>
       <c r="AZ11" s="31"/>
@@ -3331,10 +3331,10 @@
         <v>0.200098</v>
       </c>
       <c r="BB11" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="BC11" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="BD11" s="30" t="s">
         <v>251</v>
@@ -3377,7 +3377,7 @@
       <c r="CD11" s="34"/>
       <c r="CE11" s="34"/>
       <c r="CF11" s="30" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="CG11" s="30"/>
       <c r="CH11" s="30"/>
@@ -3385,20 +3385,20 @@
     </row>
     <row r="12" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="C12" s="30" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D12" s="34"/>
       <c r="E12" s="30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F12" s="30" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G12" s="30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H12" s="30" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I12" s="34"/>
       <c r="J12" s="30"/>
@@ -3460,7 +3460,7 @@
       <c r="AV12" s="30"/>
       <c r="AW12" s="30"/>
       <c r="AX12" s="30" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="AY12" s="31"/>
       <c r="AZ12" s="31"/>
@@ -3468,10 +3468,10 @@
         <v>0.200098</v>
       </c>
       <c r="BB12" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="BC12" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="BD12" s="30" t="s">
         <v>251</v>
@@ -3514,7 +3514,7 @@
       <c r="CD12" s="34"/>
       <c r="CE12" s="34"/>
       <c r="CF12" s="30" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="CG12" s="30"/>
       <c r="CH12" s="30"/>
@@ -3522,15 +3522,15 @@
     </row>
     <row r="13" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="C13" s="30" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D13" s="34"/>
       <c r="E13" s="30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F13" s="30"/>
       <c r="G13" s="30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H13" s="34"/>
       <c r="I13" s="34"/>
@@ -3593,7 +3593,7 @@
       <c r="AV13" s="30"/>
       <c r="AW13" s="30"/>
       <c r="AX13" s="30" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="AY13" s="31"/>
       <c r="AZ13" s="31"/>
@@ -3601,10 +3601,10 @@
         <v>0.200098</v>
       </c>
       <c r="BB13" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="BC13" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="BD13" s="30" t="s">
         <v>251</v>
@@ -3647,7 +3647,7 @@
       <c r="CD13" s="34"/>
       <c r="CE13" s="34"/>
       <c r="CF13" s="30" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="CG13" s="30"/>
       <c r="CH13" s="30"/>
@@ -3655,20 +3655,20 @@
     </row>
     <row r="14" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="C14" s="30" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D14" s="34"/>
       <c r="E14" s="30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G14" s="30" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H14" s="30" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I14" s="34"/>
       <c r="J14" s="30"/>
@@ -3730,7 +3730,7 @@
       <c r="AV14" s="30"/>
       <c r="AW14" s="30"/>
       <c r="AX14" s="30" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="AY14" s="31"/>
       <c r="AZ14" s="31"/>
@@ -3738,10 +3738,10 @@
         <v>0.200098</v>
       </c>
       <c r="BB14" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="BC14" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="BD14" s="30" t="s">
         <v>251</v>
@@ -3784,7 +3784,7 @@
       <c r="CD14" s="34"/>
       <c r="CE14" s="34"/>
       <c r="CF14" s="30" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="CG14" s="30"/>
       <c r="CH14" s="30"/>

--- a/spec/fixtures/batch_submission_manifest_errors_test.xlsx
+++ b/spec/fixtures/batch_submission_manifest_errors_test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10410"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smc101/vagrant/morphosource-vagrant/MorphoSource_SF/spec/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70DB331-65CB-DB42-924B-0AE2C2DEE44D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C23A274A-C190-1044-9D7E-ACAA7B30BA36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="32000" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="280">
   <si>
     <t>Field Section</t>
   </si>
@@ -184,9 +184,6 @@
     <t>Flux normalization</t>
   </si>
   <si>
-    <t>Geometric calibration</t>
-  </si>
-  <si>
     <t>Shading correction</t>
   </si>
   <si>
@@ -329,9 +326,6 @@
   </si>
   <si>
     <t>Only takes yes/no values. Flux Normalization Calibration</t>
-  </si>
-  <si>
-    <t>Only takes yes/no values. Geometric Calibration</t>
   </si>
   <si>
     <t>Only takes yes/no values. Shading Correction Calibration</t>
@@ -718,9 +712,6 @@
     <t>imaging_event.ct.flux_normalization</t>
   </si>
   <si>
-    <t>imaging_event.ct.geometric_calibration</t>
-  </si>
-  <si>
     <t>imaging_event.ct.shading_correction</t>
   </si>
   <si>
@@ -921,6 +912,22 @@
   </si>
   <si>
     <t>John Doe</t>
+  </si>
+  <si>
+    <t>Pixel spacing calibration</t>
+  </si>
+  <si>
+    <t>Geometry: Geometry
+Fiducial: Fiducial</t>
+  </si>
+  <si>
+    <t>imaging_event.ct.pixel_spacing_calibration</t>
+  </si>
+  <si>
+    <t>Geometry</t>
+  </si>
+  <si>
+    <t>INVALID</t>
   </si>
 </sst>
 </file>
@@ -1060,7 +1067,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1123,6 +1130,10 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1338,8 +1349,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06ED7EC9-286B-1D49-A57D-A989376D77CC}">
-  <dimension ref="A1:CI14"/>
+  <dimension ref="A1:CI16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="55" max="55" width="18.1640625" style="41" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:87" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
@@ -1502,7 +1516,7 @@
       <c r="BB1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="BC1" s="6" t="s">
+      <c r="BC1" s="38" t="s">
         <v>11</v>
       </c>
       <c r="BD1" s="6" t="s">
@@ -1741,92 +1755,92 @@
       <c r="BB2" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="BC2" s="6" t="s">
+      <c r="BC2" s="38" t="s">
+        <v>275</v>
+      </c>
+      <c r="BD2" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="BD2" s="6" t="s">
+      <c r="BE2" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="BF2" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="BE2" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="BF2" s="6" t="s">
+      <c r="BG2" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="BG2" s="6" t="s">
+      <c r="BH2" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="BH2" s="6" t="s">
+      <c r="BI2" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="BI2" s="6" t="s">
+      <c r="BJ2" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="BJ2" s="6" t="s">
+      <c r="BK2" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="BK2" s="6" t="s">
+      <c r="BL2" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="BL2" s="6" t="s">
+      <c r="BM2" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="BM2" s="6" t="s">
+      <c r="BN2" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="BN2" s="6" t="s">
+      <c r="BO2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="BO2" s="6" t="s">
+      <c r="BP2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="BP2" s="6" t="s">
+      <c r="BQ2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="BQ2" s="6" t="s">
+      <c r="BR2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="BR2" s="6" t="s">
+      <c r="BS2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="BS2" s="6" t="s">
+      <c r="BT2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="BT2" s="6" t="s">
+      <c r="BU2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="BU2" s="6" t="s">
+      <c r="BV2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="BV2" s="6" t="s">
+      <c r="BW2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="BW2" s="6" t="s">
+      <c r="BX2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="BX2" s="6" t="s">
+      <c r="BY2" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="BY2" s="6" t="s">
+      <c r="BZ2" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="BZ2" s="6" t="s">
+      <c r="CA2" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="CA2" s="6" t="s">
+      <c r="CB2" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="CB2" s="6" t="s">
+      <c r="CC2" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="CC2" s="6" t="s">
+      <c r="CD2" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="CD2" s="6" t="s">
+      <c r="CE2" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="CE2" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="CF2" s="24" t="s">
         <v>22</v>
@@ -1843,70 +1857,70 @@
     </row>
     <row r="3" spans="1:87" ht="139.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="10" t="s">
         <v>84</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>85</v>
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="10"/>
       <c r="G3" s="37" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="11"/>
       <c r="K3" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L3" s="12"/>
       <c r="M3" s="12"/>
       <c r="N3" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="O3" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="P3" s="13" t="s">
         <v>89</v>
-      </c>
-      <c r="P3" s="13" t="s">
-        <v>90</v>
       </c>
       <c r="Q3" s="14"/>
       <c r="R3" s="14"/>
       <c r="S3" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="T3" s="13" t="s">
         <v>91</v>
-      </c>
-      <c r="T3" s="13" t="s">
-        <v>92</v>
       </c>
       <c r="U3" s="2"/>
       <c r="V3" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W3" s="13"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="2"/>
       <c r="Z3" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA3" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="AA3" s="15" t="s">
+      <c r="AB3" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="AB3" s="15" t="s">
+      <c r="AC3" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="AC3" s="13" t="s">
+      <c r="AD3" s="13" t="s">
         <v>97</v>
-      </c>
-      <c r="AD3" s="13" t="s">
-        <v>98</v>
       </c>
       <c r="AE3" s="14"/>
       <c r="AF3" s="2"/>
@@ -1923,7 +1937,7 @@
       <c r="AQ3" s="16"/>
       <c r="AR3" s="16"/>
       <c r="AS3" s="21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AT3" s="17"/>
       <c r="AU3" s="17"/>
@@ -1931,97 +1945,95 @@
       <c r="AW3" s="6"/>
       <c r="AX3" s="6"/>
       <c r="AY3" s="18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AZ3" s="18"/>
       <c r="BA3" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="BB3" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="BB3" s="19" t="s">
+      <c r="BC3" s="19"/>
+      <c r="BD3" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="BC3" s="19" t="s">
+      <c r="BE3" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="BD3" s="19" t="s">
+      <c r="BF3" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="BE3" s="19" t="s">
+      <c r="BG3" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="BF3" s="19" t="s">
+      <c r="BH3" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="BG3" s="19" t="s">
+      <c r="BI3" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="BH3" s="19" t="s">
+      <c r="BJ3" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="BI3" s="19" t="s">
+      <c r="BK3" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="BJ3" s="19" t="s">
+      <c r="BL3" s="18" t="s">
         <v>110</v>
-      </c>
-      <c r="BK3" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="BL3" s="18" t="s">
-        <v>112</v>
       </c>
       <c r="BM3" s="18"/>
       <c r="BN3" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="BO3" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="BP3" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="BO3" s="20" t="s">
+      <c r="BQ3" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="BP3" s="20" t="s">
+      <c r="BR3" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="BQ3" s="20" t="s">
+      <c r="BS3" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="BR3" s="20" t="s">
+      <c r="BT3" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="BS3" s="18" t="s">
+      <c r="BU3" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="BT3" s="18" t="s">
+      <c r="BV3" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="BU3" s="18" t="s">
+      <c r="BW3" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="BV3" s="18" t="s">
+      <c r="BX3" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="BW3" s="18" t="s">
+      <c r="BY3" s="18" t="s">
         <v>122</v>
-      </c>
-      <c r="BX3" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="BY3" s="18" t="s">
-        <v>124</v>
       </c>
       <c r="BZ3" s="19"/>
       <c r="CA3" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="CB3" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="CC3" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="CB3" s="18" t="s">
+      <c r="CD3" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="CE3" s="19" t="s">
         <v>126</v>
-      </c>
-      <c r="CC3" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="CD3" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="CE3" s="19" t="s">
-        <v>128</v>
       </c>
       <c r="CF3" s="24"/>
       <c r="CG3" s="24"/>
@@ -2030,42 +2042,42 @@
     </row>
     <row r="4" spans="1:87" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>131</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="12"/>
       <c r="K4" s="12"/>
       <c r="L4" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="Q4" s="14"/>
       <c r="R4" s="14"/>
@@ -2077,13 +2089,13 @@
       <c r="X4" s="2"/>
       <c r="Y4" s="2"/>
       <c r="Z4" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AC4" s="2"/>
       <c r="AD4" s="2"/>
@@ -2111,7 +2123,7 @@
       <c r="AZ4" s="6"/>
       <c r="BA4" s="6"/>
       <c r="BB4" s="6"/>
-      <c r="BC4" s="6"/>
+      <c r="BC4" s="38"/>
       <c r="BD4" s="6"/>
       <c r="BE4" s="6"/>
       <c r="BF4" s="6"/>
@@ -2147,284 +2159,284 @@
     </row>
     <row r="5" spans="1:87" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="F5" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G5" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="O5" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="X5" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="Y5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AB5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AD5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AE5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AF5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG5" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="AH5" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="AI5" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="AJ5" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK5" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="AL5" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="AM5" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="G5" s="35" t="s">
+      <c r="AN5" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="AO5" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="AP5" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="AQ5" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR5" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS5" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="AT5" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="AU5" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="AV5" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="AW5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="AX5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="AY5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="AZ5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="BA5" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="BB5" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="BC5" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="BD5" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="BE5" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="BF5" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="BG5" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="BH5" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="BI5" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="BJ5" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="BK5" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="BL5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="BM5" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="BN5" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO5" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="BP5" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="BQ5" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="BR5" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="BS5" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="BT5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="BU5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="BV5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="BW5" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="BX5" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="BY5" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ5" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="CA5" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="CB5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="CC5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="CD5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="CE5" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="CF5" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="CG5" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="M5" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="N5" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="O5" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="W5" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="X5" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y5" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z5" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AA5" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AB5" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AC5" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AD5" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="AE5" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="AF5" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="AG5" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="AH5" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="AI5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ5" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="AK5" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="AL5" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="AM5" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="AN5" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="AO5" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="AP5" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="AQ5" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="AR5" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="AS5" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="AT5" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="AU5" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="AV5" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="AW5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="AX5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="AY5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="AZ5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="BA5" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="BB5" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="BC5" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="BD5" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="BE5" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="BF5" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="BG5" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="BH5" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="BI5" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="BJ5" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="BK5" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="BL5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="BM5" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="BN5" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="BO5" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="BP5" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="BQ5" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="BR5" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="BS5" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="BT5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="BU5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="BV5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="BW5" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="BX5" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="BY5" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="BZ5" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="CA5" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="CB5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="CC5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="CD5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="CE5" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="CF5" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="CG5" s="24" t="s">
-        <v>138</v>
-      </c>
       <c r="CH5" s="24" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="CI5" s="24" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:87" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -2437,7 +2449,7 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
@@ -2451,13 +2463,13 @@
       <c r="AB6" s="2"/>
       <c r="AC6" s="2"/>
       <c r="AD6" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="AE6" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="AF6" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="AE6" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="AF6" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="AG6" s="21"/>
       <c r="AH6" s="21"/>
@@ -2471,7 +2483,7 @@
       <c r="AP6" s="21"/>
       <c r="AQ6" s="21"/>
       <c r="AR6" s="21" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AS6" s="21"/>
       <c r="AT6" s="3"/>
@@ -2483,7 +2495,9 @@
       <c r="AZ6" s="6"/>
       <c r="BA6" s="6"/>
       <c r="BB6" s="6"/>
-      <c r="BC6" s="6"/>
+      <c r="BC6" s="39" t="s">
+        <v>276</v>
+      </c>
       <c r="BD6" s="6"/>
       <c r="BE6" s="6"/>
       <c r="BF6" s="6"/>
@@ -2494,17 +2508,17 @@
       <c r="BK6" s="6"/>
       <c r="BL6" s="6"/>
       <c r="BM6" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="BN6" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="BO6" s="6"/>
       <c r="BP6" s="6"/>
       <c r="BQ6" s="6"/>
       <c r="BR6" s="6"/>
       <c r="BS6" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="BT6" s="6"/>
       <c r="BU6" s="6"/>
@@ -2513,16 +2527,16 @@
       <c r="BX6" s="6"/>
       <c r="BY6" s="6"/>
       <c r="BZ6" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="CA6" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="CB6" s="6"/>
       <c r="CC6" s="6"/>
       <c r="CD6" s="6"/>
       <c r="CE6" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="CF6" s="24"/>
       <c r="CG6" s="24"/>
@@ -2531,329 +2545,329 @@
     </row>
     <row r="7" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="D7" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="G7" s="35" t="s">
+        <v>271</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="I7" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="G7" s="35" t="s">
-        <v>274</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="J7" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="K7" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="L7" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="M7" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="N7" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="O7" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="P7" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="O7" s="12" t="s">
+      <c r="Q7" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="P7" s="26" t="s">
+      <c r="R7" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="Q7" s="26" t="s">
+      <c r="S7" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="R7" s="26" t="s">
+      <c r="T7" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="X7" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="Y7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="Z7" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="Y7" s="2" t="s">
+      <c r="AA7" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="Z7" s="26" t="s">
+      <c r="AB7" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="AA7" s="26" t="s">
+      <c r="AC7" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="AB7" s="26" t="s">
+      <c r="AD7" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="AC7" s="2" t="s">
+      <c r="AE7" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="AD7" s="2" t="s">
+      <c r="AF7" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="AE7" s="26" t="s">
+      <c r="AG7" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="AF7" s="2" t="s">
+      <c r="AH7" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="AG7" s="27" t="s">
+      <c r="AI7" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="AH7" s="27" t="s">
+      <c r="AJ7" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="AI7" s="27" t="s">
+      <c r="AK7" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="AJ7" s="27" t="s">
+      <c r="AL7" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="AK7" s="27" t="s">
+      <c r="AM7" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="AL7" s="27" t="s">
+      <c r="AN7" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="AM7" s="27" t="s">
+      <c r="AO7" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="AN7" s="27" t="s">
+      <c r="AP7" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="AO7" s="27" t="s">
+      <c r="AQ7" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="AP7" s="27" t="s">
+      <c r="AR7" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="AQ7" s="27" t="s">
+      <c r="AS7" s="27" t="s">
         <v>198</v>
       </c>
-      <c r="AR7" s="27" t="s">
+      <c r="AT7" s="30" t="s">
         <v>199</v>
       </c>
-      <c r="AS7" s="27" t="s">
+      <c r="AU7" s="30" t="s">
         <v>200</v>
       </c>
-      <c r="AT7" s="30" t="s">
+      <c r="AV7" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="AU7" s="30" t="s">
+      <c r="AW7" s="30" t="s">
         <v>202</v>
       </c>
-      <c r="AV7" s="30" t="s">
+      <c r="AX7" s="30" t="s">
         <v>203</v>
       </c>
-      <c r="AW7" s="30" t="s">
+      <c r="AY7" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="AX7" s="30" t="s">
+      <c r="AZ7" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="AY7" s="6" t="s">
+      <c r="BA7" s="30" t="s">
         <v>206</v>
       </c>
-      <c r="AZ7" s="6" t="s">
+      <c r="BB7" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="BA7" s="30" t="s">
+      <c r="BC7" s="40" t="s">
+        <v>277</v>
+      </c>
+      <c r="BD7" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="BB7" s="30" t="s">
+      <c r="BE7" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="BF7" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="BC7" s="30" t="s">
+      <c r="BG7" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="BD7" s="30" t="s">
+      <c r="BH7" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="BE7" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="BF7" s="30" t="s">
+      <c r="BI7" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="BG7" s="30" t="s">
+      <c r="BJ7" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="BH7" s="30" t="s">
+      <c r="BK7" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="BI7" s="30" t="s">
+      <c r="BL7" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="BJ7" s="30" t="s">
+      <c r="BM7" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="BK7" s="30" t="s">
+      <c r="BN7" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="BL7" s="6" t="s">
+      <c r="BO7" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="BM7" s="6" t="s">
+      <c r="BP7" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="BN7" s="6" t="s">
+      <c r="BQ7" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="BO7" s="6" t="s">
+      <c r="BR7" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="BP7" s="6" t="s">
+      <c r="BS7" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="BQ7" s="6" t="s">
+      <c r="BT7" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="BR7" s="6" t="s">
+      <c r="BU7" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="BS7" s="6" t="s">
+      <c r="BV7" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="BT7" s="6" t="s">
+      <c r="BW7" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="BU7" s="6" t="s">
+      <c r="BX7" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="BV7" s="6" t="s">
+      <c r="BY7" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="BW7" s="6" t="s">
+      <c r="BZ7" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="BX7" s="6" t="s">
+      <c r="CA7" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="BY7" s="6" t="s">
+      <c r="CB7" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="BZ7" s="28" t="s">
+      <c r="CC7" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="CA7" s="6" t="s">
+      <c r="CD7" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="CB7" s="6" t="s">
+      <c r="CE7" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="CC7" s="6" t="s">
+      <c r="CF7" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="CD7" s="6" t="s">
+      <c r="CG7" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="CE7" s="6" t="s">
+      <c r="CH7" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="CF7" s="30" t="s">
+      <c r="CI7" s="30" t="s">
         <v>238</v>
-      </c>
-      <c r="CG7" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="CH7" s="30" t="s">
-        <v>240</v>
-      </c>
-      <c r="CI7" s="30" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>240</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="D8" t="s">
+        <v>262</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="F8" s="30" t="s">
         <v>242</v>
       </c>
-      <c r="B8" s="29" t="s">
-        <v>243</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>244</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="G8" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="H8" t="s">
         <v>265</v>
       </c>
-      <c r="E8" s="30" t="s">
-        <v>264</v>
-      </c>
-      <c r="F8" s="30" t="s">
-        <v>245</v>
-      </c>
-      <c r="G8" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="H8" t="s">
-        <v>268</v>
-      </c>
       <c r="I8" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="J8" s="30"/>
       <c r="K8" s="30" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="L8" s="30" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="M8" s="30" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="N8" s="30" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="O8" s="30" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="P8" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q8" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="R8" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="S8" s="30" t="s">
         <v>246</v>
-      </c>
-      <c r="Q8" s="30" t="s">
-        <v>247</v>
-      </c>
-      <c r="R8" s="30" t="s">
-        <v>263</v>
-      </c>
-      <c r="S8" s="30" t="s">
-        <v>249</v>
       </c>
       <c r="T8" s="31"/>
       <c r="U8" s="31"/>
       <c r="V8" s="32"/>
       <c r="W8" s="32"/>
       <c r="X8" s="30" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="Y8" s="32"/>
       <c r="Z8" s="31">
@@ -2861,22 +2875,22 @@
       </c>
       <c r="AA8" s="31"/>
       <c r="AB8" s="31" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AC8" s="31"/>
       <c r="AD8" s="30" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AE8" s="30" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AF8" s="30" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AG8" s="30"/>
       <c r="AH8" s="30"/>
       <c r="AI8" s="30" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AJ8" s="30"/>
       <c r="AK8" s="30"/>
@@ -2886,41 +2900,41 @@
       <c r="AO8" s="30"/>
       <c r="AP8" s="30"/>
       <c r="AQ8" s="30" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AR8" s="30" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AS8" s="30" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AT8" s="30"/>
       <c r="AU8" s="30"/>
       <c r="AV8" s="30"/>
       <c r="AW8" s="30"/>
       <c r="AX8" s="30" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AY8" s="31"/>
       <c r="AZ8" s="31"/>
       <c r="BA8" s="30" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="BB8" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="BC8" s="30" t="s">
-        <v>252</v>
+        <v>249</v>
+      </c>
+      <c r="BC8" s="40" t="s">
+        <v>278</v>
       </c>
       <c r="BD8" s="30" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BE8" s="33"/>
       <c r="BF8" s="31">
         <v>3</v>
       </c>
       <c r="BG8" s="30" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="BH8" s="31">
         <v>70</v>
@@ -2934,21 +2948,21 @@
       <c r="BK8" s="30"/>
       <c r="BL8" s="33"/>
       <c r="BM8" s="30" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="BN8" s="30" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="BO8" s="30" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="BP8" s="33"/>
       <c r="BQ8" s="30" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="BR8" s="33"/>
       <c r="BS8" s="30" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="BT8" s="33"/>
       <c r="BU8" s="33"/>
@@ -2957,19 +2971,19 @@
       <c r="BX8" s="33"/>
       <c r="BY8" s="33"/>
       <c r="BZ8" s="30" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="CA8" s="30" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="CB8" s="30"/>
       <c r="CC8" s="33"/>
       <c r="CD8" s="33"/>
       <c r="CE8" s="30" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="CF8" s="30" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="CG8" s="30"/>
       <c r="CH8" s="30"/>
@@ -2978,14 +2992,14 @@
     <row r="9" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="C9" s="30" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D9" s="34"/>
       <c r="E9" s="30" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G9" s="30"/>
       <c r="J9" s="30"/>
@@ -2995,16 +3009,16 @@
       <c r="N9" s="30"/>
       <c r="O9" s="30"/>
       <c r="P9" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="S9" s="30" t="s">
         <v>246</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>247</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>248</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>249</v>
       </c>
       <c r="T9" s="31"/>
       <c r="U9" s="31"/>
@@ -3024,7 +3038,7 @@
       <c r="AC9" s="31"/>
       <c r="AD9" s="31"/>
       <c r="AE9" s="30" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AF9" s="31"/>
       <c r="AG9" s="30"/>
@@ -3040,14 +3054,14 @@
       <c r="AQ9" s="30"/>
       <c r="AR9" s="30"/>
       <c r="AS9" s="30" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AT9" s="30"/>
       <c r="AU9" s="30"/>
       <c r="AV9" s="30"/>
       <c r="AW9" s="30"/>
       <c r="AX9" s="30" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AY9" s="31"/>
       <c r="AZ9" s="31"/>
@@ -3055,13 +3069,13 @@
         <v>0.200098</v>
       </c>
       <c r="BB9" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="BC9" s="30" t="s">
-        <v>252</v>
+        <v>249</v>
+      </c>
+      <c r="BC9" s="40" t="s">
+        <v>278</v>
       </c>
       <c r="BD9" s="30" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BE9" s="34"/>
       <c r="BF9" s="31">
@@ -3101,7 +3115,7 @@
       <c r="CD9" s="34"/>
       <c r="CE9" s="34"/>
       <c r="CF9" s="30" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="CG9" s="30"/>
       <c r="CH9" s="30"/>
@@ -3110,38 +3124,38 @@
     <row r="10" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
       <c r="C10" s="30" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D10" s="34"/>
       <c r="E10" s="30"/>
       <c r="F10" s="30" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G10" s="30" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I10" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="J10" s="30"/>
       <c r="K10" s="30" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="L10" s="30"/>
       <c r="M10" s="30"/>
       <c r="N10" s="30"/>
       <c r="O10" s="30"/>
       <c r="P10" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q10" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="R10" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="S10" s="30" t="s">
         <v>246</v>
-      </c>
-      <c r="Q10" s="30" t="s">
-        <v>247</v>
-      </c>
-      <c r="R10" s="30" t="s">
-        <v>248</v>
-      </c>
-      <c r="S10" s="30" t="s">
-        <v>249</v>
       </c>
       <c r="T10" s="31"/>
       <c r="U10" s="31"/>
@@ -3161,7 +3175,7 @@
       <c r="AC10" s="31"/>
       <c r="AD10" s="31"/>
       <c r="AE10" s="30" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AF10" s="31"/>
       <c r="AG10" s="30"/>
@@ -3177,14 +3191,14 @@
       <c r="AQ10" s="30"/>
       <c r="AR10" s="30"/>
       <c r="AS10" s="30" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AT10" s="30"/>
       <c r="AU10" s="30"/>
       <c r="AV10" s="30"/>
       <c r="AW10" s="30"/>
       <c r="AX10" s="30" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AY10" s="31"/>
       <c r="AZ10" s="31"/>
@@ -3192,13 +3206,13 @@
         <v>0.200098</v>
       </c>
       <c r="BB10" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="BC10" s="30" t="s">
-        <v>252</v>
+        <v>249</v>
+      </c>
+      <c r="BC10" s="40" t="s">
+        <v>278</v>
       </c>
       <c r="BD10" s="30" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BE10" s="34"/>
       <c r="BF10" s="31">
@@ -3238,7 +3252,7 @@
       <c r="CD10" s="34"/>
       <c r="CE10" s="34"/>
       <c r="CF10" s="30" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="CG10" s="30"/>
       <c r="CH10" s="30"/>
@@ -3246,24 +3260,24 @@
     </row>
     <row r="11" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="C11" s="30" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D11" s="34"/>
       <c r="E11" s="30" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G11" s="30" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H11" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I11" s="34"/>
       <c r="J11" s="30" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="K11" s="30"/>
       <c r="L11" s="30"/>
@@ -3271,16 +3285,16 @@
       <c r="N11" s="30"/>
       <c r="O11" s="30"/>
       <c r="P11" s="30" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="Q11" s="30" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="R11" s="30" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="S11" s="30" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="T11" s="31"/>
       <c r="U11" s="31"/>
@@ -3300,7 +3314,7 @@
       <c r="AC11" s="31"/>
       <c r="AD11" s="31"/>
       <c r="AE11" s="30" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AF11" s="31"/>
       <c r="AG11" s="30"/>
@@ -3316,14 +3330,14 @@
       <c r="AQ11" s="30"/>
       <c r="AR11" s="30"/>
       <c r="AS11" s="30" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AT11" s="30"/>
       <c r="AU11" s="30"/>
       <c r="AV11" s="30"/>
       <c r="AW11" s="30"/>
       <c r="AX11" s="30" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AY11" s="31"/>
       <c r="AZ11" s="31"/>
@@ -3331,13 +3345,13 @@
         <v>0.200098</v>
       </c>
       <c r="BB11" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="BC11" s="30" t="s">
-        <v>252</v>
+        <v>249</v>
+      </c>
+      <c r="BC11" s="40" t="s">
+        <v>278</v>
       </c>
       <c r="BD11" s="30" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BE11" s="34"/>
       <c r="BF11" s="31">
@@ -3377,7 +3391,7 @@
       <c r="CD11" s="34"/>
       <c r="CE11" s="34"/>
       <c r="CF11" s="30" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="CG11" s="30"/>
       <c r="CH11" s="30"/>
@@ -3385,20 +3399,20 @@
     </row>
     <row r="12" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="C12" s="30" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D12" s="34"/>
       <c r="E12" s="30" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F12" s="30" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="G12" s="30" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H12" s="30" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="I12" s="34"/>
       <c r="J12" s="30"/>
@@ -3408,16 +3422,16 @@
       <c r="N12" s="30"/>
       <c r="O12" s="30"/>
       <c r="P12" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q12" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="R12" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="S12" s="30" t="s">
         <v>246</v>
-      </c>
-      <c r="Q12" s="30" t="s">
-        <v>247</v>
-      </c>
-      <c r="R12" s="30" t="s">
-        <v>248</v>
-      </c>
-      <c r="S12" s="30" t="s">
-        <v>249</v>
       </c>
       <c r="T12" s="31"/>
       <c r="U12" s="31"/>
@@ -3437,7 +3451,7 @@
       <c r="AC12" s="31"/>
       <c r="AD12" s="31"/>
       <c r="AE12" s="30" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AF12" s="31"/>
       <c r="AG12" s="30"/>
@@ -3453,14 +3467,14 @@
       <c r="AQ12" s="30"/>
       <c r="AR12" s="30"/>
       <c r="AS12" s="30" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AT12" s="30"/>
       <c r="AU12" s="30"/>
       <c r="AV12" s="30"/>
       <c r="AW12" s="30"/>
       <c r="AX12" s="30" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AY12" s="31"/>
       <c r="AZ12" s="31"/>
@@ -3468,13 +3482,13 @@
         <v>0.200098</v>
       </c>
       <c r="BB12" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="BC12" s="30" t="s">
-        <v>252</v>
+        <v>249</v>
+      </c>
+      <c r="BC12" s="40" t="s">
+        <v>278</v>
       </c>
       <c r="BD12" s="30" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BE12" s="34"/>
       <c r="BF12" s="31">
@@ -3514,7 +3528,7 @@
       <c r="CD12" s="34"/>
       <c r="CE12" s="34"/>
       <c r="CF12" s="30" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="CG12" s="30"/>
       <c r="CH12" s="30"/>
@@ -3522,15 +3536,15 @@
     </row>
     <row r="13" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="C13" s="30" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D13" s="34"/>
       <c r="E13" s="30" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F13" s="30"/>
       <c r="G13" s="30" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H13" s="34"/>
       <c r="I13" s="34"/>
@@ -3541,16 +3555,16 @@
       <c r="N13" s="30"/>
       <c r="O13" s="30"/>
       <c r="P13" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q13" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="R13" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="S13" s="30" t="s">
         <v>246</v>
-      </c>
-      <c r="Q13" s="30" t="s">
-        <v>247</v>
-      </c>
-      <c r="R13" s="30" t="s">
-        <v>248</v>
-      </c>
-      <c r="S13" s="30" t="s">
-        <v>249</v>
       </c>
       <c r="T13" s="31"/>
       <c r="U13" s="31"/>
@@ -3570,7 +3584,7 @@
       <c r="AC13" s="31"/>
       <c r="AD13" s="31"/>
       <c r="AE13" s="30" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AF13" s="31"/>
       <c r="AG13" s="30"/>
@@ -3586,14 +3600,14 @@
       <c r="AQ13" s="30"/>
       <c r="AR13" s="30"/>
       <c r="AS13" s="30" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AT13" s="30"/>
       <c r="AU13" s="30"/>
       <c r="AV13" s="30"/>
       <c r="AW13" s="30"/>
       <c r="AX13" s="30" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AY13" s="31"/>
       <c r="AZ13" s="31"/>
@@ -3601,13 +3615,13 @@
         <v>0.200098</v>
       </c>
       <c r="BB13" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="BC13" s="30" t="s">
-        <v>252</v>
+        <v>249</v>
+      </c>
+      <c r="BC13" s="40" t="s">
+        <v>278</v>
       </c>
       <c r="BD13" s="30" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BE13" s="34"/>
       <c r="BF13" s="31">
@@ -3647,7 +3661,7 @@
       <c r="CD13" s="34"/>
       <c r="CE13" s="34"/>
       <c r="CF13" s="30" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="CG13" s="30"/>
       <c r="CH13" s="30"/>
@@ -3655,20 +3669,20 @@
     </row>
     <row r="14" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="C14" s="30" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D14" s="34"/>
       <c r="E14" s="30" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="G14" s="30" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H14" s="30" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="I14" s="34"/>
       <c r="J14" s="30"/>
@@ -3678,16 +3692,16 @@
       <c r="N14" s="30"/>
       <c r="O14" s="30"/>
       <c r="P14" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q14" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="R14" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="S14" s="30" t="s">
         <v>246</v>
-      </c>
-      <c r="Q14" s="30" t="s">
-        <v>247</v>
-      </c>
-      <c r="R14" s="30" t="s">
-        <v>248</v>
-      </c>
-      <c r="S14" s="30" t="s">
-        <v>249</v>
       </c>
       <c r="T14" s="31"/>
       <c r="U14" s="31"/>
@@ -3707,7 +3721,7 @@
       <c r="AC14" s="31"/>
       <c r="AD14" s="31"/>
       <c r="AE14" s="30" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AF14" s="31"/>
       <c r="AG14" s="30"/>
@@ -3723,14 +3737,14 @@
       <c r="AQ14" s="30"/>
       <c r="AR14" s="30"/>
       <c r="AS14" s="30" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AT14" s="30"/>
       <c r="AU14" s="30"/>
       <c r="AV14" s="30"/>
       <c r="AW14" s="30"/>
       <c r="AX14" s="30" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AY14" s="31"/>
       <c r="AZ14" s="31"/>
@@ -3738,13 +3752,13 @@
         <v>0.200098</v>
       </c>
       <c r="BB14" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="BC14" s="30" t="s">
-        <v>252</v>
+        <v>249</v>
+      </c>
+      <c r="BC14" s="40" t="s">
+        <v>279</v>
       </c>
       <c r="BD14" s="30" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BE14" s="34"/>
       <c r="BF14" s="31">
@@ -3784,11 +3798,17 @@
       <c r="CD14" s="34"/>
       <c r="CE14" s="34"/>
       <c r="CF14" s="30" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="CG14" s="30"/>
       <c r="CH14" s="30"/>
       <c r="CI14" s="30"/>
+    </row>
+    <row r="15" spans="1:87" ht="16" x14ac:dyDescent="0.2">
+      <c r="BC15" s="40"/>
+    </row>
+    <row r="16" spans="1:87" ht="16" x14ac:dyDescent="0.2">
+      <c r="BC16" s="40"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/spec/fixtures/batch_submission_manifest_errors_test.xlsx
+++ b/spec/fixtures/batch_submission_manifest_errors_test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10410"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smc101/vagrant/morphosource-vagrant/MorphoSource_SF/spec/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{968B21FD-ED57-5448-A073-99A1BE32390E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{964F9C63-CED3-FC41-981A-FC7CB77FE7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="32000" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="278">
   <si>
     <t>Field Section</t>
   </si>
@@ -917,6 +917,9 @@
   </si>
   <si>
     <t>INVALID</t>
+  </si>
+  <si>
+    <t>not#valid</t>
   </si>
 </sst>
 </file>
@@ -2831,7 +2834,9 @@
       <c r="S8" s="30"/>
       <c r="T8" s="30"/>
       <c r="U8" s="31"/>
-      <c r="V8" s="31"/>
+      <c r="V8" s="31" t="s">
+        <v>277</v>
+      </c>
       <c r="W8" s="29" t="s">
         <v>258</v>
       </c>

--- a/spec/fixtures/batch_submission_manifest_errors_test.xlsx
+++ b/spec/fixtures/batch_submission_manifest_errors_test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10212"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smc101/vagrant/morphosource-vagrant/MorphoSource_SF/spec/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{964F9C63-CED3-FC41-981A-FC7CB77FE7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5FD756C-A380-0C4E-9646-2FC415B6D80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="32000" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="277">
   <si>
     <t>Field Section</t>
   </si>
@@ -797,12 +797,6 @@
     <t>processing_event.description</t>
   </si>
   <si>
-    <t>Field Values for Deposit, 1 Row per Deposit</t>
-  </si>
-  <si>
-    <t>Each row from this point of the spreadsheet represents a single media deposit. Values in each column will represent values for the field indicated by the column.</t>
-  </si>
-  <si>
     <t>ANSP_Fish_53046_Head.zip</t>
   </si>
   <si>
@@ -920,13 +914,16 @@
   </si>
   <si>
     <t>not#valid</t>
+  </si>
+  <si>
+    <t>https://www.morphosource.org/banner_image.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -971,6 +968,18 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="13">
@@ -1056,17 +1065,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+  <cellXfs count="36">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1079,16 +1089,14 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1098,33 +1106,31 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1338,10 +1344,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06ED7EC9-286B-1D49-A57D-A989376D77CC}">
-  <dimension ref="A1:CH16"/>
+  <dimension ref="A1:CH15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="54" max="54" width="18.1640625" style="40" customWidth="1"/>
+    <col min="3" max="3" width="47.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:86" x14ac:dyDescent="0.15">
@@ -1360,7 +1368,7 @@
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="31" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="5" t="s">
@@ -1436,43 +1444,43 @@
       <c r="AE1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AF1" s="20" t="s">
+      <c r="AF1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AG1" s="20" t="s">
+      <c r="AG1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AH1" s="20" t="s">
+      <c r="AH1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AI1" s="20" t="s">
+      <c r="AI1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AJ1" s="20" t="s">
+      <c r="AJ1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AK1" s="20" t="s">
+      <c r="AK1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="20" t="s">
+      <c r="AL1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AM1" s="20" t="s">
+      <c r="AM1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AN1" s="20" t="s">
+      <c r="AN1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AO1" s="20" t="s">
+      <c r="AO1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AP1" s="20" t="s">
+      <c r="AP1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AQ1" s="20" t="s">
+      <c r="AQ1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AR1" s="20" t="s">
+      <c r="AR1" s="14" t="s">
         <v>8</v>
       </c>
       <c r="AS1" s="3" t="s">
@@ -1502,7 +1510,7 @@
       <c r="BA1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="BB1" s="37" t="s">
+      <c r="BB1" s="6" t="s">
         <v>11</v>
       </c>
       <c r="BC1" s="6" t="s">
@@ -1589,16 +1597,16 @@
       <c r="CD1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="CE1" s="23" t="s">
+      <c r="CE1" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="CF1" s="23" t="s">
+      <c r="CF1" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="CG1" s="23" t="s">
+      <c r="CG1" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="CH1" s="23" t="s">
+      <c r="CH1" s="20" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1612,7 +1620,7 @@
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="35"/>
+      <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="11" t="s">
@@ -1674,43 +1682,43 @@
       <c r="AE2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AF2" s="20" t="s">
+      <c r="AF2" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="AG2" s="20" t="s">
+      <c r="AG2" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="AH2" s="20" t="s">
+      <c r="AH2" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="AI2" s="20" t="s">
+      <c r="AI2" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="AJ2" s="20" t="s">
+      <c r="AJ2" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="AK2" s="20" t="s">
+      <c r="AK2" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="AL2" s="20" t="s">
+      <c r="AL2" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="AM2" s="20" t="s">
+      <c r="AM2" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="AN2" s="20" t="s">
+      <c r="AN2" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="AO2" s="20" t="s">
+      <c r="AO2" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="AP2" s="20" t="s">
+      <c r="AP2" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="AQ2" s="20" t="s">
+      <c r="AQ2" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="AR2" s="20" t="s">
+      <c r="AR2" s="14" t="s">
         <v>47</v>
       </c>
       <c r="AS2" s="3" t="s">
@@ -1740,14 +1748,14 @@
       <c r="BA2" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="BB2" s="37" t="s">
-        <v>272</v>
+      <c r="BB2" s="6" t="s">
+        <v>270</v>
       </c>
       <c r="BC2" s="6" t="s">
         <v>54</v>
       </c>
       <c r="BD2" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="BE2" s="6" t="s">
         <v>55</v>
@@ -1827,16 +1835,16 @@
       <c r="CD2" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="CE2" s="23" t="s">
+      <c r="CE2" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="CF2" s="23" t="s">
+      <c r="CF2" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="CG2" s="23" t="s">
+      <c r="CG2" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="CH2" s="23" t="s">
+      <c r="CH2" s="20" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1854,8 +1862,8 @@
         <v>84</v>
       </c>
       <c r="E3" s="9"/>
-      <c r="F3" s="36" t="s">
-        <v>266</v>
+      <c r="F3" s="32" t="s">
+        <v>264</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>85</v>
@@ -1876,8 +1884,8 @@
       <c r="O3" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
       <c r="R3" s="12" t="s">
         <v>90</v>
       </c>
@@ -1891,13 +1899,13 @@
       <c r="V3" s="12"/>
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
-      <c r="Y3" s="14" t="s">
+      <c r="Y3" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z3" s="14" t="s">
+      <c r="Z3" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="AA3" s="14" t="s">
+      <c r="AA3" s="13" t="s">
         <v>95</v>
       </c>
       <c r="AB3" s="12" t="s">
@@ -1906,123 +1914,123 @@
       <c r="AC3" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="AD3" s="13"/>
+      <c r="AD3" s="2"/>
       <c r="AE3" s="2"/>
-      <c r="AF3" s="20"/>
-      <c r="AG3" s="20"/>
-      <c r="AH3" s="20"/>
-      <c r="AI3" s="20"/>
-      <c r="AJ3" s="15"/>
-      <c r="AK3" s="15"/>
-      <c r="AL3" s="15"/>
-      <c r="AM3" s="15"/>
-      <c r="AN3" s="15"/>
-      <c r="AO3" s="15"/>
-      <c r="AP3" s="15"/>
-      <c r="AQ3" s="15"/>
-      <c r="AR3" s="20" t="s">
+      <c r="AF3" s="14"/>
+      <c r="AG3" s="14"/>
+      <c r="AH3" s="14"/>
+      <c r="AI3" s="14"/>
+      <c r="AJ3" s="14"/>
+      <c r="AK3" s="14"/>
+      <c r="AL3" s="14"/>
+      <c r="AM3" s="14"/>
+      <c r="AN3" s="14"/>
+      <c r="AO3" s="14"/>
+      <c r="AP3" s="14"/>
+      <c r="AQ3" s="14"/>
+      <c r="AR3" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="AS3" s="16"/>
-      <c r="AT3" s="16"/>
-      <c r="AU3" s="16"/>
+      <c r="AS3" s="3"/>
+      <c r="AT3" s="3"/>
+      <c r="AU3" s="3"/>
       <c r="AV3" s="6"/>
       <c r="AW3" s="6"/>
-      <c r="AX3" s="17" t="s">
+      <c r="AX3" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="AY3" s="17"/>
-      <c r="AZ3" s="18" t="s">
+      <c r="AY3" s="15"/>
+      <c r="AZ3" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="BA3" s="18" t="s">
+      <c r="BA3" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="BB3" s="18"/>
-      <c r="BC3" s="18" t="s">
+      <c r="BB3" s="16"/>
+      <c r="BC3" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="BD3" s="18" t="s">
+      <c r="BD3" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="BE3" s="18" t="s">
+      <c r="BE3" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="BF3" s="18" t="s">
+      <c r="BF3" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="BG3" s="18" t="s">
+      <c r="BG3" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="BH3" s="18" t="s">
+      <c r="BH3" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="BI3" s="18" t="s">
+      <c r="BI3" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="BJ3" s="18" t="s">
+      <c r="BJ3" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="BK3" s="17" t="s">
+      <c r="BK3" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="BL3" s="17"/>
-      <c r="BM3" s="17" t="s">
+      <c r="BL3" s="15"/>
+      <c r="BM3" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="BN3" s="19" t="s">
+      <c r="BN3" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="BO3" s="19" t="s">
+      <c r="BO3" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="BP3" s="19" t="s">
+      <c r="BP3" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="BQ3" s="19" t="s">
+      <c r="BQ3" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="BR3" s="17" t="s">
+      <c r="BR3" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="BS3" s="17" t="s">
+      <c r="BS3" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="BT3" s="17" t="s">
+      <c r="BT3" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="BU3" s="17" t="s">
+      <c r="BU3" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="BV3" s="17" t="s">
+      <c r="BV3" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="BW3" s="17" t="s">
+      <c r="BW3" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="BX3" s="17" t="s">
+      <c r="BX3" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="BY3" s="18"/>
-      <c r="BZ3" s="17" t="s">
+      <c r="BY3" s="16"/>
+      <c r="BZ3" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="CA3" s="17" t="s">
+      <c r="CA3" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="CB3" s="17" t="s">
+      <c r="CB3" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="CC3" s="17" t="s">
+      <c r="CC3" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="CD3" s="18" t="s">
+      <c r="CD3" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="CE3" s="23"/>
-      <c r="CF3" s="23"/>
-      <c r="CG3" s="23"/>
-      <c r="CH3" s="23"/>
+      <c r="CE3" s="20"/>
+      <c r="CF3" s="20"/>
+      <c r="CG3" s="20"/>
+      <c r="CH3" s="20"/>
     </row>
     <row r="4" spans="1:86" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
@@ -2038,7 +2046,7 @@
       <c r="E4" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="31" t="s">
         <v>129</v>
       </c>
       <c r="G4" s="5"/>
@@ -2060,8 +2068,8 @@
       <c r="O4" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
@@ -2080,31 +2088,31 @@
       </c>
       <c r="AB4" s="2"/>
       <c r="AC4" s="2"/>
-      <c r="AD4" s="13"/>
+      <c r="AD4" s="2"/>
       <c r="AE4" s="2"/>
-      <c r="AF4" s="15"/>
-      <c r="AG4" s="15"/>
-      <c r="AH4" s="15"/>
-      <c r="AI4" s="15"/>
-      <c r="AJ4" s="15"/>
-      <c r="AK4" s="15"/>
-      <c r="AL4" s="15"/>
-      <c r="AM4" s="15"/>
-      <c r="AN4" s="15"/>
-      <c r="AO4" s="15"/>
-      <c r="AP4" s="15"/>
-      <c r="AQ4" s="15"/>
-      <c r="AR4" s="15"/>
-      <c r="AS4" s="16"/>
-      <c r="AT4" s="16"/>
-      <c r="AU4" s="16"/>
+      <c r="AF4" s="14"/>
+      <c r="AG4" s="14"/>
+      <c r="AH4" s="14"/>
+      <c r="AI4" s="14"/>
+      <c r="AJ4" s="14"/>
+      <c r="AK4" s="14"/>
+      <c r="AL4" s="14"/>
+      <c r="AM4" s="14"/>
+      <c r="AN4" s="14"/>
+      <c r="AO4" s="14"/>
+      <c r="AP4" s="14"/>
+      <c r="AQ4" s="14"/>
+      <c r="AR4" s="14"/>
+      <c r="AS4" s="3"/>
+      <c r="AT4" s="3"/>
+      <c r="AU4" s="3"/>
       <c r="AV4" s="6"/>
       <c r="AW4" s="6"/>
       <c r="AX4" s="6"/>
       <c r="AY4" s="6"/>
       <c r="AZ4" s="6"/>
       <c r="BA4" s="6"/>
-      <c r="BB4" s="37"/>
+      <c r="BB4" s="6"/>
       <c r="BC4" s="6"/>
       <c r="BD4" s="6"/>
       <c r="BE4" s="6"/>
@@ -2133,10 +2141,10 @@
       <c r="CB4" s="6"/>
       <c r="CC4" s="6"/>
       <c r="CD4" s="6"/>
-      <c r="CE4" s="23"/>
-      <c r="CF4" s="23"/>
-      <c r="CG4" s="23"/>
-      <c r="CH4" s="23"/>
+      <c r="CE4" s="20"/>
+      <c r="CF4" s="20"/>
+      <c r="CG4" s="20"/>
+      <c r="CH4" s="20"/>
     </row>
     <row r="5" spans="1:86" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
@@ -2154,7 +2162,7 @@
       <c r="E5" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="31" t="s">
         <v>135</v>
       </c>
       <c r="G5" s="5" t="s">
@@ -2232,43 +2240,43 @@
       <c r="AE5" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AF5" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="AG5" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="AH5" s="20" t="s">
+      <c r="AF5" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="AG5" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="AH5" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="AI5" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="AJ5" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK5" s="20" t="s">
+      <c r="AI5" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="AJ5" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK5" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="AL5" s="20" t="s">
+      <c r="AL5" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="AM5" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN5" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="AO5" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="AP5" s="20" t="s">
+      <c r="AM5" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN5" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="AO5" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="AP5" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="AQ5" s="20" t="s">
+      <c r="AQ5" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="AR5" s="20" t="s">
+      <c r="AR5" s="14" t="s">
         <v>138</v>
       </c>
       <c r="AS5" s="3" t="s">
@@ -2292,37 +2300,37 @@
       <c r="AY5" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="AZ5" s="21" t="s">
+      <c r="AZ5" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="BA5" s="21" t="s">
+      <c r="BA5" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="BB5" s="38" t="s">
+      <c r="BB5" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="BC5" s="21" t="s">
+      <c r="BC5" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="BD5" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="BE5" s="21" t="s">
+      <c r="BD5" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="BE5" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="BF5" s="21" t="s">
+      <c r="BF5" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="BG5" s="21" t="s">
+      <c r="BG5" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="BH5" s="21" t="s">
+      <c r="BH5" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="BI5" s="21" t="s">
+      <c r="BI5" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="BJ5" s="21" t="s">
+      <c r="BJ5" s="18" t="s">
         <v>134</v>
       </c>
       <c r="BK5" s="6" t="s">
@@ -2334,16 +2342,16 @@
       <c r="BM5" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="BN5" s="22" t="s">
+      <c r="BN5" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="BO5" s="22" t="s">
+      <c r="BO5" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="BP5" s="22" t="s">
+      <c r="BP5" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="BQ5" s="22" t="s">
+      <c r="BQ5" s="19" t="s">
         <v>137</v>
       </c>
       <c r="BR5" s="6" t="s">
@@ -2385,16 +2393,16 @@
       <c r="CD5" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="CE5" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="CF5" s="23" t="s">
+      <c r="CE5" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="CF5" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="CG5" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="CH5" s="23" t="s">
+      <c r="CG5" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="CH5" s="20" t="s">
         <v>134</v>
       </c>
     </row>
@@ -2410,8 +2418,8 @@
       <c r="E6" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="F6" s="34" t="s">
-        <v>267</v>
+      <c r="F6" s="31" t="s">
+        <v>265</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -2446,21 +2454,21 @@
       <c r="AE6" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="AF6" s="20"/>
-      <c r="AG6" s="20"/>
-      <c r="AH6" s="20"/>
-      <c r="AI6" s="20"/>
-      <c r="AJ6" s="20"/>
-      <c r="AK6" s="20"/>
-      <c r="AL6" s="20"/>
-      <c r="AM6" s="20"/>
-      <c r="AN6" s="20"/>
-      <c r="AO6" s="20"/>
-      <c r="AP6" s="20"/>
-      <c r="AQ6" s="20" t="s">
+      <c r="AF6" s="14"/>
+      <c r="AG6" s="14"/>
+      <c r="AH6" s="14"/>
+      <c r="AI6" s="14"/>
+      <c r="AJ6" s="14"/>
+      <c r="AK6" s="14"/>
+      <c r="AL6" s="14"/>
+      <c r="AM6" s="14"/>
+      <c r="AN6" s="14"/>
+      <c r="AO6" s="14"/>
+      <c r="AP6" s="14"/>
+      <c r="AQ6" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="AR6" s="20"/>
+      <c r="AR6" s="14"/>
       <c r="AS6" s="3"/>
       <c r="AT6" s="3"/>
       <c r="AU6" s="3"/>
@@ -2470,8 +2478,8 @@
       <c r="AY6" s="6"/>
       <c r="AZ6" s="6"/>
       <c r="BA6" s="6"/>
-      <c r="BB6" s="38" t="s">
-        <v>273</v>
+      <c r="BB6" s="33" t="s">
+        <v>271</v>
       </c>
       <c r="BC6" s="6"/>
       <c r="BD6" s="6"/>
@@ -2513,10 +2521,10 @@
       <c r="CD6" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="CE6" s="23"/>
-      <c r="CF6" s="23"/>
-      <c r="CG6" s="23"/>
-      <c r="CH6" s="23"/>
+      <c r="CE6" s="20"/>
+      <c r="CF6" s="20"/>
+      <c r="CG6" s="20"/>
+      <c r="CH6" s="20"/>
     </row>
     <row r="7" spans="1:86" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
@@ -2534,8 +2542,8 @@
       <c r="E7" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F7" s="34" t="s">
-        <v>268</v>
+      <c r="F7" s="31" t="s">
+        <v>266</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>159</v>
@@ -2543,7 +2551,7 @@
       <c r="H7" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="I7" s="24" t="s">
+      <c r="I7" s="21" t="s">
         <v>161</v>
       </c>
       <c r="J7" s="11" t="s">
@@ -2561,13 +2569,13 @@
       <c r="N7" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="O7" s="25" t="s">
+      <c r="O7" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="P7" s="25" t="s">
+      <c r="P7" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="Q7" s="25" t="s">
+      <c r="Q7" s="22" t="s">
         <v>169</v>
       </c>
       <c r="R7" s="2" t="s">
@@ -2591,13 +2599,13 @@
       <c r="X7" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="Y7" s="25" t="s">
+      <c r="Y7" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="Z7" s="25" t="s">
+      <c r="Z7" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="AA7" s="25" t="s">
+      <c r="AA7" s="22" t="s">
         <v>179</v>
       </c>
       <c r="AB7" s="2" t="s">
@@ -2606,64 +2614,64 @@
       <c r="AC7" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="AD7" s="25" t="s">
+      <c r="AD7" s="22" t="s">
         <v>182</v>
       </c>
       <c r="AE7" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="AF7" s="26" t="s">
+      <c r="AF7" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="AG7" s="26" t="s">
+      <c r="AG7" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="AH7" s="26" t="s">
+      <c r="AH7" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="AI7" s="26" t="s">
+      <c r="AI7" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="AJ7" s="26" t="s">
+      <c r="AJ7" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="AK7" s="26" t="s">
+      <c r="AK7" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="AL7" s="26" t="s">
+      <c r="AL7" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="AM7" s="26" t="s">
+      <c r="AM7" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="AN7" s="26" t="s">
+      <c r="AN7" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="AO7" s="26" t="s">
+      <c r="AO7" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="AP7" s="26" t="s">
+      <c r="AP7" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="AQ7" s="26" t="s">
+      <c r="AQ7" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="AR7" s="26" t="s">
+      <c r="AR7" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="AS7" s="29" t="s">
+      <c r="AS7" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="AT7" s="29" t="s">
+      <c r="AT7" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="AU7" s="29" t="s">
+      <c r="AU7" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="AV7" s="29" t="s">
+      <c r="AV7" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="AW7" s="29" t="s">
+      <c r="AW7" s="26" t="s">
         <v>201</v>
       </c>
       <c r="AX7" s="6" t="s">
@@ -2672,37 +2680,37 @@
       <c r="AY7" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="AZ7" s="29" t="s">
+      <c r="AZ7" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="BA7" s="29" t="s">
+      <c r="BA7" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="BB7" s="39" t="s">
-        <v>274</v>
-      </c>
-      <c r="BC7" s="29" t="s">
+      <c r="BB7" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="BC7" s="26" t="s">
         <v>206</v>
       </c>
       <c r="BD7" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="BE7" s="29" t="s">
+        <v>263</v>
+      </c>
+      <c r="BE7" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="BF7" s="29" t="s">
+      <c r="BF7" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="BG7" s="29" t="s">
+      <c r="BG7" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="BH7" s="29" t="s">
+      <c r="BH7" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="BI7" s="29" t="s">
+      <c r="BI7" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="BJ7" s="29" t="s">
+      <c r="BJ7" s="26" t="s">
         <v>212</v>
       </c>
       <c r="BK7" s="6" t="s">
@@ -2747,7 +2755,7 @@
       <c r="BX7" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="BY7" s="27" t="s">
+      <c r="BY7" s="24" t="s">
         <v>227</v>
       </c>
       <c r="BZ7" s="6" t="s">
@@ -2765,1005 +2773,1128 @@
       <c r="CD7" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="CE7" s="29" t="s">
+      <c r="CE7" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="CF7" s="29" t="s">
+      <c r="CF7" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="CG7" s="29" t="s">
+      <c r="CG7" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="CH7" s="29" t="s">
+      <c r="CH7" s="26" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:86" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="4"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="26" t="s">
         <v>237</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="D8" t="s">
+        <v>257</v>
+      </c>
+      <c r="E8" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="F8" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="G8" t="s">
+        <v>260</v>
+      </c>
+      <c r="H8" t="s">
+        <v>260</v>
+      </c>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="K8" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="L8" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="M8" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="N8" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="O8" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="D8" t="s">
-        <v>259</v>
-      </c>
-      <c r="E8" s="29" t="s">
+      <c r="P8" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="Q8" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="R8" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="S8" s="27"/>
+      <c r="T8" s="27"/>
+      <c r="U8" s="28"/>
+      <c r="V8" s="28" t="s">
+        <v>275</v>
+      </c>
+      <c r="W8" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="X8" s="28"/>
+      <c r="Y8" s="27">
+        <v>2.169024E-2</v>
+      </c>
+      <c r="Z8" s="27"/>
+      <c r="AA8" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="AB8" s="27"/>
+      <c r="AC8" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="AD8" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="AE8" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="AF8" s="26"/>
+      <c r="AG8" s="26"/>
+      <c r="AH8" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="AI8" s="26"/>
+      <c r="AJ8" s="26"/>
+      <c r="AK8" s="26"/>
+      <c r="AL8" s="26"/>
+      <c r="AM8" s="26"/>
+      <c r="AN8" s="26"/>
+      <c r="AO8" s="26"/>
+      <c r="AP8" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="AQ8" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="AR8" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="AS8" s="26"/>
+      <c r="AT8" s="26"/>
+      <c r="AU8" s="26"/>
+      <c r="AV8" s="26"/>
+      <c r="AW8" s="26" t="s">
         <v>269</v>
       </c>
-      <c r="G8" t="s">
-        <v>262</v>
-      </c>
-      <c r="H8" t="s">
-        <v>262</v>
-      </c>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29" t="s">
-        <v>261</v>
-      </c>
-      <c r="K8" s="29" t="s">
-        <v>261</v>
-      </c>
-      <c r="L8" s="29" t="s">
-        <v>261</v>
-      </c>
-      <c r="M8" s="29" t="s">
-        <v>261</v>
-      </c>
-      <c r="N8" s="29" t="s">
-        <v>261</v>
-      </c>
-      <c r="O8" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="P8" s="29" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q8" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="R8" s="29" t="s">
+      <c r="AX8" s="27"/>
+      <c r="AY8" s="27"/>
+      <c r="AZ8" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="BA8" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="BB8" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="BC8" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="S8" s="30"/>
-      <c r="T8" s="30"/>
-      <c r="U8" s="31"/>
-      <c r="V8" s="31" t="s">
-        <v>277</v>
-      </c>
-      <c r="W8" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="X8" s="31"/>
-      <c r="Y8" s="30">
-        <v>2.169024E-2</v>
-      </c>
-      <c r="Z8" s="30"/>
-      <c r="AA8" s="30" t="s">
-        <v>258</v>
-      </c>
-      <c r="AB8" s="30"/>
-      <c r="AC8" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="AD8" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="AE8" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="AF8" s="29"/>
-      <c r="AG8" s="29"/>
-      <c r="AH8" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="AI8" s="29"/>
-      <c r="AJ8" s="29"/>
-      <c r="AK8" s="29"/>
-      <c r="AL8" s="29"/>
-      <c r="AM8" s="29"/>
-      <c r="AN8" s="29"/>
-      <c r="AO8" s="29"/>
-      <c r="AP8" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="AQ8" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="AR8" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="AS8" s="29"/>
-      <c r="AT8" s="29"/>
-      <c r="AU8" s="29"/>
-      <c r="AV8" s="29"/>
-      <c r="AW8" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="AX8" s="30"/>
-      <c r="AY8" s="30"/>
-      <c r="AZ8" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="BA8" s="29" t="s">
-        <v>247</v>
-      </c>
-      <c r="BB8" s="39" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC8" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="BD8" s="32"/>
-      <c r="BE8" s="30">
+      <c r="BD8" s="29"/>
+      <c r="BE8" s="27">
         <v>3</v>
       </c>
-      <c r="BF8" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="BG8" s="30">
+      <c r="BF8" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="BG8" s="27">
         <v>70</v>
       </c>
-      <c r="BH8" s="30">
+      <c r="BH8" s="27">
         <v>1.4E-2</v>
       </c>
-      <c r="BI8" s="30">
+      <c r="BI8" s="27">
         <v>200</v>
       </c>
-      <c r="BJ8" s="29"/>
-      <c r="BK8" s="32"/>
-      <c r="BL8" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="BM8" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="BN8" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="BO8" s="32"/>
-      <c r="BP8" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="BQ8" s="32"/>
-      <c r="BR8" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="BS8" s="32"/>
-      <c r="BT8" s="32"/>
-      <c r="BU8" s="32"/>
-      <c r="BV8" s="32"/>
-      <c r="BW8" s="32"/>
-      <c r="BX8" s="32"/>
-      <c r="BY8" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="BZ8" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="CA8" s="29"/>
-      <c r="CB8" s="32"/>
-      <c r="CC8" s="32"/>
-      <c r="CD8" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="CE8" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="CF8" s="29"/>
-      <c r="CG8" s="29"/>
-      <c r="CH8" s="29"/>
+      <c r="BJ8" s="26"/>
+      <c r="BK8" s="29"/>
+      <c r="BL8" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="BM8" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="BN8" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="BO8" s="29"/>
+      <c r="BP8" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="BQ8" s="29"/>
+      <c r="BR8" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="BS8" s="29"/>
+      <c r="BT8" s="29"/>
+      <c r="BU8" s="29"/>
+      <c r="BV8" s="29"/>
+      <c r="BW8" s="29"/>
+      <c r="BX8" s="29"/>
+      <c r="BY8" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="BZ8" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="CA8" s="26"/>
+      <c r="CB8" s="29"/>
+      <c r="CC8" s="29"/>
+      <c r="CD8" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="CE8" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="CF8" s="26"/>
+      <c r="CG8" s="26"/>
+      <c r="CH8" s="26"/>
     </row>
     <row r="9" spans="1:86" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
-      <c r="C9" s="29" t="s">
-        <v>248</v>
-      </c>
-      <c r="D9" s="33"/>
-      <c r="E9" s="29" t="s">
-        <v>257</v>
-      </c>
-      <c r="F9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29" t="s">
+      <c r="C9" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="D9" s="30"/>
+      <c r="E9" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="F9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="P9" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q9" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="P9" s="29" t="s">
+      <c r="R9" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="Q9" s="29" t="s">
+      <c r="S9" s="27"/>
+      <c r="T9" s="27"/>
+      <c r="U9" s="30"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="30"/>
+      <c r="X9" s="30"/>
+      <c r="Y9" s="27">
+        <v>2.725352E-2</v>
+      </c>
+      <c r="Z9" s="27">
+        <v>2.725352E-2</v>
+      </c>
+      <c r="AA9" s="27">
+        <v>2.725352E-2</v>
+      </c>
+      <c r="AB9" s="27"/>
+      <c r="AC9" s="27"/>
+      <c r="AD9" s="26" t="s">
         <v>243</v>
       </c>
-      <c r="R9" s="29" t="s">
+      <c r="AE9" s="27"/>
+      <c r="AF9" s="26"/>
+      <c r="AG9" s="26"/>
+      <c r="AH9" s="26"/>
+      <c r="AI9" s="26"/>
+      <c r="AJ9" s="26"/>
+      <c r="AK9" s="26"/>
+      <c r="AL9" s="26"/>
+      <c r="AM9" s="26"/>
+      <c r="AN9" s="26"/>
+      <c r="AO9" s="26"/>
+      <c r="AP9" s="26"/>
+      <c r="AQ9" s="26"/>
+      <c r="AR9" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="S9" s="30"/>
-      <c r="T9" s="30"/>
-      <c r="U9" s="33"/>
-      <c r="V9" s="33"/>
-      <c r="W9" s="33"/>
-      <c r="X9" s="33"/>
-      <c r="Y9" s="30">
-        <v>2.725352E-2</v>
-      </c>
-      <c r="Z9" s="30">
-        <v>2.725352E-2</v>
-      </c>
-      <c r="AA9" s="30">
-        <v>2.725352E-2</v>
-      </c>
-      <c r="AB9" s="30"/>
-      <c r="AC9" s="30"/>
-      <c r="AD9" s="29" t="s">
+      <c r="AS9" s="26"/>
+      <c r="AT9" s="26"/>
+      <c r="AU9" s="26"/>
+      <c r="AV9" s="26"/>
+      <c r="AW9" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="AX9" s="27"/>
+      <c r="AY9" s="27"/>
+      <c r="AZ9" s="27">
+        <v>0.200098</v>
+      </c>
+      <c r="BA9" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="AE9" s="30"/>
-      <c r="AF9" s="29"/>
-      <c r="AG9" s="29"/>
-      <c r="AH9" s="29"/>
-      <c r="AI9" s="29"/>
-      <c r="AJ9" s="29"/>
-      <c r="AK9" s="29"/>
-      <c r="AL9" s="29"/>
-      <c r="AM9" s="29"/>
-      <c r="AN9" s="29"/>
-      <c r="AO9" s="29"/>
-      <c r="AP9" s="29"/>
-      <c r="AQ9" s="29"/>
-      <c r="AR9" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="AS9" s="29"/>
-      <c r="AT9" s="29"/>
-      <c r="AU9" s="29"/>
-      <c r="AV9" s="29"/>
-      <c r="AW9" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="AX9" s="30"/>
-      <c r="AY9" s="30"/>
-      <c r="AZ9" s="30">
-        <v>0.200098</v>
-      </c>
-      <c r="BA9" s="29" t="s">
-        <v>247</v>
-      </c>
-      <c r="BB9" s="39" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC9" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="BD9" s="33"/>
-      <c r="BE9" s="30">
+      <c r="BB9" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="BC9" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="BD9" s="30"/>
+      <c r="BE9" s="27">
         <v>3</v>
       </c>
-      <c r="BF9" s="30">
+      <c r="BF9" s="27">
         <v>1680</v>
       </c>
-      <c r="BG9" s="30">
+      <c r="BG9" s="27">
         <v>70</v>
       </c>
-      <c r="BH9" s="30">
+      <c r="BH9" s="27">
         <v>1.54E-2</v>
       </c>
-      <c r="BI9" s="30">
+      <c r="BI9" s="27">
         <v>220</v>
       </c>
-      <c r="BJ9" s="29"/>
-      <c r="BK9" s="33"/>
-      <c r="BL9" s="33"/>
-      <c r="BM9" s="33"/>
-      <c r="BN9" s="33"/>
-      <c r="BO9" s="33"/>
-      <c r="BP9" s="33"/>
-      <c r="BQ9" s="33"/>
-      <c r="BR9" s="33"/>
-      <c r="BS9" s="33"/>
-      <c r="BT9" s="33"/>
-      <c r="BU9" s="33"/>
-      <c r="BV9" s="33"/>
-      <c r="BW9" s="33"/>
-      <c r="BX9" s="33"/>
-      <c r="BY9" s="29"/>
-      <c r="BZ9" s="29"/>
-      <c r="CA9" s="29"/>
-      <c r="CB9" s="33"/>
-      <c r="CC9" s="33"/>
-      <c r="CD9" s="33"/>
-      <c r="CE9" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="CF9" s="29"/>
-      <c r="CG9" s="29"/>
-      <c r="CH9" s="29"/>
+      <c r="BJ9" s="26"/>
+      <c r="BK9" s="30"/>
+      <c r="BL9" s="30"/>
+      <c r="BM9" s="30"/>
+      <c r="BN9" s="30"/>
+      <c r="BO9" s="30"/>
+      <c r="BP9" s="30"/>
+      <c r="BQ9" s="30"/>
+      <c r="BR9" s="30"/>
+      <c r="BS9" s="30"/>
+      <c r="BT9" s="30"/>
+      <c r="BU9" s="30"/>
+      <c r="BV9" s="30"/>
+      <c r="BW9" s="30"/>
+      <c r="BX9" s="30"/>
+      <c r="BY9" s="26"/>
+      <c r="BZ9" s="26"/>
+      <c r="CA9" s="26"/>
+      <c r="CB9" s="30"/>
+      <c r="CC9" s="30"/>
+      <c r="CD9" s="30"/>
+      <c r="CE9" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="CF9" s="26"/>
+      <c r="CG9" s="26"/>
+      <c r="CH9" s="26"/>
     </row>
     <row r="10" spans="1:86" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
-      <c r="C10" s="29" t="s">
-        <v>249</v>
-      </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="F10" s="29" t="s">
+      <c r="C10" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="D10" s="30"/>
+      <c r="E10" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="H10" t="s">
+        <v>259</v>
+      </c>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="P10" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q10" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="R10" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="S10" s="27"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="30"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="30"/>
+      <c r="X10" s="30"/>
+      <c r="Y10" s="27">
+        <v>1.5365230000000001E-2</v>
+      </c>
+      <c r="Z10" s="27">
+        <v>1.5365230000000001E-2</v>
+      </c>
+      <c r="AA10" s="27">
+        <v>1.5365230000000001E-2</v>
+      </c>
+      <c r="AB10" s="27"/>
+      <c r="AC10" s="27"/>
+      <c r="AD10" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="AE10" s="27"/>
+      <c r="AF10" s="26"/>
+      <c r="AG10" s="26"/>
+      <c r="AH10" s="26"/>
+      <c r="AI10" s="26"/>
+      <c r="AJ10" s="26"/>
+      <c r="AK10" s="26"/>
+      <c r="AL10" s="26"/>
+      <c r="AM10" s="26"/>
+      <c r="AN10" s="26"/>
+      <c r="AO10" s="26"/>
+      <c r="AP10" s="26"/>
+      <c r="AQ10" s="26"/>
+      <c r="AR10" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="AS10" s="26"/>
+      <c r="AT10" s="26"/>
+      <c r="AU10" s="26"/>
+      <c r="AV10" s="26"/>
+      <c r="AW10" s="26" t="s">
         <v>269</v>
       </c>
-      <c r="H10" t="s">
-        <v>261</v>
-      </c>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29" t="s">
-        <v>263</v>
-      </c>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="P10" s="29" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q10" s="29" t="s">
-        <v>243</v>
-      </c>
-      <c r="R10" s="29" t="s">
+      <c r="AX10" s="27"/>
+      <c r="AY10" s="27"/>
+      <c r="AZ10" s="27">
+        <v>0.200098</v>
+      </c>
+      <c r="BA10" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="BB10" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="BC10" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="S10" s="30"/>
-      <c r="T10" s="30"/>
-      <c r="U10" s="33"/>
-      <c r="V10" s="33"/>
-      <c r="W10" s="33"/>
-      <c r="X10" s="33"/>
-      <c r="Y10" s="30">
-        <v>1.5365230000000001E-2</v>
-      </c>
-      <c r="Z10" s="30">
-        <v>1.5365230000000001E-2</v>
-      </c>
-      <c r="AA10" s="30">
-        <v>1.5365230000000001E-2</v>
-      </c>
-      <c r="AB10" s="30"/>
-      <c r="AC10" s="30"/>
-      <c r="AD10" s="29" t="s">
-        <v>245</v>
-      </c>
-      <c r="AE10" s="30"/>
-      <c r="AF10" s="29"/>
-      <c r="AG10" s="29"/>
-      <c r="AH10" s="29"/>
-      <c r="AI10" s="29"/>
-      <c r="AJ10" s="29"/>
-      <c r="AK10" s="29"/>
-      <c r="AL10" s="29"/>
-      <c r="AM10" s="29"/>
-      <c r="AN10" s="29"/>
-      <c r="AO10" s="29"/>
-      <c r="AP10" s="29"/>
-      <c r="AQ10" s="29"/>
-      <c r="AR10" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="AS10" s="29"/>
-      <c r="AT10" s="29"/>
-      <c r="AU10" s="29"/>
-      <c r="AV10" s="29"/>
-      <c r="AW10" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="AX10" s="30"/>
-      <c r="AY10" s="30"/>
-      <c r="AZ10" s="30">
-        <v>0.200098</v>
-      </c>
-      <c r="BA10" s="29" t="s">
-        <v>247</v>
-      </c>
-      <c r="BB10" s="39" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC10" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="BD10" s="33"/>
-      <c r="BE10" s="30">
+      <c r="BD10" s="30"/>
+      <c r="BE10" s="27">
         <v>3</v>
       </c>
-      <c r="BF10" s="30">
+      <c r="BF10" s="27">
         <v>1680</v>
       </c>
-      <c r="BG10" s="30">
+      <c r="BG10" s="27">
         <v>70</v>
       </c>
-      <c r="BH10" s="30">
+      <c r="BH10" s="27">
         <v>1.54E-2</v>
       </c>
-      <c r="BI10" s="30">
+      <c r="BI10" s="27">
         <v>220</v>
       </c>
-      <c r="BJ10" s="29"/>
-      <c r="BK10" s="33"/>
-      <c r="BL10" s="33"/>
-      <c r="BM10" s="33"/>
-      <c r="BN10" s="33"/>
-      <c r="BO10" s="33"/>
-      <c r="BP10" s="33"/>
-      <c r="BQ10" s="33"/>
-      <c r="BR10" s="33"/>
-      <c r="BS10" s="33"/>
-      <c r="BT10" s="33"/>
-      <c r="BU10" s="33"/>
-      <c r="BV10" s="33"/>
-      <c r="BW10" s="33"/>
-      <c r="BX10" s="33"/>
-      <c r="BY10" s="29"/>
-      <c r="BZ10" s="29"/>
-      <c r="CA10" s="29"/>
-      <c r="CB10" s="33"/>
-      <c r="CC10" s="33"/>
-      <c r="CD10" s="33"/>
-      <c r="CE10" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="CF10" s="29"/>
-      <c r="CG10" s="29"/>
-      <c r="CH10" s="29"/>
+      <c r="BJ10" s="26"/>
+      <c r="BK10" s="30"/>
+      <c r="BL10" s="30"/>
+      <c r="BM10" s="30"/>
+      <c r="BN10" s="30"/>
+      <c r="BO10" s="30"/>
+      <c r="BP10" s="30"/>
+      <c r="BQ10" s="30"/>
+      <c r="BR10" s="30"/>
+      <c r="BS10" s="30"/>
+      <c r="BT10" s="30"/>
+      <c r="BU10" s="30"/>
+      <c r="BV10" s="30"/>
+      <c r="BW10" s="30"/>
+      <c r="BX10" s="30"/>
+      <c r="BY10" s="26"/>
+      <c r="BZ10" s="26"/>
+      <c r="CA10" s="26"/>
+      <c r="CB10" s="30"/>
+      <c r="CC10" s="30"/>
+      <c r="CD10" s="30"/>
+      <c r="CE10" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="CF10" s="26"/>
+      <c r="CG10" s="26"/>
+      <c r="CH10" s="26"/>
     </row>
     <row r="11" spans="1:86" ht="16" x14ac:dyDescent="0.2">
-      <c r="C11" s="29" t="s">
-        <v>250</v>
-      </c>
-      <c r="D11" s="33"/>
-      <c r="E11" s="29" t="s">
-        <v>255</v>
-      </c>
-      <c r="F11" s="29" t="s">
+      <c r="C11" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="D11" s="30"/>
+      <c r="E11" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="G11" t="s">
+        <v>258</v>
+      </c>
+      <c r="H11" s="30"/>
+      <c r="I11" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="26"/>
+      <c r="O11" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="P11" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q11" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="R11" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="S11" s="27"/>
+      <c r="T11" s="27"/>
+      <c r="U11" s="30"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="30"/>
+      <c r="X11" s="30"/>
+      <c r="Y11" s="27">
+        <v>4.8993170000000003E-2</v>
+      </c>
+      <c r="Z11" s="27">
+        <v>4.8993170000000003E-2</v>
+      </c>
+      <c r="AA11" s="27">
+        <v>4.8993170000000003E-2</v>
+      </c>
+      <c r="AB11" s="27"/>
+      <c r="AC11" s="27"/>
+      <c r="AD11" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="AE11" s="27"/>
+      <c r="AF11" s="26"/>
+      <c r="AG11" s="26"/>
+      <c r="AH11" s="26"/>
+      <c r="AI11" s="26"/>
+      <c r="AJ11" s="26"/>
+      <c r="AK11" s="26"/>
+      <c r="AL11" s="26"/>
+      <c r="AM11" s="26"/>
+      <c r="AN11" s="26"/>
+      <c r="AO11" s="26"/>
+      <c r="AP11" s="26"/>
+      <c r="AQ11" s="26"/>
+      <c r="AR11" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="AS11" s="26"/>
+      <c r="AT11" s="26"/>
+      <c r="AU11" s="26"/>
+      <c r="AV11" s="26"/>
+      <c r="AW11" s="26" t="s">
         <v>269</v>
       </c>
-      <c r="G11" t="s">
-        <v>260</v>
-      </c>
-      <c r="H11" s="33"/>
-      <c r="I11" s="29" t="s">
-        <v>261</v>
-      </c>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="29" t="s">
-        <v>251</v>
-      </c>
-      <c r="P11" s="29" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q11" s="29" t="s">
-        <v>243</v>
-      </c>
-      <c r="R11" s="29" t="s">
+      <c r="AX11" s="27"/>
+      <c r="AY11" s="27"/>
+      <c r="AZ11" s="27">
+        <v>0.200098</v>
+      </c>
+      <c r="BA11" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="BB11" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="BC11" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="S11" s="30"/>
-      <c r="T11" s="30"/>
-      <c r="U11" s="33"/>
-      <c r="V11" s="33"/>
-      <c r="W11" s="33"/>
-      <c r="X11" s="33"/>
-      <c r="Y11" s="30">
-        <v>4.8993170000000003E-2</v>
-      </c>
-      <c r="Z11" s="30">
-        <v>4.8993170000000003E-2</v>
-      </c>
-      <c r="AA11" s="30">
-        <v>4.8993170000000003E-2</v>
-      </c>
-      <c r="AB11" s="30"/>
-      <c r="AC11" s="30"/>
-      <c r="AD11" s="29" t="s">
-        <v>245</v>
-      </c>
-      <c r="AE11" s="30"/>
-      <c r="AF11" s="29"/>
-      <c r="AG11" s="29"/>
-      <c r="AH11" s="29"/>
-      <c r="AI11" s="29"/>
-      <c r="AJ11" s="29"/>
-      <c r="AK11" s="29"/>
-      <c r="AL11" s="29"/>
-      <c r="AM11" s="29"/>
-      <c r="AN11" s="29"/>
-      <c r="AO11" s="29"/>
-      <c r="AP11" s="29"/>
-      <c r="AQ11" s="29"/>
-      <c r="AR11" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="AS11" s="29"/>
-      <c r="AT11" s="29"/>
-      <c r="AU11" s="29"/>
-      <c r="AV11" s="29"/>
-      <c r="AW11" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="AX11" s="30"/>
-      <c r="AY11" s="30"/>
-      <c r="AZ11" s="30">
-        <v>0.200098</v>
-      </c>
-      <c r="BA11" s="29" t="s">
-        <v>247</v>
-      </c>
-      <c r="BB11" s="39" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC11" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="BD11" s="33"/>
-      <c r="BE11" s="30">
+      <c r="BD11" s="30"/>
+      <c r="BE11" s="27">
         <v>3</v>
       </c>
-      <c r="BF11" s="30">
+      <c r="BF11" s="27">
         <v>600</v>
       </c>
-      <c r="BG11" s="30">
+      <c r="BG11" s="27">
         <v>70</v>
       </c>
-      <c r="BH11" s="30">
+      <c r="BH11" s="27">
         <v>1.54E-2</v>
       </c>
-      <c r="BI11" s="30">
+      <c r="BI11" s="27">
         <v>220</v>
       </c>
-      <c r="BJ11" s="29"/>
-      <c r="BK11" s="33"/>
-      <c r="BL11" s="33"/>
-      <c r="BM11" s="33"/>
-      <c r="BN11" s="33"/>
-      <c r="BO11" s="33"/>
-      <c r="BP11" s="33"/>
-      <c r="BQ11" s="33"/>
-      <c r="BR11" s="33"/>
-      <c r="BS11" s="33"/>
-      <c r="BT11" s="33"/>
-      <c r="BU11" s="33"/>
-      <c r="BV11" s="33"/>
-      <c r="BW11" s="33"/>
-      <c r="BX11" s="33"/>
-      <c r="BY11" s="29"/>
-      <c r="BZ11" s="29"/>
-      <c r="CA11" s="29"/>
-      <c r="CB11" s="33"/>
-      <c r="CC11" s="33"/>
-      <c r="CD11" s="33"/>
-      <c r="CE11" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="CF11" s="29"/>
-      <c r="CG11" s="29"/>
-      <c r="CH11" s="29"/>
+      <c r="BJ11" s="26"/>
+      <c r="BK11" s="30"/>
+      <c r="BL11" s="30"/>
+      <c r="BM11" s="30"/>
+      <c r="BN11" s="30"/>
+      <c r="BO11" s="30"/>
+      <c r="BP11" s="30"/>
+      <c r="BQ11" s="30"/>
+      <c r="BR11" s="30"/>
+      <c r="BS11" s="30"/>
+      <c r="BT11" s="30"/>
+      <c r="BU11" s="30"/>
+      <c r="BV11" s="30"/>
+      <c r="BW11" s="30"/>
+      <c r="BX11" s="30"/>
+      <c r="BY11" s="26"/>
+      <c r="BZ11" s="26"/>
+      <c r="CA11" s="26"/>
+      <c r="CB11" s="30"/>
+      <c r="CC11" s="30"/>
+      <c r="CD11" s="30"/>
+      <c r="CE11" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="CF11" s="26"/>
+      <c r="CG11" s="26"/>
+      <c r="CH11" s="26"/>
     </row>
     <row r="12" spans="1:86" ht="16" x14ac:dyDescent="0.2">
-      <c r="C12" s="29" t="s">
-        <v>252</v>
-      </c>
-      <c r="D12" s="33"/>
-      <c r="E12" s="29" t="s">
-        <v>256</v>
-      </c>
-      <c r="F12" s="29" t="s">
+      <c r="C12" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="D12" s="30"/>
+      <c r="E12" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="G12" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="H12" s="30"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="26"/>
+      <c r="O12" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="P12" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q12" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="R12" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="S12" s="27"/>
+      <c r="T12" s="27"/>
+      <c r="U12" s="30"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="30"/>
+      <c r="X12" s="30"/>
+      <c r="Y12" s="27">
+        <v>1.4276580000000001E-2</v>
+      </c>
+      <c r="Z12" s="27">
+        <v>1.4276580000000001E-2</v>
+      </c>
+      <c r="AA12" s="27">
+        <v>1.4276580000000001E-2</v>
+      </c>
+      <c r="AB12" s="27"/>
+      <c r="AC12" s="27"/>
+      <c r="AD12" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="AE12" s="27"/>
+      <c r="AF12" s="26"/>
+      <c r="AG12" s="26"/>
+      <c r="AH12" s="26"/>
+      <c r="AI12" s="26"/>
+      <c r="AJ12" s="26"/>
+      <c r="AK12" s="26"/>
+      <c r="AL12" s="26"/>
+      <c r="AM12" s="26"/>
+      <c r="AN12" s="26"/>
+      <c r="AO12" s="26"/>
+      <c r="AP12" s="26"/>
+      <c r="AQ12" s="26"/>
+      <c r="AR12" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="AS12" s="26"/>
+      <c r="AT12" s="26"/>
+      <c r="AU12" s="26"/>
+      <c r="AV12" s="26"/>
+      <c r="AW12" s="26" t="s">
         <v>269</v>
       </c>
-      <c r="G12" s="29" t="s">
-        <v>252</v>
-      </c>
-      <c r="H12" s="33"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
-      <c r="N12" s="29"/>
-      <c r="O12" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="P12" s="29" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q12" s="29" t="s">
-        <v>243</v>
-      </c>
-      <c r="R12" s="29" t="s">
+      <c r="AX12" s="27"/>
+      <c r="AY12" s="27"/>
+      <c r="AZ12" s="27">
+        <v>0.200098</v>
+      </c>
+      <c r="BA12" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="BB12" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="BC12" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="S12" s="30"/>
-      <c r="T12" s="30"/>
-      <c r="U12" s="33"/>
-      <c r="V12" s="33"/>
-      <c r="W12" s="33"/>
-      <c r="X12" s="33"/>
-      <c r="Y12" s="30">
-        <v>1.4276580000000001E-2</v>
-      </c>
-      <c r="Z12" s="30">
-        <v>1.4276580000000001E-2</v>
-      </c>
-      <c r="AA12" s="30">
-        <v>1.4276580000000001E-2</v>
-      </c>
-      <c r="AB12" s="30"/>
-      <c r="AC12" s="30"/>
-      <c r="AD12" s="29" t="s">
-        <v>245</v>
-      </c>
-      <c r="AE12" s="30"/>
-      <c r="AF12" s="29"/>
-      <c r="AG12" s="29"/>
-      <c r="AH12" s="29"/>
-      <c r="AI12" s="29"/>
-      <c r="AJ12" s="29"/>
-      <c r="AK12" s="29"/>
-      <c r="AL12" s="29"/>
-      <c r="AM12" s="29"/>
-      <c r="AN12" s="29"/>
-      <c r="AO12" s="29"/>
-      <c r="AP12" s="29"/>
-      <c r="AQ12" s="29"/>
-      <c r="AR12" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="AS12" s="29"/>
-      <c r="AT12" s="29"/>
-      <c r="AU12" s="29"/>
-      <c r="AV12" s="29"/>
-      <c r="AW12" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="AX12" s="30"/>
-      <c r="AY12" s="30"/>
-      <c r="AZ12" s="30">
-        <v>0.200098</v>
-      </c>
-      <c r="BA12" s="29" t="s">
-        <v>247</v>
-      </c>
-      <c r="BB12" s="39" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC12" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="BD12" s="33"/>
-      <c r="BE12" s="30">
+      <c r="BD12" s="30"/>
+      <c r="BE12" s="27">
         <v>3</v>
       </c>
-      <c r="BF12" s="30">
+      <c r="BF12" s="27">
         <v>1440</v>
       </c>
-      <c r="BG12" s="30">
+      <c r="BG12" s="27">
         <v>70</v>
       </c>
-      <c r="BH12" s="30">
+      <c r="BH12" s="27">
         <v>1.4E-2</v>
       </c>
-      <c r="BI12" s="30">
+      <c r="BI12" s="27">
         <v>200</v>
       </c>
-      <c r="BJ12" s="29"/>
-      <c r="BK12" s="33"/>
-      <c r="BL12" s="33"/>
-      <c r="BM12" s="33"/>
-      <c r="BN12" s="33"/>
-      <c r="BO12" s="33"/>
-      <c r="BP12" s="33"/>
-      <c r="BQ12" s="33"/>
-      <c r="BR12" s="33"/>
-      <c r="BS12" s="33"/>
-      <c r="BT12" s="33"/>
-      <c r="BU12" s="33"/>
-      <c r="BV12" s="33"/>
-      <c r="BW12" s="33"/>
-      <c r="BX12" s="33"/>
-      <c r="BY12" s="29"/>
-      <c r="BZ12" s="29"/>
-      <c r="CA12" s="29"/>
-      <c r="CB12" s="33"/>
-      <c r="CC12" s="33"/>
-      <c r="CD12" s="33"/>
-      <c r="CE12" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="CF12" s="29"/>
-      <c r="CG12" s="29"/>
-      <c r="CH12" s="29"/>
+      <c r="BJ12" s="26"/>
+      <c r="BK12" s="30"/>
+      <c r="BL12" s="30"/>
+      <c r="BM12" s="30"/>
+      <c r="BN12" s="30"/>
+      <c r="BO12" s="30"/>
+      <c r="BP12" s="30"/>
+      <c r="BQ12" s="30"/>
+      <c r="BR12" s="30"/>
+      <c r="BS12" s="30"/>
+      <c r="BT12" s="30"/>
+      <c r="BU12" s="30"/>
+      <c r="BV12" s="30"/>
+      <c r="BW12" s="30"/>
+      <c r="BX12" s="30"/>
+      <c r="BY12" s="26"/>
+      <c r="BZ12" s="26"/>
+      <c r="CA12" s="26"/>
+      <c r="CB12" s="30"/>
+      <c r="CC12" s="30"/>
+      <c r="CD12" s="30"/>
+      <c r="CE12" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="CF12" s="26"/>
+      <c r="CG12" s="26"/>
+      <c r="CH12" s="26"/>
     </row>
     <row r="13" spans="1:86" ht="16" x14ac:dyDescent="0.2">
-      <c r="C13" s="29" t="s">
-        <v>253</v>
-      </c>
-      <c r="D13" s="33"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29" t="s">
+      <c r="C13" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="D13" s="30"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="26"/>
+      <c r="O13" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="P13" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q13" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="R13" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="S13" s="27"/>
+      <c r="T13" s="27"/>
+      <c r="U13" s="30"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="30"/>
+      <c r="X13" s="30"/>
+      <c r="Y13" s="27">
+        <v>2.725352E-2</v>
+      </c>
+      <c r="Z13" s="27">
+        <v>2.725352E-2</v>
+      </c>
+      <c r="AA13" s="27">
+        <v>2.725352E-2</v>
+      </c>
+      <c r="AB13" s="27"/>
+      <c r="AC13" s="27"/>
+      <c r="AD13" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="AE13" s="27"/>
+      <c r="AF13" s="26"/>
+      <c r="AG13" s="26"/>
+      <c r="AH13" s="26"/>
+      <c r="AI13" s="26"/>
+      <c r="AJ13" s="26"/>
+      <c r="AK13" s="26"/>
+      <c r="AL13" s="26"/>
+      <c r="AM13" s="26"/>
+      <c r="AN13" s="26"/>
+      <c r="AO13" s="26"/>
+      <c r="AP13" s="26"/>
+      <c r="AQ13" s="26"/>
+      <c r="AR13" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="AS13" s="26"/>
+      <c r="AT13" s="26"/>
+      <c r="AU13" s="26"/>
+      <c r="AV13" s="26"/>
+      <c r="AW13" s="26" t="s">
         <v>269</v>
       </c>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="P13" s="29" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q13" s="29" t="s">
-        <v>243</v>
-      </c>
-      <c r="R13" s="29" t="s">
+      <c r="AX13" s="27"/>
+      <c r="AY13" s="27"/>
+      <c r="AZ13" s="27">
+        <v>0.200098</v>
+      </c>
+      <c r="BA13" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="BB13" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="BC13" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="S13" s="30"/>
-      <c r="T13" s="30"/>
-      <c r="U13" s="33"/>
-      <c r="V13" s="33"/>
-      <c r="W13" s="33"/>
-      <c r="X13" s="33"/>
-      <c r="Y13" s="30">
-        <v>2.725352E-2</v>
-      </c>
-      <c r="Z13" s="30">
-        <v>2.725352E-2</v>
-      </c>
-      <c r="AA13" s="30">
-        <v>2.725352E-2</v>
-      </c>
-      <c r="AB13" s="30"/>
-      <c r="AC13" s="30"/>
-      <c r="AD13" s="29" t="s">
-        <v>245</v>
-      </c>
-      <c r="AE13" s="30"/>
-      <c r="AF13" s="29"/>
-      <c r="AG13" s="29"/>
-      <c r="AH13" s="29"/>
-      <c r="AI13" s="29"/>
-      <c r="AJ13" s="29"/>
-      <c r="AK13" s="29"/>
-      <c r="AL13" s="29"/>
-      <c r="AM13" s="29"/>
-      <c r="AN13" s="29"/>
-      <c r="AO13" s="29"/>
-      <c r="AP13" s="29"/>
-      <c r="AQ13" s="29"/>
-      <c r="AR13" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="AS13" s="29"/>
-      <c r="AT13" s="29"/>
-      <c r="AU13" s="29"/>
-      <c r="AV13" s="29"/>
-      <c r="AW13" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="AX13" s="30"/>
-      <c r="AY13" s="30"/>
-      <c r="AZ13" s="30">
-        <v>0.200098</v>
-      </c>
-      <c r="BA13" s="29" t="s">
-        <v>247</v>
-      </c>
-      <c r="BB13" s="39" t="s">
-        <v>275</v>
-      </c>
-      <c r="BC13" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="BD13" s="33"/>
-      <c r="BE13" s="30">
+      <c r="BD13" s="30"/>
+      <c r="BE13" s="27">
         <v>3</v>
       </c>
-      <c r="BF13" s="30">
+      <c r="BF13" s="27">
         <v>1680</v>
       </c>
-      <c r="BG13" s="30">
+      <c r="BG13" s="27">
         <v>70</v>
       </c>
-      <c r="BH13" s="30">
+      <c r="BH13" s="27">
         <v>1.54E-2</v>
       </c>
-      <c r="BI13" s="30">
+      <c r="BI13" s="27">
         <v>220</v>
       </c>
-      <c r="BJ13" s="29"/>
-      <c r="BK13" s="33"/>
-      <c r="BL13" s="33"/>
-      <c r="BM13" s="33"/>
-      <c r="BN13" s="33"/>
-      <c r="BO13" s="33"/>
-      <c r="BP13" s="33"/>
-      <c r="BQ13" s="33"/>
-      <c r="BR13" s="33"/>
-      <c r="BS13" s="33"/>
-      <c r="BT13" s="33"/>
-      <c r="BU13" s="33"/>
-      <c r="BV13" s="33"/>
-      <c r="BW13" s="33"/>
-      <c r="BX13" s="33"/>
-      <c r="BY13" s="29"/>
-      <c r="BZ13" s="29"/>
-      <c r="CA13" s="29"/>
-      <c r="CB13" s="33"/>
-      <c r="CC13" s="33"/>
-      <c r="CD13" s="33"/>
-      <c r="CE13" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="CF13" s="29"/>
-      <c r="CG13" s="29"/>
-      <c r="CH13" s="29"/>
+      <c r="BJ13" s="26"/>
+      <c r="BK13" s="30"/>
+      <c r="BL13" s="30"/>
+      <c r="BM13" s="30"/>
+      <c r="BN13" s="30"/>
+      <c r="BO13" s="30"/>
+      <c r="BP13" s="30"/>
+      <c r="BQ13" s="30"/>
+      <c r="BR13" s="30"/>
+      <c r="BS13" s="30"/>
+      <c r="BT13" s="30"/>
+      <c r="BU13" s="30"/>
+      <c r="BV13" s="30"/>
+      <c r="BW13" s="30"/>
+      <c r="BX13" s="30"/>
+      <c r="BY13" s="26"/>
+      <c r="BZ13" s="26"/>
+      <c r="CA13" s="26"/>
+      <c r="CB13" s="30"/>
+      <c r="CC13" s="30"/>
+      <c r="CD13" s="30"/>
+      <c r="CE13" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="CF13" s="26"/>
+      <c r="CG13" s="26"/>
+      <c r="CH13" s="26"/>
     </row>
     <row r="14" spans="1:86" ht="16" x14ac:dyDescent="0.2">
-      <c r="C14" s="29" t="s">
-        <v>253</v>
-      </c>
-      <c r="D14" s="33"/>
-      <c r="E14" s="29" t="s">
-        <v>256</v>
-      </c>
-      <c r="F14" s="29" t="s">
-        <v>270</v>
-      </c>
-      <c r="G14" s="29" t="s">
-        <v>252</v>
-      </c>
-      <c r="H14" s="33"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="29"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="29" t="s">
+      <c r="C14" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="D14" s="30"/>
+      <c r="E14" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="F14" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="H14" s="30"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="P14" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q14" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="P14" s="29" t="s">
+      <c r="R14" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="Q14" s="29" t="s">
+      <c r="S14" s="27"/>
+      <c r="T14" s="27"/>
+      <c r="U14" s="30"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="30"/>
+      <c r="X14" s="30"/>
+      <c r="Y14" s="27">
+        <v>1.4276580000000001E-2</v>
+      </c>
+      <c r="Z14" s="27">
+        <v>1.4276580000000001E-2</v>
+      </c>
+      <c r="AA14" s="27">
+        <v>1.4276580000000001E-2</v>
+      </c>
+      <c r="AB14" s="27"/>
+      <c r="AC14" s="27"/>
+      <c r="AD14" s="26" t="s">
         <v>243</v>
       </c>
-      <c r="R14" s="29" t="s">
+      <c r="AE14" s="27"/>
+      <c r="AF14" s="26"/>
+      <c r="AG14" s="26"/>
+      <c r="AH14" s="26"/>
+      <c r="AI14" s="26"/>
+      <c r="AJ14" s="26"/>
+      <c r="AK14" s="26"/>
+      <c r="AL14" s="26"/>
+      <c r="AM14" s="26"/>
+      <c r="AN14" s="26"/>
+      <c r="AO14" s="26"/>
+      <c r="AP14" s="26"/>
+      <c r="AQ14" s="26"/>
+      <c r="AR14" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="S14" s="30"/>
-      <c r="T14" s="30"/>
-      <c r="U14" s="33"/>
-      <c r="V14" s="33"/>
-      <c r="W14" s="33"/>
-      <c r="X14" s="33"/>
-      <c r="Y14" s="30">
-        <v>1.4276580000000001E-2</v>
-      </c>
-      <c r="Z14" s="30">
-        <v>1.4276580000000001E-2</v>
-      </c>
-      <c r="AA14" s="30">
-        <v>1.4276580000000001E-2</v>
-      </c>
-      <c r="AB14" s="30"/>
-      <c r="AC14" s="30"/>
-      <c r="AD14" s="29" t="s">
+      <c r="AS14" s="26"/>
+      <c r="AT14" s="26"/>
+      <c r="AU14" s="26"/>
+      <c r="AV14" s="26"/>
+      <c r="AW14" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="AX14" s="27"/>
+      <c r="AY14" s="27"/>
+      <c r="AZ14" s="27">
+        <v>0.200098</v>
+      </c>
+      <c r="BA14" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="AE14" s="30"/>
-      <c r="AF14" s="29"/>
-      <c r="AG14" s="29"/>
-      <c r="AH14" s="29"/>
-      <c r="AI14" s="29"/>
-      <c r="AJ14" s="29"/>
-      <c r="AK14" s="29"/>
-      <c r="AL14" s="29"/>
-      <c r="AM14" s="29"/>
-      <c r="AN14" s="29"/>
-      <c r="AO14" s="29"/>
-      <c r="AP14" s="29"/>
-      <c r="AQ14" s="29"/>
-      <c r="AR14" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="AS14" s="29"/>
-      <c r="AT14" s="29"/>
-      <c r="AU14" s="29"/>
-      <c r="AV14" s="29"/>
-      <c r="AW14" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="AX14" s="30"/>
-      <c r="AY14" s="30"/>
-      <c r="AZ14" s="30">
-        <v>0.200098</v>
-      </c>
-      <c r="BA14" s="29" t="s">
-        <v>247</v>
-      </c>
-      <c r="BB14" s="39" t="s">
-        <v>276</v>
-      </c>
-      <c r="BC14" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="BD14" s="33"/>
-      <c r="BE14" s="30">
+      <c r="BB14" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="BC14" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="BD14" s="30"/>
+      <c r="BE14" s="27">
         <v>3</v>
       </c>
-      <c r="BF14" s="30">
+      <c r="BF14" s="27">
         <v>1440</v>
       </c>
-      <c r="BG14" s="30">
+      <c r="BG14" s="27">
         <v>70</v>
       </c>
-      <c r="BH14" s="30">
+      <c r="BH14" s="27">
         <v>1.4E-2</v>
       </c>
-      <c r="BI14" s="30">
+      <c r="BI14" s="27">
         <v>200</v>
       </c>
-      <c r="BJ14" s="29"/>
-      <c r="BK14" s="33"/>
-      <c r="BL14" s="33"/>
-      <c r="BM14" s="33"/>
-      <c r="BN14" s="33"/>
-      <c r="BO14" s="33"/>
-      <c r="BP14" s="33"/>
-      <c r="BQ14" s="33"/>
-      <c r="BR14" s="33"/>
-      <c r="BS14" s="33"/>
-      <c r="BT14" s="33"/>
-      <c r="BU14" s="33"/>
-      <c r="BV14" s="33"/>
-      <c r="BW14" s="33"/>
-      <c r="BX14" s="33"/>
-      <c r="BY14" s="29"/>
-      <c r="BZ14" s="29"/>
-      <c r="CA14" s="29"/>
-      <c r="CB14" s="33"/>
-      <c r="CC14" s="33"/>
-      <c r="CD14" s="33"/>
-      <c r="CE14" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="CF14" s="29"/>
-      <c r="CG14" s="29"/>
-      <c r="CH14" s="29"/>
+      <c r="BJ14" s="26"/>
+      <c r="BK14" s="30"/>
+      <c r="BL14" s="30"/>
+      <c r="BM14" s="30"/>
+      <c r="BN14" s="30"/>
+      <c r="BO14" s="30"/>
+      <c r="BP14" s="30"/>
+      <c r="BQ14" s="30"/>
+      <c r="BR14" s="30"/>
+      <c r="BS14" s="30"/>
+      <c r="BT14" s="30"/>
+      <c r="BU14" s="30"/>
+      <c r="BV14" s="30"/>
+      <c r="BW14" s="30"/>
+      <c r="BX14" s="30"/>
+      <c r="BY14" s="26"/>
+      <c r="BZ14" s="26"/>
+      <c r="CA14" s="26"/>
+      <c r="CB14" s="30"/>
+      <c r="CC14" s="30"/>
+      <c r="CD14" s="30"/>
+      <c r="CE14" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="CF14" s="26"/>
+      <c r="CG14" s="26"/>
+      <c r="CH14" s="26"/>
     </row>
     <row r="15" spans="1:86" ht="16" x14ac:dyDescent="0.2">
-      <c r="BB15" s="39"/>
-    </row>
-    <row r="16" spans="1:86" ht="16" x14ac:dyDescent="0.2">
-      <c r="BB16" s="39"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="34" t="s">
+        <v>276</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="P15" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q15" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="R15" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="S15" s="27"/>
+      <c r="T15" s="27"/>
+      <c r="U15" s="28"/>
+      <c r="V15" s="28"/>
+      <c r="W15" s="26"/>
+      <c r="X15" s="28"/>
+      <c r="Y15" s="27">
+        <v>2.169024E-2</v>
+      </c>
+      <c r="Z15" s="27">
+        <v>1.4276580000000001E-2</v>
+      </c>
+      <c r="AA15" s="27">
+        <v>1.4276580000000001E-2</v>
+      </c>
+      <c r="AB15" s="27"/>
+      <c r="AC15" s="26"/>
+      <c r="AD15" s="35" t="s">
+        <v>243</v>
+      </c>
+      <c r="AE15" s="26"/>
+      <c r="AF15" s="26"/>
+      <c r="AG15" s="26"/>
+      <c r="AH15" s="26"/>
+      <c r="AI15" s="26"/>
+      <c r="AJ15" s="26"/>
+      <c r="AK15" s="26"/>
+      <c r="AL15" s="26"/>
+      <c r="AM15" s="26"/>
+      <c r="AN15" s="26"/>
+      <c r="AO15" s="26"/>
+      <c r="AP15" s="26"/>
+      <c r="AQ15" s="26"/>
+      <c r="AR15" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="AS15" s="26"/>
+      <c r="AT15" s="26"/>
+      <c r="AU15" s="26"/>
+      <c r="AV15" s="26"/>
+      <c r="AW15" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="AX15" s="27"/>
+      <c r="AY15" s="27"/>
+      <c r="AZ15" s="27">
+        <v>0.200098</v>
+      </c>
+      <c r="BA15" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="BB15" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="BC15" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="BD15" s="29"/>
+      <c r="BE15" s="27">
+        <v>3</v>
+      </c>
+      <c r="BF15" s="27">
+        <v>1440</v>
+      </c>
+      <c r="BG15" s="27">
+        <v>70</v>
+      </c>
+      <c r="BH15" s="27">
+        <v>1.4E-2</v>
+      </c>
+      <c r="BI15" s="27">
+        <v>200</v>
+      </c>
+      <c r="BJ15" s="26"/>
+      <c r="BK15" s="29"/>
+      <c r="BL15" s="26"/>
+      <c r="BM15" s="26"/>
+      <c r="BN15" s="26"/>
+      <c r="BO15" s="29"/>
+      <c r="BP15" s="26"/>
+      <c r="BQ15" s="29"/>
+      <c r="BR15" s="26"/>
+      <c r="BS15" s="29"/>
+      <c r="BT15" s="29"/>
+      <c r="BU15" s="29"/>
+      <c r="BV15" s="29"/>
+      <c r="BW15" s="29"/>
+      <c r="BX15" s="29"/>
+      <c r="BY15" s="26"/>
+      <c r="BZ15" s="26"/>
+      <c r="CA15" s="26"/>
+      <c r="CB15" s="29"/>
+      <c r="CC15" s="29"/>
+      <c r="CD15" s="26"/>
+      <c r="CE15" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="CF15" s="26"/>
+      <c r="CG15" s="26"/>
+      <c r="CH15" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/spec/fixtures/batch_submission_manifest_errors_test.xlsx
+++ b/spec/fixtures/batch_submission_manifest_errors_test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10212"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smc101/vagrant/morphosource-vagrant/MorphoSource_SF/spec/fixtures/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smc101/vagrant/morphosource-vagrant/MorphoSource/spec/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5FD756C-A380-0C4E-9646-2FC415B6D80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD27215-A2CE-764D-8931-59FD4D7C1FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="32000" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="32000" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="278">
   <si>
     <t>Field Section</t>
   </si>
@@ -450,6 +450,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Values for Controlled Vocabulary type fields must match one of the options provided in this row. Each Controlled Vocabulary option is listed as a short-hand term value and a longer length full text description of the option. </t>
     </r>
@@ -459,6 +460,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Controlled vocabulary option values must match short-hand term values! </t>
     </r>
@@ -467,6 +469,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>They can't match full text descriptions of options, that will produce an error on manifest submission. An example options list could look like this.
 FirstOpt: First Example Option
@@ -917,6 +920,9 @@
   </si>
   <si>
     <t>https://www.morphosource.org/banner_image.png</t>
+  </si>
+  <si>
+    <t>file with space.zip</t>
   </si>
 </sst>
 </file>
@@ -933,47 +939,56 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF272727"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF222222"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1344,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06ED7EC9-286B-1D49-A57D-A989376D77CC}">
-  <dimension ref="A1:CH15"/>
+  <dimension ref="A1:CH16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="47.33203125" bestFit="1" customWidth="1"/>
@@ -3896,6 +3911,141 @@
       <c r="CG15" s="26"/>
       <c r="CH15" s="26"/>
     </row>
+    <row r="16" spans="1:86" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="4"/>
+      <c r="C16" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="F16" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="P16" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q16" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="R16" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="S16" s="27"/>
+      <c r="T16" s="27"/>
+      <c r="U16" s="30"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="30"/>
+      <c r="X16" s="30"/>
+      <c r="Y16" s="27">
+        <v>1.5365230000000001E-2</v>
+      </c>
+      <c r="Z16" s="27">
+        <v>1.5365230000000001E-2</v>
+      </c>
+      <c r="AA16" s="27">
+        <v>1.5365230000000001E-2</v>
+      </c>
+      <c r="AB16" s="27"/>
+      <c r="AC16" s="27"/>
+      <c r="AD16" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="AE16" s="27"/>
+      <c r="AF16" s="26"/>
+      <c r="AG16" s="26"/>
+      <c r="AH16" s="26"/>
+      <c r="AI16" s="26"/>
+      <c r="AJ16" s="26"/>
+      <c r="AK16" s="26"/>
+      <c r="AL16" s="26"/>
+      <c r="AM16" s="26"/>
+      <c r="AN16" s="26"/>
+      <c r="AO16" s="26"/>
+      <c r="AP16" s="26"/>
+      <c r="AQ16" s="26"/>
+      <c r="AR16" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="AS16" s="26"/>
+      <c r="AT16" s="26"/>
+      <c r="AU16" s="26"/>
+      <c r="AV16" s="26"/>
+      <c r="AW16" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="AX16" s="27"/>
+      <c r="AY16" s="27"/>
+      <c r="AZ16" s="27">
+        <v>0.200098</v>
+      </c>
+      <c r="BA16" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="BB16" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="BC16" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="BD16" s="30"/>
+      <c r="BE16" s="27">
+        <v>3</v>
+      </c>
+      <c r="BF16" s="27">
+        <v>1680</v>
+      </c>
+      <c r="BG16" s="27">
+        <v>70</v>
+      </c>
+      <c r="BH16" s="27">
+        <v>1.54E-2</v>
+      </c>
+      <c r="BI16" s="27">
+        <v>220</v>
+      </c>
+      <c r="BJ16" s="26"/>
+      <c r="BK16" s="30"/>
+      <c r="BL16" s="30"/>
+      <c r="BM16" s="30"/>
+      <c r="BN16" s="30"/>
+      <c r="BO16" s="30"/>
+      <c r="BP16" s="30"/>
+      <c r="BQ16" s="30"/>
+      <c r="BR16" s="30"/>
+      <c r="BS16" s="30"/>
+      <c r="BT16" s="30"/>
+      <c r="BU16" s="30"/>
+      <c r="BV16" s="30"/>
+      <c r="BW16" s="30"/>
+      <c r="BX16" s="30"/>
+      <c r="BY16" s="26"/>
+      <c r="BZ16" s="26"/>
+      <c r="CA16" s="26"/>
+      <c r="CB16" s="30"/>
+      <c r="CC16" s="30"/>
+      <c r="CD16" s="30"/>
+      <c r="CE16" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="CF16" s="26"/>
+      <c r="CG16" s="26"/>
+      <c r="CH16" s="26"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/spec/fixtures/batch_submission_manifest_errors_test.xlsx
+++ b/spec/fixtures/batch_submission_manifest_errors_test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smc101/vagrant/morphosource-vagrant/MorphoSource/spec/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD27215-A2CE-764D-8931-59FD4D7C1FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717466AA-632E-1F40-A810-73A630BAEECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="32000" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="276">
   <si>
     <t>Field Section</t>
   </si>
@@ -278,9 +278,6 @@
   </si>
   <si>
     <t>Ignore this in most use cases! Parent media filename OR URL endpoint link for downloading parent media file</t>
-  </si>
-  <si>
-    <t>iDigBio UUID for specimen record</t>
   </si>
   <si>
     <t>Collection code modifier (e.g., "VP-", typically designates a sub-collection within a repository. Not a universal element because not all repositories have sub-collections. However, this field is critical when applicable to avoid confusing specimens from different sub-collections. Please make sure you do not incorrectly omit a collection code fromt the specimen identifier</t>
@@ -575,9 +572,6 @@
     <t>biological_specimen.ms_id</t>
   </si>
   <si>
-    <t>biological_specimen.idigbio_uuid</t>
-  </si>
-  <si>
     <t>biological_specimen.occurrence_id</t>
   </si>
   <si>
@@ -870,9 +864,6 @@
   </si>
   <si>
     <t>not_both</t>
-  </si>
-  <si>
-    <t>ce447a9f-1500-43d6-83c2-59de00c6ca9c</t>
   </si>
   <si>
     <t>Filter</t>
@@ -923,13 +914,16 @@
   </si>
   <si>
     <t>file with space.zip</t>
+  </si>
+  <si>
+    <t>urn:catalog:CM:VP:19998</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -994,6 +988,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF333333"/>
+      <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1084,7 +1084,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1143,6 +1143,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1359,15 +1360,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06ED7EC9-286B-1D49-A57D-A989376D77CC}">
-  <dimension ref="A1:CH16"/>
+  <dimension ref="A1:CG16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="47.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="18.1640625" customWidth="1"/>
+    <col min="53" max="53" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:86" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:85" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1405,8 +1406,8 @@
       <c r="M1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="11" t="s">
-        <v>3</v>
+      <c r="N1" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>4</v>
@@ -1436,7 +1437,7 @@
         <v>4</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y1" s="2" t="s">
         <v>5</v>
@@ -1451,13 +1452,13 @@
         <v>5</v>
       </c>
       <c r="AC1" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE1" s="2" t="s">
         <v>7</v>
+      </c>
+      <c r="AE1" s="14" t="s">
+        <v>8</v>
       </c>
       <c r="AF1" s="14" t="s">
         <v>8</v>
@@ -1495,8 +1496,8 @@
       <c r="AQ1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AR1" s="14" t="s">
-        <v>8</v>
+      <c r="AR1" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="AS1" s="3" t="s">
         <v>9</v>
@@ -1504,8 +1505,8 @@
       <c r="AT1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AU1" s="3" t="s">
-        <v>9</v>
+      <c r="AU1" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="AV1" s="6" t="s">
         <v>10</v>
@@ -1517,7 +1518,7 @@
         <v>10</v>
       </c>
       <c r="AY1" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ1" s="6" t="s">
         <v>11</v>
@@ -1595,13 +1596,13 @@
         <v>11</v>
       </c>
       <c r="BY1" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BZ1" s="6" t="s">
         <v>12</v>
       </c>
       <c r="CA1" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CB1" s="6" t="s">
         <v>13</v>
@@ -1609,8 +1610,8 @@
       <c r="CC1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="CD1" s="6" t="s">
-        <v>13</v>
+      <c r="CD1" s="20" t="s">
+        <v>14</v>
       </c>
       <c r="CE1" s="20" t="s">
         <v>14</v>
@@ -1621,11 +1622,8 @@
       <c r="CG1" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="CH1" s="20" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="2" spans="1:86" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:85" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
@@ -1645,225 +1643,224 @@
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
+      <c r="N2" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="O2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE2" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF2" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG2" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH2" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI2" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ2" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="AK2" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="AL2" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM2" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN2" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="AO2" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP2" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="AQ2" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="AR2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AS2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AT2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AU2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AV2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="T2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W2" s="2" t="s">
+      <c r="AW2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AX2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF2" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG2" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH2" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="AI2" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ2" s="14" t="s">
+      <c r="AY2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AZ2" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="BA2" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="BB2" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="BC2" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="BD2" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE2" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG2" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI2" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ2" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK2" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL2" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM2" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP2" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ2" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR2" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS2" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT2" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU2" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV2" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW2" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="BX2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="BY2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="BZ2" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="CA2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="CB2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="CC2" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="CD2" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="CE2" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="CF2" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="CG2" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="AK2" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="AL2" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="AM2" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN2" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="AO2" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="AP2" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AQ2" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="AR2" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AS2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AT2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="AU2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="AV2" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="AW2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="AX2" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="AY2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="AZ2" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="BA2" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="BB2" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="BC2" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD2" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="BE2" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="BF2" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="BG2" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="BH2" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="BI2" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="BJ2" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="BK2" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="BL2" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="BM2" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="BN2" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="BO2" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="BP2" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="BQ2" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="BR2" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="BS2" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="BT2" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="BU2" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="BV2" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="BW2" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="BX2" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="BY2" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="BZ2" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="CA2" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="CB2" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="CC2" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="CD2" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="CE2" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="CF2" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="CG2" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="CH2" s="20" t="s">
-        <v>39</v>
-      </c>
     </row>
-    <row r="3" spans="1:86" ht="139.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:85" ht="139.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
         <v>81</v>
       </c>
@@ -1878,59 +1875,57 @@
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="32" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>85</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="10"/>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
       <c r="M3" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="O3" s="12" t="s">
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
       <c r="R3" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="S3" s="12" t="s">
+      <c r="S3" s="2"/>
+      <c r="T3" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="T3" s="2"/>
-      <c r="U3" s="12" t="s">
+      <c r="U3" s="12"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="V3" s="12"/>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
       <c r="Y3" s="13" t="s">
         <v>93</v>
       </c>
       <c r="Z3" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="AA3" s="13" t="s">
+      <c r="AA3" s="12" t="s">
         <v>95</v>
       </c>
       <c r="AB3" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="AC3" s="12" t="s">
-        <v>97</v>
-      </c>
+      <c r="AC3" s="2"/>
       <c r="AD3" s="2"/>
-      <c r="AE3" s="2"/>
+      <c r="AE3" s="14"/>
       <c r="AF3" s="14"/>
       <c r="AG3" s="14"/>
       <c r="AH3" s="14"/>
@@ -1942,26 +1937,28 @@
       <c r="AN3" s="14"/>
       <c r="AO3" s="14"/>
       <c r="AP3" s="14"/>
-      <c r="AQ3" s="14"/>
-      <c r="AR3" s="14" t="s">
-        <v>98</v>
-      </c>
+      <c r="AQ3" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR3" s="3"/>
       <c r="AS3" s="3"/>
       <c r="AT3" s="3"/>
-      <c r="AU3" s="3"/>
+      <c r="AU3" s="6"/>
       <c r="AV3" s="6"/>
-      <c r="AW3" s="6"/>
-      <c r="AX3" s="15" t="s">
+      <c r="AW3" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="AX3" s="15"/>
+      <c r="AY3" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="AY3" s="15"/>
       <c r="AZ3" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="BA3" s="16" t="s">
+      <c r="BA3" s="16"/>
+      <c r="BB3" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="BB3" s="16"/>
       <c r="BC3" s="16" t="s">
         <v>102</v>
       </c>
@@ -1983,14 +1980,14 @@
       <c r="BI3" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="BJ3" s="16" t="s">
+      <c r="BJ3" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="BK3" s="15" t="s">
+      <c r="BK3" s="15"/>
+      <c r="BL3" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="BL3" s="15"/>
-      <c r="BM3" s="15" t="s">
+      <c r="BM3" s="17" t="s">
         <v>111</v>
       </c>
       <c r="BN3" s="17" t="s">
@@ -2002,7 +1999,7 @@
       <c r="BP3" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="BQ3" s="17" t="s">
+      <c r="BQ3" s="15" t="s">
         <v>115</v>
       </c>
       <c r="BR3" s="15" t="s">
@@ -2023,10 +2020,10 @@
       <c r="BW3" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="BX3" s="15" t="s">
+      <c r="BX3" s="16"/>
+      <c r="BY3" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="BY3" s="16"/>
       <c r="BZ3" s="15" t="s">
         <v>123</v>
       </c>
@@ -2034,55 +2031,52 @@
         <v>124</v>
       </c>
       <c r="CB3" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="CC3" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="CC3" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="CD3" s="16" t="s">
-        <v>126</v>
-      </c>
+      <c r="CD3" s="20"/>
       <c r="CE3" s="20"/>
       <c r="CF3" s="20"/>
       <c r="CG3" s="20"/>
-      <c r="CH3" s="20"/>
     </row>
-    <row r="4" spans="1:86" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:85" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>129</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
+      <c r="J4" s="11" t="s">
+        <v>129</v>
+      </c>
       <c r="K4" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
@@ -2091,20 +2085,20 @@
       <c r="U4" s="2"/>
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
+      <c r="X4" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="Y4" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="AA4" s="2" t="s">
-        <v>131</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="AA4" s="2"/>
       <c r="AB4" s="2"/>
       <c r="AC4" s="2"/>
       <c r="AD4" s="2"/>
-      <c r="AE4" s="2"/>
+      <c r="AE4" s="14"/>
       <c r="AF4" s="14"/>
       <c r="AG4" s="14"/>
       <c r="AH4" s="14"/>
@@ -2117,10 +2111,10 @@
       <c r="AO4" s="14"/>
       <c r="AP4" s="14"/>
       <c r="AQ4" s="14"/>
-      <c r="AR4" s="14"/>
+      <c r="AR4" s="3"/>
       <c r="AS4" s="3"/>
       <c r="AT4" s="3"/>
-      <c r="AU4" s="3"/>
+      <c r="AU4" s="6"/>
       <c r="AV4" s="6"/>
       <c r="AW4" s="6"/>
       <c r="AX4" s="6"/>
@@ -2155,286 +2149,282 @@
       <c r="CA4" s="6"/>
       <c r="CB4" s="6"/>
       <c r="CC4" s="6"/>
-      <c r="CD4" s="6"/>
+      <c r="CD4" s="20"/>
       <c r="CE4" s="20"/>
       <c r="CF4" s="20"/>
       <c r="CG4" s="20"/>
-      <c r="CH4" s="20"/>
     </row>
-    <row r="5" spans="1:86" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:85" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="C5" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="F5" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F5" s="31" t="s">
-        <v>135</v>
-      </c>
       <c r="G5" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="N5" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>134</v>
       </c>
       <c r="Q5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="V5" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="W5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AB5" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="AC5" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="T5" s="2" t="s">
+      <c r="AD5" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="U5" s="2" t="s">
+      <c r="AE5" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AF5" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AG5" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH5" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AI5" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AJ5" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="AK5" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="AL5" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AM5" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AN5" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AO5" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="AP5" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="V5" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="W5" s="2" t="s">
+      <c r="AQ5" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="AR5" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AS5" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AT5" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AU5" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="AV5" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="AW5" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="AX5" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="AY5" s="18" t="s">
         <v>136</v>
-      </c>
-      <c r="X5" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y5" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="Z5" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="AA5" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="AB5" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="AC5" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AD5" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AE5" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AF5" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="AG5" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="AH5" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="AI5" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="AJ5" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK5" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="AL5" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="AM5" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN5" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="AO5" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="AP5" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="AQ5" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="AR5" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="AS5" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="AT5" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="AU5" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="AV5" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="AW5" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="AX5" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="AY5" s="6" t="s">
-        <v>134</v>
       </c>
       <c r="AZ5" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="BA5" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="BB5" s="33" t="s">
-        <v>135</v>
+      <c r="BA5" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="BB5" s="18" t="s">
+        <v>137</v>
       </c>
       <c r="BC5" s="18" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="BD5" s="18" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="BE5" s="18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="BF5" s="18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="BG5" s="18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="BH5" s="18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="BI5" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="BJ5" s="18" t="s">
-        <v>134</v>
+        <v>133</v>
+      </c>
+      <c r="BJ5" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="BK5" s="6" t="s">
         <v>134</v>
       </c>
       <c r="BL5" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="BM5" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
+      </c>
+      <c r="BM5" s="19" t="s">
+        <v>138</v>
       </c>
       <c r="BN5" s="19" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="BO5" s="19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="BP5" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="BQ5" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
+      </c>
+      <c r="BQ5" s="6" t="s">
+        <v>134</v>
       </c>
       <c r="BR5" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="BS5" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="BT5" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="BU5" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="BV5" s="6" t="s">
         <v>137</v>
       </c>
       <c r="BW5" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BX5" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="BY5" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="BZ5" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="CA5" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="CB5" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="CC5" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="CD5" s="6" t="s">
+      <c r="CD5" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="CE5" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="CE5" s="20" t="s">
-        <v>134</v>
-      </c>
       <c r="CF5" s="20" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="CG5" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="CH5" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:86" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:85" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -2443,12 +2433,12 @@
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
       <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
+      <c r="N6" s="2"/>
       <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2" t="s">
-        <v>143</v>
-      </c>
+      <c r="P6" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
@@ -2459,16 +2449,16 @@
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
       <c r="AA6" s="2"/>
-      <c r="AB6" s="2"/>
+      <c r="AB6" s="2" t="s">
+        <v>143</v>
+      </c>
       <c r="AC6" s="2" t="s">
         <v>144</v>
       </c>
       <c r="AD6" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="AE6" s="2" t="s">
-        <v>146</v>
-      </c>
+      <c r="AE6" s="14"/>
       <c r="AF6" s="14"/>
       <c r="AG6" s="14"/>
       <c r="AH6" s="14"/>
@@ -2479,23 +2469,23 @@
       <c r="AM6" s="14"/>
       <c r="AN6" s="14"/>
       <c r="AO6" s="14"/>
-      <c r="AP6" s="14"/>
-      <c r="AQ6" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="AR6" s="14"/>
+      <c r="AP6" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="AQ6" s="14"/>
+      <c r="AR6" s="3"/>
       <c r="AS6" s="3"/>
       <c r="AT6" s="3"/>
-      <c r="AU6" s="3"/>
+      <c r="AU6" s="6"/>
       <c r="AV6" s="6"/>
       <c r="AW6" s="6"/>
       <c r="AX6" s="6"/>
       <c r="AY6" s="6"/>
       <c r="AZ6" s="6"/>
-      <c r="BA6" s="6"/>
-      <c r="BB6" s="33" t="s">
-        <v>271</v>
-      </c>
+      <c r="BA6" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="BB6" s="6"/>
       <c r="BC6" s="6"/>
       <c r="BD6" s="6"/>
       <c r="BE6" s="6"/>
@@ -2504,489 +2494,482 @@
       <c r="BH6" s="6"/>
       <c r="BI6" s="6"/>
       <c r="BJ6" s="6"/>
-      <c r="BK6" s="6"/>
+      <c r="BK6" s="6" t="s">
+        <v>147</v>
+      </c>
       <c r="BL6" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="BM6" s="6" t="s">
-        <v>149</v>
-      </c>
+      <c r="BM6" s="6"/>
       <c r="BN6" s="6"/>
       <c r="BO6" s="6"/>
       <c r="BP6" s="6"/>
-      <c r="BQ6" s="6"/>
-      <c r="BR6" s="6" t="s">
-        <v>150</v>
-      </c>
+      <c r="BQ6" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="BR6" s="6"/>
       <c r="BS6" s="6"/>
       <c r="BT6" s="6"/>
       <c r="BU6" s="6"/>
       <c r="BV6" s="6"/>
       <c r="BW6" s="6"/>
-      <c r="BX6" s="6"/>
+      <c r="BX6" s="6" t="s">
+        <v>150</v>
+      </c>
       <c r="BY6" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="BZ6" s="6" t="s">
-        <v>152</v>
-      </c>
+      <c r="BZ6" s="6"/>
       <c r="CA6" s="6"/>
       <c r="CB6" s="6"/>
-      <c r="CC6" s="6"/>
-      <c r="CD6" s="6" t="s">
-        <v>153</v>
-      </c>
+      <c r="CC6" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="CD6" s="20"/>
       <c r="CE6" s="20"/>
       <c r="CF6" s="20"/>
       <c r="CG6" s="20"/>
-      <c r="CH6" s="20"/>
     </row>
-    <row r="7" spans="1:86" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:85" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="31" t="s">
+        <v>263</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F7" s="31" t="s">
-        <v>266</v>
-      </c>
-      <c r="G7" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="I7" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="J7" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="K7" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="L7" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="M7" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="N7" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="N7" s="11" t="s">
+      <c r="O7" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="O7" s="22" t="s">
+      <c r="P7" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="P7" s="22" t="s">
+      <c r="Q7" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Q7" s="22" t="s">
+      <c r="R7" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="X7" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="Y7" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="Y7" s="22" t="s">
+      <c r="Z7" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="Z7" s="22" t="s">
+      <c r="AA7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AA7" s="22" t="s">
+      <c r="AB7" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="AB7" s="2" t="s">
+      <c r="AC7" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="AC7" s="2" t="s">
+      <c r="AD7" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="AD7" s="22" t="s">
+      <c r="AE7" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="AE7" s="2" t="s">
+      <c r="AF7" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="AF7" s="23" t="s">
+      <c r="AG7" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="AG7" s="23" t="s">
+      <c r="AH7" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="AH7" s="23" t="s">
+      <c r="AI7" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="AI7" s="23" t="s">
+      <c r="AJ7" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="AJ7" s="23" t="s">
+      <c r="AK7" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="AK7" s="23" t="s">
+      <c r="AL7" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="AL7" s="23" t="s">
+      <c r="AM7" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="AM7" s="23" t="s">
+      <c r="AN7" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="AN7" s="23" t="s">
+      <c r="AO7" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="AO7" s="23" t="s">
+      <c r="AP7" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="AP7" s="23" t="s">
+      <c r="AQ7" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="AQ7" s="23" t="s">
+      <c r="AR7" s="26" t="s">
         <v>195</v>
       </c>
-      <c r="AR7" s="23" t="s">
+      <c r="AS7" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="AS7" s="26" t="s">
+      <c r="AT7" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="AT7" s="26" t="s">
+      <c r="AU7" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="AU7" s="26" t="s">
+      <c r="AV7" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="AV7" s="26" t="s">
+      <c r="AW7" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="AW7" s="26" t="s">
+      <c r="AX7" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="AX7" s="6" t="s">
+      <c r="AY7" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="AY7" s="6" t="s">
+      <c r="AZ7" s="26" t="s">
         <v>203</v>
       </c>
-      <c r="AZ7" s="26" t="s">
+      <c r="BA7" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="BB7" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="BA7" s="26" t="s">
+      <c r="BC7" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="BD7" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="BB7" s="26" t="s">
-        <v>272</v>
-      </c>
-      <c r="BC7" s="26" t="s">
+      <c r="BE7" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="BD7" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="BE7" s="26" t="s">
+      <c r="BF7" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="BF7" s="26" t="s">
+      <c r="BG7" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="BG7" s="26" t="s">
+      <c r="BH7" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="BH7" s="26" t="s">
+      <c r="BI7" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="BI7" s="26" t="s">
+      <c r="BJ7" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="BJ7" s="26" t="s">
+      <c r="BK7" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="BK7" s="6" t="s">
+      <c r="BL7" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="BL7" s="6" t="s">
+      <c r="BM7" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="BM7" s="6" t="s">
+      <c r="BN7" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="BN7" s="6" t="s">
+      <c r="BO7" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="BO7" s="6" t="s">
+      <c r="BP7" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="BP7" s="6" t="s">
+      <c r="BQ7" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="BQ7" s="6" t="s">
+      <c r="BR7" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="BR7" s="6" t="s">
+      <c r="BS7" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="BS7" s="6" t="s">
+      <c r="BT7" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="BT7" s="6" t="s">
+      <c r="BU7" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="BU7" s="6" t="s">
+      <c r="BV7" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="BV7" s="6" t="s">
+      <c r="BW7" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="BW7" s="6" t="s">
+      <c r="BX7" s="24" t="s">
         <v>225</v>
       </c>
-      <c r="BX7" s="6" t="s">
+      <c r="BY7" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="BY7" s="24" t="s">
+      <c r="BZ7" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="BZ7" s="6" t="s">
+      <c r="CA7" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="CA7" s="6" t="s">
+      <c r="CB7" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="CB7" s="6" t="s">
+      <c r="CC7" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="CC7" s="6" t="s">
+      <c r="CD7" s="26" t="s">
         <v>231</v>
       </c>
-      <c r="CD7" s="6" t="s">
+      <c r="CE7" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="CE7" s="26" t="s">
+      <c r="CF7" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="CF7" s="26" t="s">
+      <c r="CG7" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="CG7" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="CH7" s="26" t="s">
-        <v>236</v>
-      </c>
     </row>
-    <row r="8" spans="1:86" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:85" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
       <c r="B8" s="25"/>
       <c r="C8" s="26" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="I8" s="26"/>
       <c r="J8" s="26" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="K8" s="26" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="L8" s="26" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="M8" s="26" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="N8" s="26" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="O8" s="26" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P8" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q8" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="Q8" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="R8" s="26" t="s">
-        <v>242</v>
-      </c>
+      <c r="R8" s="27"/>
       <c r="S8" s="27"/>
-      <c r="T8" s="27"/>
-      <c r="U8" s="28"/>
-      <c r="V8" s="28" t="s">
-        <v>275</v>
-      </c>
-      <c r="W8" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="X8" s="28"/>
-      <c r="Y8" s="27">
+      <c r="T8" s="28"/>
+      <c r="U8" s="28" t="s">
+        <v>272</v>
+      </c>
+      <c r="V8" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="W8" s="28"/>
+      <c r="X8" s="27">
         <v>2.169024E-2</v>
       </c>
-      <c r="Z8" s="27"/>
-      <c r="AA8" s="27" t="s">
-        <v>256</v>
-      </c>
-      <c r="AB8" s="27"/>
+      <c r="Y8" s="27"/>
+      <c r="Z8" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="AA8" s="27"/>
+      <c r="AB8" s="26" t="s">
+        <v>254</v>
+      </c>
       <c r="AC8" s="26" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AD8" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="AE8" s="26" t="s">
-        <v>256</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="AE8" s="26"/>
       <c r="AF8" s="26"/>
-      <c r="AG8" s="26"/>
-      <c r="AH8" s="26" t="s">
-        <v>256</v>
-      </c>
+      <c r="AG8" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="AH8" s="26"/>
       <c r="AI8" s="26"/>
       <c r="AJ8" s="26"/>
       <c r="AK8" s="26"/>
       <c r="AL8" s="26"/>
       <c r="AM8" s="26"/>
       <c r="AN8" s="26"/>
-      <c r="AO8" s="26"/>
+      <c r="AO8" s="26" t="s">
+        <v>254</v>
+      </c>
       <c r="AP8" s="26" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AQ8" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="AR8" s="26" t="s">
-        <v>244</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="AR8" s="26"/>
       <c r="AS8" s="26"/>
       <c r="AT8" s="26"/>
       <c r="AU8" s="26"/>
-      <c r="AV8" s="26"/>
-      <c r="AW8" s="26" t="s">
-        <v>269</v>
-      </c>
+      <c r="AV8" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="AW8" s="27"/>
       <c r="AX8" s="27"/>
-      <c r="AY8" s="27"/>
+      <c r="AY8" s="26" t="s">
+        <v>254</v>
+      </c>
       <c r="AZ8" s="26" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="BA8" s="26" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="BB8" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="BC8" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="BD8" s="29"/>
-      <c r="BE8" s="27">
+        <v>242</v>
+      </c>
+      <c r="BC8" s="29"/>
+      <c r="BD8" s="27">
         <v>3</v>
       </c>
-      <c r="BF8" s="26" t="s">
-        <v>256</v>
+      <c r="BE8" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="BF8" s="27">
+        <v>70</v>
       </c>
       <c r="BG8" s="27">
-        <v>70</v>
+        <v>1.4E-2</v>
       </c>
       <c r="BH8" s="27">
-        <v>1.4E-2</v>
-      </c>
-      <c r="BI8" s="27">
         <v>200</v>
       </c>
-      <c r="BJ8" s="26"/>
-      <c r="BK8" s="29"/>
+      <c r="BI8" s="26"/>
+      <c r="BJ8" s="29"/>
+      <c r="BK8" s="26" t="s">
+        <v>254</v>
+      </c>
       <c r="BL8" s="26" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="BM8" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="BN8" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="BO8" s="29"/>
-      <c r="BP8" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="BQ8" s="29"/>
-      <c r="BR8" s="26" t="s">
-        <v>256</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="BN8" s="29"/>
+      <c r="BO8" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="BP8" s="29"/>
+      <c r="BQ8" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="BR8" s="29"/>
       <c r="BS8" s="29"/>
       <c r="BT8" s="29"/>
       <c r="BU8" s="29"/>
       <c r="BV8" s="29"/>
       <c r="BW8" s="29"/>
-      <c r="BX8" s="29"/>
+      <c r="BX8" s="26" t="s">
+        <v>254</v>
+      </c>
       <c r="BY8" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="BZ8" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="CA8" s="26"/>
+        <v>254</v>
+      </c>
+      <c r="BZ8" s="26"/>
+      <c r="CA8" s="29"/>
       <c r="CB8" s="29"/>
-      <c r="CC8" s="29"/>
+      <c r="CC8" s="26" t="s">
+        <v>254</v>
+      </c>
       <c r="CD8" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="CE8" s="26" t="s">
-        <v>269</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="CE8" s="26"/>
       <c r="CF8" s="26"/>
       <c r="CG8" s="26"/>
-      <c r="CH8" s="26"/>
     </row>
-    <row r="9" spans="1:86" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:85" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="C9" s="26" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D9" s="30"/>
       <c r="E9" s="26" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F9" s="26"/>
       <c r="I9" s="26"/>
@@ -2994,40 +2977,40 @@
       <c r="K9" s="26"/>
       <c r="L9" s="26"/>
       <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
+      <c r="N9" s="26" t="s">
+        <v>237</v>
+      </c>
       <c r="O9" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="P9" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="P9" s="26" t="s">
+      <c r="Q9" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="Q9" s="26" t="s">
-        <v>241</v>
-      </c>
-      <c r="R9" s="26" t="s">
-        <v>242</v>
-      </c>
+      <c r="R9" s="27"/>
       <c r="S9" s="27"/>
-      <c r="T9" s="27"/>
+      <c r="T9" s="30"/>
       <c r="U9" s="30"/>
       <c r="V9" s="30"/>
       <c r="W9" s="30"/>
-      <c r="X9" s="30"/>
+      <c r="X9" s="27">
+        <v>2.725352E-2</v>
+      </c>
       <c r="Y9" s="27">
         <v>2.725352E-2</v>
       </c>
       <c r="Z9" s="27">
         <v>2.725352E-2</v>
       </c>
-      <c r="AA9" s="27">
-        <v>2.725352E-2</v>
-      </c>
+      <c r="AA9" s="27"/>
       <c r="AB9" s="27"/>
-      <c r="AC9" s="27"/>
-      <c r="AD9" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="AE9" s="27"/>
+      <c r="AC9" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="AD9" s="27"/>
+      <c r="AE9" s="26"/>
       <c r="AF9" s="26"/>
       <c r="AG9" s="26"/>
       <c r="AH9" s="26"/>
@@ -3039,48 +3022,48 @@
       <c r="AN9" s="26"/>
       <c r="AO9" s="26"/>
       <c r="AP9" s="26"/>
-      <c r="AQ9" s="26"/>
-      <c r="AR9" s="26" t="s">
-        <v>244</v>
-      </c>
+      <c r="AQ9" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="AR9" s="26"/>
       <c r="AS9" s="26"/>
       <c r="AT9" s="26"/>
       <c r="AU9" s="26"/>
-      <c r="AV9" s="26"/>
-      <c r="AW9" s="26" t="s">
-        <v>269</v>
-      </c>
+      <c r="AV9" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="AW9" s="27"/>
       <c r="AX9" s="27"/>
-      <c r="AY9" s="27"/>
-      <c r="AZ9" s="27">
+      <c r="AY9" s="27">
         <v>0.200098</v>
       </c>
+      <c r="AZ9" s="26" t="s">
+        <v>243</v>
+      </c>
       <c r="BA9" s="26" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="BB9" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="BC9" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="BD9" s="30"/>
+        <v>242</v>
+      </c>
+      <c r="BC9" s="30"/>
+      <c r="BD9" s="27">
+        <v>3</v>
+      </c>
       <c r="BE9" s="27">
-        <v>3</v>
+        <v>1680</v>
       </c>
       <c r="BF9" s="27">
-        <v>1680</v>
+        <v>70</v>
       </c>
       <c r="BG9" s="27">
-        <v>70</v>
+        <v>1.54E-2</v>
       </c>
       <c r="BH9" s="27">
-        <v>1.54E-2</v>
-      </c>
-      <c r="BI9" s="27">
         <v>220</v>
       </c>
-      <c r="BJ9" s="26"/>
+      <c r="BI9" s="26"/>
+      <c r="BJ9" s="30"/>
       <c r="BK9" s="30"/>
       <c r="BL9" s="30"/>
       <c r="BM9" s="30"/>
@@ -3094,76 +3077,75 @@
       <c r="BU9" s="30"/>
       <c r="BV9" s="30"/>
       <c r="BW9" s="30"/>
-      <c r="BX9" s="30"/>
+      <c r="BX9" s="26"/>
       <c r="BY9" s="26"/>
       <c r="BZ9" s="26"/>
-      <c r="CA9" s="26"/>
+      <c r="CA9" s="30"/>
       <c r="CB9" s="30"/>
       <c r="CC9" s="30"/>
-      <c r="CD9" s="30"/>
-      <c r="CE9" s="26" t="s">
-        <v>269</v>
-      </c>
+      <c r="CD9" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="CE9" s="26"/>
       <c r="CF9" s="26"/>
       <c r="CG9" s="26"/>
-      <c r="CH9" s="26"/>
     </row>
-    <row r="10" spans="1:86" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:85" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
       <c r="C10" s="26" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D10" s="30"/>
       <c r="E10" s="26" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H10" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I10" s="26"/>
-      <c r="J10" s="26" t="s">
-        <v>261</v>
+      <c r="J10" s="36" t="s">
+        <v>275</v>
       </c>
       <c r="K10" s="26"/>
       <c r="L10" s="26"/>
       <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
+      <c r="N10" s="26" t="s">
+        <v>237</v>
+      </c>
       <c r="O10" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="P10" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="P10" s="26" t="s">
+      <c r="Q10" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="Q10" s="26" t="s">
-        <v>241</v>
-      </c>
-      <c r="R10" s="26" t="s">
-        <v>242</v>
-      </c>
+      <c r="R10" s="27"/>
       <c r="S10" s="27"/>
-      <c r="T10" s="27"/>
+      <c r="T10" s="30"/>
       <c r="U10" s="30"/>
       <c r="V10" s="30"/>
       <c r="W10" s="30"/>
-      <c r="X10" s="30"/>
+      <c r="X10" s="27">
+        <v>1.5365230000000001E-2</v>
+      </c>
       <c r="Y10" s="27">
         <v>1.5365230000000001E-2</v>
       </c>
       <c r="Z10" s="27">
         <v>1.5365230000000001E-2</v>
       </c>
-      <c r="AA10" s="27">
-        <v>1.5365230000000001E-2</v>
-      </c>
+      <c r="AA10" s="27"/>
       <c r="AB10" s="27"/>
-      <c r="AC10" s="27"/>
-      <c r="AD10" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="AE10" s="27"/>
+      <c r="AC10" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="AD10" s="27"/>
+      <c r="AE10" s="26"/>
       <c r="AF10" s="26"/>
       <c r="AG10" s="26"/>
       <c r="AH10" s="26"/>
@@ -3175,48 +3157,48 @@
       <c r="AN10" s="26"/>
       <c r="AO10" s="26"/>
       <c r="AP10" s="26"/>
-      <c r="AQ10" s="26"/>
-      <c r="AR10" s="26" t="s">
-        <v>244</v>
-      </c>
+      <c r="AQ10" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="AR10" s="26"/>
       <c r="AS10" s="26"/>
       <c r="AT10" s="26"/>
       <c r="AU10" s="26"/>
-      <c r="AV10" s="26"/>
-      <c r="AW10" s="26" t="s">
-        <v>269</v>
-      </c>
+      <c r="AV10" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="AW10" s="27"/>
       <c r="AX10" s="27"/>
-      <c r="AY10" s="27"/>
-      <c r="AZ10" s="27">
+      <c r="AY10" s="27">
         <v>0.200098</v>
       </c>
+      <c r="AZ10" s="26" t="s">
+        <v>243</v>
+      </c>
       <c r="BA10" s="26" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="BB10" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="BC10" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="BD10" s="30"/>
+        <v>242</v>
+      </c>
+      <c r="BC10" s="30"/>
+      <c r="BD10" s="27">
+        <v>3</v>
+      </c>
       <c r="BE10" s="27">
-        <v>3</v>
+        <v>1680</v>
       </c>
       <c r="BF10" s="27">
-        <v>1680</v>
+        <v>70</v>
       </c>
       <c r="BG10" s="27">
-        <v>70</v>
+        <v>1.54E-2</v>
       </c>
       <c r="BH10" s="27">
-        <v>1.54E-2</v>
-      </c>
-      <c r="BI10" s="27">
         <v>220</v>
       </c>
-      <c r="BJ10" s="26"/>
+      <c r="BI10" s="26"/>
+      <c r="BJ10" s="30"/>
       <c r="BK10" s="30"/>
       <c r="BL10" s="30"/>
       <c r="BM10" s="30"/>
@@ -3230,76 +3212,75 @@
       <c r="BU10" s="30"/>
       <c r="BV10" s="30"/>
       <c r="BW10" s="30"/>
-      <c r="BX10" s="30"/>
+      <c r="BX10" s="26"/>
       <c r="BY10" s="26"/>
       <c r="BZ10" s="26"/>
-      <c r="CA10" s="26"/>
+      <c r="CA10" s="30"/>
       <c r="CB10" s="30"/>
       <c r="CC10" s="30"/>
-      <c r="CD10" s="30"/>
-      <c r="CE10" s="26" t="s">
-        <v>269</v>
-      </c>
+      <c r="CD10" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="CE10" s="26"/>
       <c r="CF10" s="26"/>
       <c r="CG10" s="26"/>
-      <c r="CH10" s="26"/>
     </row>
-    <row r="11" spans="1:86" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:85" ht="16" x14ac:dyDescent="0.2">
       <c r="C11" s="26" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D11" s="30"/>
       <c r="E11" s="26" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G11" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H11" s="30"/>
       <c r="I11" s="26" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="J11" s="26"/>
       <c r="K11" s="26"/>
       <c r="L11" s="26"/>
       <c r="M11" s="26"/>
-      <c r="N11" s="26"/>
+      <c r="N11" s="26" t="s">
+        <v>247</v>
+      </c>
       <c r="O11" s="26" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="P11" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q11" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="Q11" s="26" t="s">
-        <v>241</v>
-      </c>
-      <c r="R11" s="26" t="s">
-        <v>242</v>
-      </c>
+      <c r="R11" s="27"/>
       <c r="S11" s="27"/>
-      <c r="T11" s="27"/>
+      <c r="T11" s="30"/>
       <c r="U11" s="30"/>
       <c r="V11" s="30"/>
       <c r="W11" s="30"/>
-      <c r="X11" s="30"/>
+      <c r="X11" s="27">
+        <v>4.8993170000000003E-2</v>
+      </c>
       <c r="Y11" s="27">
         <v>4.8993170000000003E-2</v>
       </c>
       <c r="Z11" s="27">
         <v>4.8993170000000003E-2</v>
       </c>
-      <c r="AA11" s="27">
-        <v>4.8993170000000003E-2</v>
-      </c>
+      <c r="AA11" s="27"/>
       <c r="AB11" s="27"/>
-      <c r="AC11" s="27"/>
-      <c r="AD11" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="AE11" s="27"/>
+      <c r="AC11" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="AD11" s="27"/>
+      <c r="AE11" s="26"/>
       <c r="AF11" s="26"/>
       <c r="AG11" s="26"/>
       <c r="AH11" s="26"/>
@@ -3311,48 +3292,48 @@
       <c r="AN11" s="26"/>
       <c r="AO11" s="26"/>
       <c r="AP11" s="26"/>
-      <c r="AQ11" s="26"/>
-      <c r="AR11" s="26" t="s">
-        <v>244</v>
-      </c>
+      <c r="AQ11" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="AR11" s="26"/>
       <c r="AS11" s="26"/>
       <c r="AT11" s="26"/>
       <c r="AU11" s="26"/>
-      <c r="AV11" s="26"/>
-      <c r="AW11" s="26" t="s">
-        <v>269</v>
-      </c>
+      <c r="AV11" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="AW11" s="27"/>
       <c r="AX11" s="27"/>
-      <c r="AY11" s="27"/>
-      <c r="AZ11" s="27">
+      <c r="AY11" s="27">
         <v>0.200098</v>
       </c>
+      <c r="AZ11" s="26" t="s">
+        <v>243</v>
+      </c>
       <c r="BA11" s="26" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="BB11" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="BC11" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="BD11" s="30"/>
+        <v>242</v>
+      </c>
+      <c r="BC11" s="30"/>
+      <c r="BD11" s="27">
+        <v>3</v>
+      </c>
       <c r="BE11" s="27">
-        <v>3</v>
+        <v>600</v>
       </c>
       <c r="BF11" s="27">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="BG11" s="27">
-        <v>70</v>
+        <v>1.54E-2</v>
       </c>
       <c r="BH11" s="27">
-        <v>1.54E-2</v>
-      </c>
-      <c r="BI11" s="27">
         <v>220</v>
       </c>
-      <c r="BJ11" s="26"/>
+      <c r="BI11" s="26"/>
+      <c r="BJ11" s="30"/>
       <c r="BK11" s="30"/>
       <c r="BL11" s="30"/>
       <c r="BM11" s="30"/>
@@ -3366,33 +3347,32 @@
       <c r="BU11" s="30"/>
       <c r="BV11" s="30"/>
       <c r="BW11" s="30"/>
-      <c r="BX11" s="30"/>
+      <c r="BX11" s="26"/>
       <c r="BY11" s="26"/>
       <c r="BZ11" s="26"/>
-      <c r="CA11" s="26"/>
+      <c r="CA11" s="30"/>
       <c r="CB11" s="30"/>
       <c r="CC11" s="30"/>
-      <c r="CD11" s="30"/>
-      <c r="CE11" s="26" t="s">
-        <v>269</v>
-      </c>
+      <c r="CD11" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="CE11" s="26"/>
       <c r="CF11" s="26"/>
       <c r="CG11" s="26"/>
-      <c r="CH11" s="26"/>
     </row>
-    <row r="12" spans="1:86" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:85" ht="16" x14ac:dyDescent="0.2">
       <c r="C12" s="26" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D12" s="30"/>
       <c r="E12" s="26" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H12" s="30"/>
       <c r="I12" s="26"/>
@@ -3400,40 +3380,40 @@
       <c r="K12" s="26"/>
       <c r="L12" s="26"/>
       <c r="M12" s="26"/>
-      <c r="N12" s="26"/>
+      <c r="N12" s="26" t="s">
+        <v>237</v>
+      </c>
       <c r="O12" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="P12" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="P12" s="26" t="s">
+      <c r="Q12" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="Q12" s="26" t="s">
-        <v>241</v>
-      </c>
-      <c r="R12" s="26" t="s">
-        <v>242</v>
-      </c>
+      <c r="R12" s="27"/>
       <c r="S12" s="27"/>
-      <c r="T12" s="27"/>
+      <c r="T12" s="30"/>
       <c r="U12" s="30"/>
       <c r="V12" s="30"/>
       <c r="W12" s="30"/>
-      <c r="X12" s="30"/>
+      <c r="X12" s="27">
+        <v>1.4276580000000001E-2</v>
+      </c>
       <c r="Y12" s="27">
         <v>1.4276580000000001E-2</v>
       </c>
       <c r="Z12" s="27">
         <v>1.4276580000000001E-2</v>
       </c>
-      <c r="AA12" s="27">
-        <v>1.4276580000000001E-2</v>
-      </c>
+      <c r="AA12" s="27"/>
       <c r="AB12" s="27"/>
-      <c r="AC12" s="27"/>
-      <c r="AD12" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="AE12" s="27"/>
+      <c r="AC12" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="AD12" s="27"/>
+      <c r="AE12" s="26"/>
       <c r="AF12" s="26"/>
       <c r="AG12" s="26"/>
       <c r="AH12" s="26"/>
@@ -3445,48 +3425,48 @@
       <c r="AN12" s="26"/>
       <c r="AO12" s="26"/>
       <c r="AP12" s="26"/>
-      <c r="AQ12" s="26"/>
-      <c r="AR12" s="26" t="s">
-        <v>244</v>
-      </c>
+      <c r="AQ12" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="AR12" s="26"/>
       <c r="AS12" s="26"/>
       <c r="AT12" s="26"/>
       <c r="AU12" s="26"/>
-      <c r="AV12" s="26"/>
-      <c r="AW12" s="26" t="s">
-        <v>269</v>
-      </c>
+      <c r="AV12" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="AW12" s="27"/>
       <c r="AX12" s="27"/>
-      <c r="AY12" s="27"/>
-      <c r="AZ12" s="27">
+      <c r="AY12" s="27">
         <v>0.200098</v>
       </c>
+      <c r="AZ12" s="26" t="s">
+        <v>243</v>
+      </c>
       <c r="BA12" s="26" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="BB12" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="BC12" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="BD12" s="30"/>
+        <v>242</v>
+      </c>
+      <c r="BC12" s="30"/>
+      <c r="BD12" s="27">
+        <v>3</v>
+      </c>
       <c r="BE12" s="27">
-        <v>3</v>
+        <v>1440</v>
       </c>
       <c r="BF12" s="27">
-        <v>1440</v>
+        <v>70</v>
       </c>
       <c r="BG12" s="27">
-        <v>70</v>
+        <v>1.4E-2</v>
       </c>
       <c r="BH12" s="27">
-        <v>1.4E-2</v>
-      </c>
-      <c r="BI12" s="27">
         <v>200</v>
       </c>
-      <c r="BJ12" s="26"/>
+      <c r="BI12" s="26"/>
+      <c r="BJ12" s="30"/>
       <c r="BK12" s="30"/>
       <c r="BL12" s="30"/>
       <c r="BM12" s="30"/>
@@ -3500,28 +3480,27 @@
       <c r="BU12" s="30"/>
       <c r="BV12" s="30"/>
       <c r="BW12" s="30"/>
-      <c r="BX12" s="30"/>
+      <c r="BX12" s="26"/>
       <c r="BY12" s="26"/>
       <c r="BZ12" s="26"/>
-      <c r="CA12" s="26"/>
+      <c r="CA12" s="30"/>
       <c r="CB12" s="30"/>
       <c r="CC12" s="30"/>
-      <c r="CD12" s="30"/>
-      <c r="CE12" s="26" t="s">
-        <v>269</v>
-      </c>
+      <c r="CD12" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="CE12" s="26"/>
       <c r="CF12" s="26"/>
       <c r="CG12" s="26"/>
-      <c r="CH12" s="26"/>
     </row>
-    <row r="13" spans="1:86" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:85" ht="16" x14ac:dyDescent="0.2">
       <c r="C13" s="26" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D13" s="30"/>
       <c r="E13" s="26"/>
       <c r="F13" s="26" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G13" s="30"/>
       <c r="H13" s="30"/>
@@ -3530,40 +3509,40 @@
       <c r="K13" s="26"/>
       <c r="L13" s="26"/>
       <c r="M13" s="26"/>
-      <c r="N13" s="26"/>
+      <c r="N13" s="26" t="s">
+        <v>237</v>
+      </c>
       <c r="O13" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="P13" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="P13" s="26" t="s">
+      <c r="Q13" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="Q13" s="26" t="s">
-        <v>241</v>
-      </c>
-      <c r="R13" s="26" t="s">
-        <v>242</v>
-      </c>
+      <c r="R13" s="27"/>
       <c r="S13" s="27"/>
-      <c r="T13" s="27"/>
+      <c r="T13" s="30"/>
       <c r="U13" s="30"/>
       <c r="V13" s="30"/>
       <c r="W13" s="30"/>
-      <c r="X13" s="30"/>
+      <c r="X13" s="27">
+        <v>2.725352E-2</v>
+      </c>
       <c r="Y13" s="27">
         <v>2.725352E-2</v>
       </c>
       <c r="Z13" s="27">
         <v>2.725352E-2</v>
       </c>
-      <c r="AA13" s="27">
-        <v>2.725352E-2</v>
-      </c>
+      <c r="AA13" s="27"/>
       <c r="AB13" s="27"/>
-      <c r="AC13" s="27"/>
-      <c r="AD13" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="AE13" s="27"/>
+      <c r="AC13" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="AD13" s="27"/>
+      <c r="AE13" s="26"/>
       <c r="AF13" s="26"/>
       <c r="AG13" s="26"/>
       <c r="AH13" s="26"/>
@@ -3575,48 +3554,48 @@
       <c r="AN13" s="26"/>
       <c r="AO13" s="26"/>
       <c r="AP13" s="26"/>
-      <c r="AQ13" s="26"/>
-      <c r="AR13" s="26" t="s">
-        <v>244</v>
-      </c>
+      <c r="AQ13" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="AR13" s="26"/>
       <c r="AS13" s="26"/>
       <c r="AT13" s="26"/>
       <c r="AU13" s="26"/>
-      <c r="AV13" s="26"/>
-      <c r="AW13" s="26" t="s">
-        <v>269</v>
-      </c>
+      <c r="AV13" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="AW13" s="27"/>
       <c r="AX13" s="27"/>
-      <c r="AY13" s="27"/>
-      <c r="AZ13" s="27">
+      <c r="AY13" s="27">
         <v>0.200098</v>
       </c>
+      <c r="AZ13" s="26" t="s">
+        <v>243</v>
+      </c>
       <c r="BA13" s="26" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="BB13" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="BC13" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="BD13" s="30"/>
+        <v>242</v>
+      </c>
+      <c r="BC13" s="30"/>
+      <c r="BD13" s="27">
+        <v>3</v>
+      </c>
       <c r="BE13" s="27">
-        <v>3</v>
+        <v>1680</v>
       </c>
       <c r="BF13" s="27">
-        <v>1680</v>
+        <v>70</v>
       </c>
       <c r="BG13" s="27">
-        <v>70</v>
+        <v>1.54E-2</v>
       </c>
       <c r="BH13" s="27">
-        <v>1.54E-2</v>
-      </c>
-      <c r="BI13" s="27">
         <v>220</v>
       </c>
-      <c r="BJ13" s="26"/>
+      <c r="BI13" s="26"/>
+      <c r="BJ13" s="30"/>
       <c r="BK13" s="30"/>
       <c r="BL13" s="30"/>
       <c r="BM13" s="30"/>
@@ -3630,33 +3609,32 @@
       <c r="BU13" s="30"/>
       <c r="BV13" s="30"/>
       <c r="BW13" s="30"/>
-      <c r="BX13" s="30"/>
+      <c r="BX13" s="26"/>
       <c r="BY13" s="26"/>
       <c r="BZ13" s="26"/>
-      <c r="CA13" s="26"/>
+      <c r="CA13" s="30"/>
       <c r="CB13" s="30"/>
       <c r="CC13" s="30"/>
-      <c r="CD13" s="30"/>
-      <c r="CE13" s="26" t="s">
-        <v>269</v>
-      </c>
+      <c r="CD13" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="CE13" s="26"/>
       <c r="CF13" s="26"/>
       <c r="CG13" s="26"/>
-      <c r="CH13" s="26"/>
     </row>
-    <row r="14" spans="1:86" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:85" ht="16" x14ac:dyDescent="0.2">
       <c r="C14" s="26" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D14" s="30"/>
       <c r="E14" s="26" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G14" s="26" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H14" s="30"/>
       <c r="I14" s="26"/>
@@ -3664,40 +3642,40 @@
       <c r="K14" s="26"/>
       <c r="L14" s="26"/>
       <c r="M14" s="26"/>
-      <c r="N14" s="26"/>
+      <c r="N14" s="26" t="s">
+        <v>237</v>
+      </c>
       <c r="O14" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="P14" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="P14" s="26" t="s">
+      <c r="Q14" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="Q14" s="26" t="s">
-        <v>241</v>
-      </c>
-      <c r="R14" s="26" t="s">
-        <v>242</v>
-      </c>
+      <c r="R14" s="27"/>
       <c r="S14" s="27"/>
-      <c r="T14" s="27"/>
+      <c r="T14" s="30"/>
       <c r="U14" s="30"/>
       <c r="V14" s="30"/>
       <c r="W14" s="30"/>
-      <c r="X14" s="30"/>
+      <c r="X14" s="27">
+        <v>1.4276580000000001E-2</v>
+      </c>
       <c r="Y14" s="27">
         <v>1.4276580000000001E-2</v>
       </c>
       <c r="Z14" s="27">
         <v>1.4276580000000001E-2</v>
       </c>
-      <c r="AA14" s="27">
-        <v>1.4276580000000001E-2</v>
-      </c>
+      <c r="AA14" s="27"/>
       <c r="AB14" s="27"/>
-      <c r="AC14" s="27"/>
-      <c r="AD14" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="AE14" s="27"/>
+      <c r="AC14" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="AD14" s="27"/>
+      <c r="AE14" s="26"/>
       <c r="AF14" s="26"/>
       <c r="AG14" s="26"/>
       <c r="AH14" s="26"/>
@@ -3709,48 +3687,48 @@
       <c r="AN14" s="26"/>
       <c r="AO14" s="26"/>
       <c r="AP14" s="26"/>
-      <c r="AQ14" s="26"/>
-      <c r="AR14" s="26" t="s">
-        <v>244</v>
-      </c>
+      <c r="AQ14" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="AR14" s="26"/>
       <c r="AS14" s="26"/>
       <c r="AT14" s="26"/>
       <c r="AU14" s="26"/>
-      <c r="AV14" s="26"/>
-      <c r="AW14" s="26" t="s">
-        <v>269</v>
-      </c>
+      <c r="AV14" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="AW14" s="27"/>
       <c r="AX14" s="27"/>
-      <c r="AY14" s="27"/>
-      <c r="AZ14" s="27">
+      <c r="AY14" s="27">
         <v>0.200098</v>
       </c>
+      <c r="AZ14" s="26" t="s">
+        <v>243</v>
+      </c>
       <c r="BA14" s="26" t="s">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="BB14" s="26" t="s">
-        <v>274</v>
-      </c>
-      <c r="BC14" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="BD14" s="30"/>
+        <v>242</v>
+      </c>
+      <c r="BC14" s="30"/>
+      <c r="BD14" s="27">
+        <v>3</v>
+      </c>
       <c r="BE14" s="27">
-        <v>3</v>
+        <v>1440</v>
       </c>
       <c r="BF14" s="27">
-        <v>1440</v>
+        <v>70</v>
       </c>
       <c r="BG14" s="27">
-        <v>70</v>
+        <v>1.4E-2</v>
       </c>
       <c r="BH14" s="27">
-        <v>1.4E-2</v>
-      </c>
-      <c r="BI14" s="27">
         <v>200</v>
       </c>
-      <c r="BJ14" s="26"/>
+      <c r="BI14" s="26"/>
+      <c r="BJ14" s="30"/>
       <c r="BK14" s="30"/>
       <c r="BL14" s="30"/>
       <c r="BM14" s="30"/>
@@ -3764,72 +3742,71 @@
       <c r="BU14" s="30"/>
       <c r="BV14" s="30"/>
       <c r="BW14" s="30"/>
-      <c r="BX14" s="30"/>
+      <c r="BX14" s="26"/>
       <c r="BY14" s="26"/>
       <c r="BZ14" s="26"/>
-      <c r="CA14" s="26"/>
+      <c r="CA14" s="30"/>
       <c r="CB14" s="30"/>
       <c r="CC14" s="30"/>
-      <c r="CD14" s="30"/>
-      <c r="CE14" s="26" t="s">
-        <v>269</v>
-      </c>
+      <c r="CD14" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="CE14" s="26"/>
       <c r="CF14" s="26"/>
       <c r="CG14" s="26"/>
-      <c r="CH14" s="26"/>
     </row>
-    <row r="15" spans="1:86" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:85" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
       <c r="B15" s="25"/>
       <c r="C15" s="34" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I15" s="26"/>
-      <c r="J15" s="26" t="s">
-        <v>261</v>
+      <c r="J15" s="36" t="s">
+        <v>275</v>
       </c>
       <c r="K15" s="26"/>
       <c r="L15" s="26"/>
       <c r="M15" s="26"/>
-      <c r="N15" s="26"/>
+      <c r="N15" s="26" t="s">
+        <v>237</v>
+      </c>
       <c r="O15" s="26" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P15" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q15" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="Q15" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="R15" s="26" t="s">
-        <v>242</v>
-      </c>
+      <c r="R15" s="27"/>
       <c r="S15" s="27"/>
-      <c r="T15" s="27"/>
+      <c r="T15" s="28"/>
       <c r="U15" s="28"/>
-      <c r="V15" s="28"/>
-      <c r="W15" s="26"/>
-      <c r="X15" s="28"/>
+      <c r="V15" s="26"/>
+      <c r="W15" s="28"/>
+      <c r="X15" s="27">
+        <v>2.169024E-2</v>
+      </c>
       <c r="Y15" s="27">
-        <v>2.169024E-2</v>
+        <v>1.4276580000000001E-2</v>
       </c>
       <c r="Z15" s="27">
         <v>1.4276580000000001E-2</v>
       </c>
-      <c r="AA15" s="27">
-        <v>1.4276580000000001E-2</v>
-      </c>
-      <c r="AB15" s="27"/>
-      <c r="AC15" s="26"/>
-      <c r="AD15" s="35" t="s">
-        <v>243</v>
-      </c>
+      <c r="AA15" s="27"/>
+      <c r="AB15" s="26"/>
+      <c r="AC15" s="35" t="s">
+        <v>241</v>
+      </c>
+      <c r="AD15" s="26"/>
       <c r="AE15" s="26"/>
       <c r="AF15" s="26"/>
       <c r="AG15" s="26"/>
@@ -3842,130 +3819,129 @@
       <c r="AN15" s="26"/>
       <c r="AO15" s="26"/>
       <c r="AP15" s="26"/>
-      <c r="AQ15" s="26"/>
-      <c r="AR15" s="26" t="s">
-        <v>244</v>
-      </c>
+      <c r="AQ15" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="AR15" s="26"/>
       <c r="AS15" s="26"/>
       <c r="AT15" s="26"/>
       <c r="AU15" s="26"/>
-      <c r="AV15" s="26"/>
-      <c r="AW15" s="26" t="s">
-        <v>269</v>
-      </c>
+      <c r="AV15" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="AW15" s="27"/>
       <c r="AX15" s="27"/>
-      <c r="AY15" s="27"/>
-      <c r="AZ15" s="27">
+      <c r="AY15" s="27">
         <v>0.200098</v>
       </c>
+      <c r="AZ15" s="26" t="s">
+        <v>243</v>
+      </c>
       <c r="BA15" s="26" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="BB15" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="BC15" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="BD15" s="29"/>
+        <v>242</v>
+      </c>
+      <c r="BC15" s="29"/>
+      <c r="BD15" s="27">
+        <v>3</v>
+      </c>
       <c r="BE15" s="27">
-        <v>3</v>
+        <v>1440</v>
       </c>
       <c r="BF15" s="27">
-        <v>1440</v>
+        <v>70</v>
       </c>
       <c r="BG15" s="27">
-        <v>70</v>
+        <v>1.4E-2</v>
       </c>
       <c r="BH15" s="27">
-        <v>1.4E-2</v>
-      </c>
-      <c r="BI15" s="27">
         <v>200</v>
       </c>
-      <c r="BJ15" s="26"/>
-      <c r="BK15" s="29"/>
+      <c r="BI15" s="26"/>
+      <c r="BJ15" s="29"/>
+      <c r="BK15" s="26"/>
       <c r="BL15" s="26"/>
       <c r="BM15" s="26"/>
-      <c r="BN15" s="26"/>
-      <c r="BO15" s="29"/>
-      <c r="BP15" s="26"/>
-      <c r="BQ15" s="29"/>
-      <c r="BR15" s="26"/>
+      <c r="BN15" s="29"/>
+      <c r="BO15" s="26"/>
+      <c r="BP15" s="29"/>
+      <c r="BQ15" s="26"/>
+      <c r="BR15" s="29"/>
       <c r="BS15" s="29"/>
       <c r="BT15" s="29"/>
       <c r="BU15" s="29"/>
       <c r="BV15" s="29"/>
       <c r="BW15" s="29"/>
-      <c r="BX15" s="29"/>
+      <c r="BX15" s="26"/>
       <c r="BY15" s="26"/>
       <c r="BZ15" s="26"/>
-      <c r="CA15" s="26"/>
+      <c r="CA15" s="29"/>
       <c r="CB15" s="29"/>
-      <c r="CC15" s="29"/>
-      <c r="CD15" s="26"/>
-      <c r="CE15" s="26" t="s">
-        <v>269</v>
-      </c>
+      <c r="CC15" s="26"/>
+      <c r="CD15" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="CE15" s="26"/>
       <c r="CF15" s="26"/>
       <c r="CG15" s="26"/>
-      <c r="CH15" s="26"/>
     </row>
-    <row r="16" spans="1:86" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:85" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
       <c r="C16" s="26" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I16" s="26"/>
-      <c r="J16" s="26" t="s">
-        <v>261</v>
+      <c r="J16" s="36" t="s">
+        <v>275</v>
       </c>
       <c r="K16" s="26"/>
       <c r="L16" s="26"/>
       <c r="M16" s="26"/>
-      <c r="N16" s="26"/>
+      <c r="N16" s="26" t="s">
+        <v>237</v>
+      </c>
       <c r="O16" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="P16" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="P16" s="26" t="s">
+      <c r="Q16" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="Q16" s="26" t="s">
-        <v>241</v>
-      </c>
-      <c r="R16" s="26" t="s">
-        <v>242</v>
-      </c>
+      <c r="R16" s="27"/>
       <c r="S16" s="27"/>
-      <c r="T16" s="27"/>
+      <c r="T16" s="30"/>
       <c r="U16" s="30"/>
       <c r="V16" s="30"/>
       <c r="W16" s="30"/>
-      <c r="X16" s="30"/>
+      <c r="X16" s="27">
+        <v>1.5365230000000001E-2</v>
+      </c>
       <c r="Y16" s="27">
         <v>1.5365230000000001E-2</v>
       </c>
       <c r="Z16" s="27">
         <v>1.5365230000000001E-2</v>
       </c>
-      <c r="AA16" s="27">
-        <v>1.5365230000000001E-2</v>
-      </c>
+      <c r="AA16" s="27"/>
       <c r="AB16" s="27"/>
-      <c r="AC16" s="27"/>
-      <c r="AD16" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="AE16" s="27"/>
+      <c r="AC16" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="AD16" s="27"/>
+      <c r="AE16" s="26"/>
       <c r="AF16" s="26"/>
       <c r="AG16" s="26"/>
       <c r="AH16" s="26"/>
@@ -3977,48 +3953,48 @@
       <c r="AN16" s="26"/>
       <c r="AO16" s="26"/>
       <c r="AP16" s="26"/>
-      <c r="AQ16" s="26"/>
-      <c r="AR16" s="26" t="s">
-        <v>244</v>
-      </c>
+      <c r="AQ16" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="AR16" s="26"/>
       <c r="AS16" s="26"/>
       <c r="AT16" s="26"/>
       <c r="AU16" s="26"/>
-      <c r="AV16" s="26"/>
-      <c r="AW16" s="26" t="s">
-        <v>269</v>
-      </c>
+      <c r="AV16" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="AW16" s="27"/>
       <c r="AX16" s="27"/>
-      <c r="AY16" s="27"/>
-      <c r="AZ16" s="27">
+      <c r="AY16" s="27">
         <v>0.200098</v>
       </c>
+      <c r="AZ16" s="26" t="s">
+        <v>243</v>
+      </c>
       <c r="BA16" s="26" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="BB16" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="BC16" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="BD16" s="30"/>
+        <v>242</v>
+      </c>
+      <c r="BC16" s="30"/>
+      <c r="BD16" s="27">
+        <v>3</v>
+      </c>
       <c r="BE16" s="27">
-        <v>3</v>
+        <v>1680</v>
       </c>
       <c r="BF16" s="27">
-        <v>1680</v>
+        <v>70</v>
       </c>
       <c r="BG16" s="27">
-        <v>70</v>
+        <v>1.54E-2</v>
       </c>
       <c r="BH16" s="27">
-        <v>1.54E-2</v>
-      </c>
-      <c r="BI16" s="27">
         <v>220</v>
       </c>
-      <c r="BJ16" s="26"/>
+      <c r="BI16" s="26"/>
+      <c r="BJ16" s="30"/>
       <c r="BK16" s="30"/>
       <c r="BL16" s="30"/>
       <c r="BM16" s="30"/>
@@ -4032,19 +4008,18 @@
       <c r="BU16" s="30"/>
       <c r="BV16" s="30"/>
       <c r="BW16" s="30"/>
-      <c r="BX16" s="30"/>
+      <c r="BX16" s="26"/>
       <c r="BY16" s="26"/>
       <c r="BZ16" s="26"/>
-      <c r="CA16" s="26"/>
+      <c r="CA16" s="30"/>
       <c r="CB16" s="30"/>
       <c r="CC16" s="30"/>
-      <c r="CD16" s="30"/>
-      <c r="CE16" s="26" t="s">
-        <v>269</v>
-      </c>
+      <c r="CD16" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="CE16" s="26"/>
       <c r="CF16" s="26"/>
       <c r="CG16" s="26"/>
-      <c r="CH16" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
